--- a/proxybuying-obsidian/AI-Context/references/TabsStatus_Part-2.xlsx
+++ b/proxybuying-obsidian/AI-Context/references/TabsStatus_Part-2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">TABS STATUS - PART-2</t>
   </si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">PAYMENT TERMS</t>
   </si>
   <si>
-    <t>Show/Close</t>
+    <t>Collapsed</t>
   </si>
   <si>
     <t>NOTES</t>
@@ -81,7 +81,10 @@
     <t>Open</t>
   </si>
   <si>
-    <t xml:space="preserve">Open - Note 10.1</t>
+    <t xml:space="preserve">Expanded +)</t>
+  </si>
+  <si>
+    <t>Expanded</t>
   </si>
   <si>
     <t xml:space="preserve">MESSAGE W/ PROXY</t>
@@ -93,19 +96,16 @@
     <t>PAYMENT</t>
   </si>
   <si>
-    <t>Closed</t>
-  </si>
-  <si>
     <t xml:space="preserve"> TABS STATUS ON PROXY BUYER PAGE</t>
   </si>
   <si>
     <t xml:space="preserve">MESSAGE W/ BUYER</t>
   </si>
   <si>
-    <t xml:space="preserve">Show/Close - Note 6-1</t>
+    <t xml:space="preserve">Collapsed +)</t>
   </si>
   <si>
-    <t>Never</t>
+    <t>Hidden</t>
   </si>
   <si>
     <t xml:space="preserve"> TABS STATUS ON CARRIER PAGE</t>
@@ -123,7 +123,10 @@
     <t xml:space="preserve"> Step-7 already covered in Step-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> 10.1 = grep shows the file is /templates//trips/_order_detail_body.html:266 - I have edited the file on staging, purge cloudflare cache, hard reset the browser but the text won't changed.</t>
+    <t xml:space="preserve"> 10.2 = grep shows the file is /templates//trips/_order_detail_body.html:266 - I have edited the file on staging, purge cloudflare cache, hard reset the browser but the text won't changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strangely, my edited text is shown on step-11 - not on step 10-2</t>
   </si>
   <si>
     <r>
@@ -150,7 +153,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.000000"/>
       <name val="Arial"/>
@@ -175,21 +178,17 @@
     </font>
     <font/>
     <font>
+      <b/>
       <sz val="10.000000"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10.000000"/>
       <color indexed="2"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.000000"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -236,7 +235,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -272,6 +271,21 @@
     </border>
     <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
         <color theme="1"/>
       </left>
       <right style="thin">
@@ -282,21 +296,6 @@
       </top>
       <bottom style="thin">
         <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -348,11 +347,48 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -371,98 +407,92 @@
     </xf>
     <xf fontId="4" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="2" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="4" numFmtId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="1" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="1" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="4" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf fontId="6" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
-    <xf fontId="8" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -474,8 +504,17 @@
     <xf fontId="3" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="6" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="6" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="6" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1018,16 +1057,16 @@
       <c r="C2" s="7">
         <v>6</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>8</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>9</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="8">
@@ -1055,22 +1094,22 @@
         <v>4</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="4"/>
@@ -1095,22 +1134,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>15</v>
       </c>
       <c r="I4" s="4"/>
@@ -1131,28 +1170,28 @@
       <c r="X4" s="4"/>
     </row>
     <row r="5" ht="27">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="12" t="s">
         <v>18</v>
       </c>
       <c r="I5" s="4"/>
@@ -1173,27 +1212,27 @@
       <c r="X5" s="4"/>
     </row>
     <row r="6" ht="27">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>20</v>
+      <c r="H6" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -1213,26 +1252,26 @@
       <c r="X6" s="4"/>
     </row>
     <row r="7" ht="27">
-      <c r="A7" s="18"/>
-      <c r="B7" s="21" t="s">
-        <v>22</v>
+      <c r="A7" s="16"/>
+      <c r="B7" s="19" t="s">
+        <v>23</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="4"/>
@@ -1253,26 +1292,26 @@
       <c r="X7" s="4"/>
     </row>
     <row r="8" ht="27">
-      <c r="A8" s="18"/>
-      <c r="B8" s="21" t="s">
-        <v>23</v>
+      <c r="A8" s="16"/>
+      <c r="B8" s="19" t="s">
+        <v>24</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="4"/>
@@ -1293,27 +1332,27 @@
       <c r="X8" s="4"/>
     </row>
     <row r="9">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>25</v>
+      <c r="C9" s="10" t="s">
+        <v>18</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>25</v>
+      <c r="D9" s="22" t="s">
+        <v>18</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="E9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>25</v>
+      <c r="H9" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1333,28 +1372,28 @@
       <c r="X9" s="4"/>
     </row>
     <row r="10" ht="27">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="25" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="4"/>
@@ -1375,26 +1414,26 @@
       <c r="X10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="18"/>
-      <c r="B11" s="27" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>20</v>
+      <c r="C11" s="25" t="s">
+        <v>22</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>20</v>
+      <c r="D11" s="25" t="s">
+        <v>22</v>
       </c>
-      <c r="E11" s="28" t="s">
-        <v>20</v>
+      <c r="E11" s="25" t="s">
+        <v>22</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="25" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="4"/>
@@ -1415,26 +1454,26 @@
       <c r="X11" s="4"/>
     </row>
     <row r="12" ht="27">
-      <c r="A12" s="18"/>
-      <c r="B12" s="29" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="25" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="4"/>
@@ -1455,26 +1494,26 @@
       <c r="X12" s="4"/>
     </row>
     <row r="13" ht="27">
-      <c r="A13" s="18"/>
-      <c r="B13" s="30" t="s">
-        <v>23</v>
+      <c r="A13" s="16"/>
+      <c r="B13" s="28" t="s">
+        <v>24</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="25" t="s">
         <v>18</v>
       </c>
       <c r="I13" s="4"/>
@@ -1495,26 +1534,26 @@
       <c r="X13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="22"/>
-      <c r="B14" s="31" t="s">
-        <v>24</v>
+      <c r="A14" s="20"/>
+      <c r="B14" s="29" t="s">
+        <v>25</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="25" t="s">
         <v>29</v>
       </c>
       <c r="I14" s="4"/>
@@ -1535,28 +1574,28 @@
       <c r="X14" s="4"/>
     </row>
     <row r="15" ht="27">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="4"/>
@@ -1577,27 +1616,27 @@
       <c r="X15" s="4"/>
     </row>
     <row r="16">
-      <c r="A16" s="18"/>
-      <c r="B16" s="34" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>20</v>
+      <c r="C16" s="10" t="s">
+        <v>22</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>20</v>
+      <c r="D16" s="10" t="s">
+        <v>22</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>20</v>
+      <c r="E16" s="10" t="s">
+        <v>22</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>20</v>
+      <c r="G16" s="10" t="s">
+        <v>22</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>20</v>
+      <c r="H16" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -1617,26 +1656,26 @@
       <c r="X16" s="4"/>
     </row>
     <row r="17" ht="27">
-      <c r="A17" s="18"/>
-      <c r="B17" s="35" t="s">
+      <c r="A17" s="16"/>
+      <c r="B17" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I17" s="4"/>
@@ -1657,26 +1696,26 @@
       <c r="X17" s="4"/>
     </row>
     <row r="18" ht="27">
-      <c r="A18" s="18"/>
-      <c r="B18" s="35" t="s">
-        <v>22</v>
+      <c r="A18" s="16"/>
+      <c r="B18" s="33" t="s">
+        <v>23</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I18" s="4"/>
@@ -1697,26 +1736,26 @@
       <c r="X18" s="4"/>
     </row>
     <row r="19">
-      <c r="A19" s="22"/>
-      <c r="B19" s="36" t="s">
-        <v>24</v>
+      <c r="A19" s="20"/>
+      <c r="B19" s="34" t="s">
+        <v>25</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="10" t="s">
         <v>29</v>
       </c>
       <c r="I19" s="4"/>
@@ -1737,7 +1776,7 @@
       <c r="X19" s="4"/>
     </row>
     <row r="20">
-      <c r="A20" s="37"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1763,7 +1802,7 @@
       <c r="X20" s="4"/>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="36" t="s">
         <v>31</v>
       </c>
       <c r="B21" s="4"/>
@@ -1791,16 +1830,16 @@
       <c r="X21" s="4"/>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="41"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -1819,16 +1858,16 @@
       <c r="X22" s="4"/>
     </row>
     <row r="23" ht="29.25" customHeight="1">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="41"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="39"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -1847,16 +1886,16 @@
       <c r="X23" s="4"/>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="41"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
@@ -1875,16 +1914,16 @@
       <c r="X24" s="4"/>
     </row>
     <row r="25" ht="28.5" customHeight="1">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="41"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="39"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -1902,17 +1941,17 @@
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
     </row>
-    <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="43" t="s">
+    <row r="26" ht="15.75">
+      <c r="A26" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="41"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
@@ -1930,7 +1969,17 @@
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
     </row>
-    <row r="27">
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
@@ -1949,14 +1998,6 @@
       <c r="X27" s="4"/>
     </row>
     <row r="28">
-      <c r="A28" s="37"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
@@ -1975,7 +2016,7 @@
       <c r="X28" s="4"/>
     </row>
     <row r="29">
-      <c r="A29" s="37"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -2001,7 +2042,7 @@
       <c r="X29" s="4"/>
     </row>
     <row r="30">
-      <c r="A30" s="37"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -2027,7 +2068,7 @@
       <c r="X30" s="4"/>
     </row>
     <row r="31">
-      <c r="A31" s="37"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -2053,7 +2094,7 @@
       <c r="X31" s="4"/>
     </row>
     <row r="32">
-      <c r="A32" s="37"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -2079,7 +2120,7 @@
       <c r="X32" s="4"/>
     </row>
     <row r="33">
-      <c r="A33" s="37"/>
+      <c r="A33" s="35"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -2105,7 +2146,7 @@
       <c r="X33" s="4"/>
     </row>
     <row r="34">
-      <c r="A34" s="37"/>
+      <c r="A34" s="35"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -2131,7 +2172,7 @@
       <c r="X34" s="4"/>
     </row>
     <row r="35">
-      <c r="A35" s="37"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -2157,7 +2198,7 @@
       <c r="X35" s="4"/>
     </row>
     <row r="36">
-      <c r="A36" s="37"/>
+      <c r="A36" s="35"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -2183,7 +2224,7 @@
       <c r="X36" s="4"/>
     </row>
     <row r="37">
-      <c r="A37" s="37"/>
+      <c r="A37" s="35"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -2209,7 +2250,7 @@
       <c r="X37" s="4"/>
     </row>
     <row r="38">
-      <c r="A38" s="37"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -2235,7 +2276,7 @@
       <c r="X38" s="4"/>
     </row>
     <row r="39">
-      <c r="A39" s="37"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -2261,7 +2302,7 @@
       <c r="X39" s="4"/>
     </row>
     <row r="40">
-      <c r="A40" s="37"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -2287,7 +2328,7 @@
       <c r="X40" s="4"/>
     </row>
     <row r="41">
-      <c r="A41" s="37"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -2313,7 +2354,7 @@
       <c r="X41" s="4"/>
     </row>
     <row r="42">
-      <c r="A42" s="37"/>
+      <c r="A42" s="35"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -2339,7 +2380,7 @@
       <c r="X42" s="4"/>
     </row>
     <row r="43">
-      <c r="A43" s="37"/>
+      <c r="A43" s="35"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -2365,7 +2406,7 @@
       <c r="X43" s="4"/>
     </row>
     <row r="44">
-      <c r="A44" s="37"/>
+      <c r="A44" s="35"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -2391,7 +2432,7 @@
       <c r="X44" s="4"/>
     </row>
     <row r="45">
-      <c r="A45" s="37"/>
+      <c r="A45" s="35"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -2417,7 +2458,7 @@
       <c r="X45" s="4"/>
     </row>
     <row r="46">
-      <c r="A46" s="37"/>
+      <c r="A46" s="35"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -2443,7 +2484,7 @@
       <c r="X46" s="4"/>
     </row>
     <row r="47">
-      <c r="A47" s="37"/>
+      <c r="A47" s="35"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -2469,7 +2510,7 @@
       <c r="X47" s="4"/>
     </row>
     <row r="48">
-      <c r="A48" s="37"/>
+      <c r="A48" s="35"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -2495,7 +2536,7 @@
       <c r="X48" s="4"/>
     </row>
     <row r="49">
-      <c r="A49" s="37"/>
+      <c r="A49" s="35"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -2521,7 +2562,7 @@
       <c r="X49" s="4"/>
     </row>
     <row r="50">
-      <c r="A50" s="37"/>
+      <c r="A50" s="35"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -2547,7 +2588,7 @@
       <c r="X50" s="4"/>
     </row>
     <row r="51">
-      <c r="A51" s="37"/>
+      <c r="A51" s="35"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -2573,7 +2614,7 @@
       <c r="X51" s="4"/>
     </row>
     <row r="52">
-      <c r="A52" s="37"/>
+      <c r="A52" s="35"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -2599,7 +2640,7 @@
       <c r="X52" s="4"/>
     </row>
     <row r="53">
-      <c r="A53" s="37"/>
+      <c r="A53" s="35"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -2625,7 +2666,7 @@
       <c r="X53" s="4"/>
     </row>
     <row r="54">
-      <c r="A54" s="37"/>
+      <c r="A54" s="35"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -2651,7 +2692,7 @@
       <c r="X54" s="4"/>
     </row>
     <row r="55">
-      <c r="A55" s="37"/>
+      <c r="A55" s="35"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -2677,7 +2718,7 @@
       <c r="X55" s="4"/>
     </row>
     <row r="56">
-      <c r="A56" s="37"/>
+      <c r="A56" s="35"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -2703,7 +2744,7 @@
       <c r="X56" s="4"/>
     </row>
     <row r="57">
-      <c r="A57" s="37"/>
+      <c r="A57" s="35"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
@@ -2729,7 +2770,7 @@
       <c r="X57" s="4"/>
     </row>
     <row r="58">
-      <c r="A58" s="37"/>
+      <c r="A58" s="35"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
@@ -2755,7 +2796,7 @@
       <c r="X58" s="4"/>
     </row>
     <row r="59">
-      <c r="A59" s="37"/>
+      <c r="A59" s="35"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -2781,7 +2822,7 @@
       <c r="X59" s="4"/>
     </row>
     <row r="60">
-      <c r="A60" s="37"/>
+      <c r="A60" s="35"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
@@ -2807,7 +2848,7 @@
       <c r="X60" s="4"/>
     </row>
     <row r="61">
-      <c r="A61" s="37"/>
+      <c r="A61" s="35"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
@@ -2833,7 +2874,7 @@
       <c r="X61" s="4"/>
     </row>
     <row r="62">
-      <c r="A62" s="37"/>
+      <c r="A62" s="35"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
@@ -2859,7 +2900,7 @@
       <c r="X62" s="4"/>
     </row>
     <row r="63">
-      <c r="A63" s="37"/>
+      <c r="A63" s="35"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
@@ -2885,7 +2926,7 @@
       <c r="X63" s="4"/>
     </row>
     <row r="64">
-      <c r="A64" s="37"/>
+      <c r="A64" s="35"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
@@ -2911,7 +2952,7 @@
       <c r="X64" s="4"/>
     </row>
     <row r="65">
-      <c r="A65" s="37"/>
+      <c r="A65" s="35"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
@@ -2937,7 +2978,7 @@
       <c r="X65" s="4"/>
     </row>
     <row r="66">
-      <c r="A66" s="37"/>
+      <c r="A66" s="35"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
@@ -2963,7 +3004,7 @@
       <c r="X66" s="4"/>
     </row>
     <row r="67">
-      <c r="A67" s="37"/>
+      <c r="A67" s="35"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
@@ -2989,7 +3030,7 @@
       <c r="X67" s="4"/>
     </row>
     <row r="68">
-      <c r="A68" s="37"/>
+      <c r="A68" s="35"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -3015,7 +3056,7 @@
       <c r="X68" s="4"/>
     </row>
     <row r="69">
-      <c r="A69" s="37"/>
+      <c r="A69" s="35"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -3041,7 +3082,7 @@
       <c r="X69" s="4"/>
     </row>
     <row r="70">
-      <c r="A70" s="37"/>
+      <c r="A70" s="35"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -3067,7 +3108,7 @@
       <c r="X70" s="4"/>
     </row>
     <row r="71">
-      <c r="A71" s="37"/>
+      <c r="A71" s="35"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -3093,7 +3134,7 @@
       <c r="X71" s="4"/>
     </row>
     <row r="72">
-      <c r="A72" s="37"/>
+      <c r="A72" s="35"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -3119,7 +3160,7 @@
       <c r="X72" s="4"/>
     </row>
     <row r="73">
-      <c r="A73" s="37"/>
+      <c r="A73" s="35"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -3145,7 +3186,7 @@
       <c r="X73" s="4"/>
     </row>
     <row r="74">
-      <c r="A74" s="37"/>
+      <c r="A74" s="35"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -3171,7 +3212,7 @@
       <c r="X74" s="4"/>
     </row>
     <row r="75">
-      <c r="A75" s="37"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -3197,7 +3238,7 @@
       <c r="X75" s="4"/>
     </row>
     <row r="76">
-      <c r="A76" s="37"/>
+      <c r="A76" s="35"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -3223,7 +3264,7 @@
       <c r="X76" s="4"/>
     </row>
     <row r="77">
-      <c r="A77" s="37"/>
+      <c r="A77" s="35"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -3249,7 +3290,7 @@
       <c r="X77" s="4"/>
     </row>
     <row r="78">
-      <c r="A78" s="37"/>
+      <c r="A78" s="35"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -3275,7 +3316,7 @@
       <c r="X78" s="4"/>
     </row>
     <row r="79">
-      <c r="A79" s="37"/>
+      <c r="A79" s="35"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -3301,7 +3342,7 @@
       <c r="X79" s="4"/>
     </row>
     <row r="80">
-      <c r="A80" s="37"/>
+      <c r="A80" s="35"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -3327,7 +3368,7 @@
       <c r="X80" s="4"/>
     </row>
     <row r="81">
-      <c r="A81" s="37"/>
+      <c r="A81" s="35"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -3353,7 +3394,7 @@
       <c r="X81" s="4"/>
     </row>
     <row r="82">
-      <c r="A82" s="37"/>
+      <c r="A82" s="35"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -3379,7 +3420,7 @@
       <c r="X82" s="4"/>
     </row>
     <row r="83">
-      <c r="A83" s="37"/>
+      <c r="A83" s="35"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -3405,7 +3446,7 @@
       <c r="X83" s="4"/>
     </row>
     <row r="84">
-      <c r="A84" s="37"/>
+      <c r="A84" s="35"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -3431,7 +3472,7 @@
       <c r="X84" s="4"/>
     </row>
     <row r="85">
-      <c r="A85" s="37"/>
+      <c r="A85" s="35"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -3457,7 +3498,7 @@
       <c r="X85" s="4"/>
     </row>
     <row r="86">
-      <c r="A86" s="37"/>
+      <c r="A86" s="35"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -3483,7 +3524,7 @@
       <c r="X86" s="4"/>
     </row>
     <row r="87">
-      <c r="A87" s="37"/>
+      <c r="A87" s="35"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -3509,7 +3550,7 @@
       <c r="X87" s="4"/>
     </row>
     <row r="88">
-      <c r="A88" s="37"/>
+      <c r="A88" s="35"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -3535,7 +3576,7 @@
       <c r="X88" s="4"/>
     </row>
     <row r="89">
-      <c r="A89" s="37"/>
+      <c r="A89" s="35"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -3561,7 +3602,7 @@
       <c r="X89" s="4"/>
     </row>
     <row r="90">
-      <c r="A90" s="37"/>
+      <c r="A90" s="35"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -3587,7 +3628,7 @@
       <c r="X90" s="4"/>
     </row>
     <row r="91">
-      <c r="A91" s="37"/>
+      <c r="A91" s="35"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -3613,7 +3654,7 @@
       <c r="X91" s="4"/>
     </row>
     <row r="92">
-      <c r="A92" s="37"/>
+      <c r="A92" s="35"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -3639,7 +3680,7 @@
       <c r="X92" s="4"/>
     </row>
     <row r="93">
-      <c r="A93" s="37"/>
+      <c r="A93" s="35"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -3665,7 +3706,7 @@
       <c r="X93" s="4"/>
     </row>
     <row r="94">
-      <c r="A94" s="37"/>
+      <c r="A94" s="35"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -3691,7 +3732,7 @@
       <c r="X94" s="4"/>
     </row>
     <row r="95">
-      <c r="A95" s="37"/>
+      <c r="A95" s="35"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -3717,7 +3758,7 @@
       <c r="X95" s="4"/>
     </row>
     <row r="96">
-      <c r="A96" s="37"/>
+      <c r="A96" s="35"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
@@ -3743,7 +3784,7 @@
       <c r="X96" s="4"/>
     </row>
     <row r="97">
-      <c r="A97" s="37"/>
+      <c r="A97" s="35"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -3769,7 +3810,7 @@
       <c r="X97" s="4"/>
     </row>
     <row r="98">
-      <c r="A98" s="37"/>
+      <c r="A98" s="35"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
@@ -3795,7 +3836,7 @@
       <c r="X98" s="4"/>
     </row>
     <row r="99">
-      <c r="A99" s="37"/>
+      <c r="A99" s="35"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -3821,7 +3862,7 @@
       <c r="X99" s="4"/>
     </row>
     <row r="100">
-      <c r="A100" s="37"/>
+      <c r="A100" s="35"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -3847,7 +3888,7 @@
       <c r="X100" s="4"/>
     </row>
     <row r="101">
-      <c r="A101" s="37"/>
+      <c r="A101" s="35"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -3873,7 +3914,7 @@
       <c r="X101" s="4"/>
     </row>
     <row r="102">
-      <c r="A102" s="37"/>
+      <c r="A102" s="35"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -3899,7 +3940,7 @@
       <c r="X102" s="4"/>
     </row>
     <row r="103">
-      <c r="A103" s="37"/>
+      <c r="A103" s="35"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
@@ -3925,7 +3966,7 @@
       <c r="X103" s="4"/>
     </row>
     <row r="104">
-      <c r="A104" s="37"/>
+      <c r="A104" s="35"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
@@ -3951,7 +3992,7 @@
       <c r="X104" s="4"/>
     </row>
     <row r="105">
-      <c r="A105" s="37"/>
+      <c r="A105" s="35"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
@@ -3977,7 +4018,7 @@
       <c r="X105" s="4"/>
     </row>
     <row r="106">
-      <c r="A106" s="37"/>
+      <c r="A106" s="35"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
@@ -4003,7 +4044,7 @@
       <c r="X106" s="4"/>
     </row>
     <row r="107">
-      <c r="A107" s="37"/>
+      <c r="A107" s="35"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
@@ -4029,7 +4070,7 @@
       <c r="X107" s="4"/>
     </row>
     <row r="108">
-      <c r="A108" s="37"/>
+      <c r="A108" s="35"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
@@ -4055,7 +4096,7 @@
       <c r="X108" s="4"/>
     </row>
     <row r="109">
-      <c r="A109" s="37"/>
+      <c r="A109" s="35"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -4081,7 +4122,7 @@
       <c r="X109" s="4"/>
     </row>
     <row r="110">
-      <c r="A110" s="37"/>
+      <c r="A110" s="35"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
@@ -4107,7 +4148,7 @@
       <c r="X110" s="4"/>
     </row>
     <row r="111">
-      <c r="A111" s="37"/>
+      <c r="A111" s="35"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
@@ -4133,7 +4174,7 @@
       <c r="X111" s="4"/>
     </row>
     <row r="112">
-      <c r="A112" s="37"/>
+      <c r="A112" s="35"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
@@ -4159,7 +4200,7 @@
       <c r="X112" s="4"/>
     </row>
     <row r="113">
-      <c r="A113" s="37"/>
+      <c r="A113" s="35"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
@@ -4185,7 +4226,7 @@
       <c r="X113" s="4"/>
     </row>
     <row r="114">
-      <c r="A114" s="37"/>
+      <c r="A114" s="35"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
@@ -4211,7 +4252,7 @@
       <c r="X114" s="4"/>
     </row>
     <row r="115">
-      <c r="A115" s="37"/>
+      <c r="A115" s="35"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -4237,7 +4278,7 @@
       <c r="X115" s="4"/>
     </row>
     <row r="116">
-      <c r="A116" s="37"/>
+      <c r="A116" s="35"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -4263,7 +4304,7 @@
       <c r="X116" s="4"/>
     </row>
     <row r="117">
-      <c r="A117" s="37"/>
+      <c r="A117" s="35"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
@@ -4289,7 +4330,7 @@
       <c r="X117" s="4"/>
     </row>
     <row r="118">
-      <c r="A118" s="37"/>
+      <c r="A118" s="35"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
@@ -4315,7 +4356,7 @@
       <c r="X118" s="4"/>
     </row>
     <row r="119">
-      <c r="A119" s="37"/>
+      <c r="A119" s="35"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -4341,7 +4382,7 @@
       <c r="X119" s="4"/>
     </row>
     <row r="120">
-      <c r="A120" s="37"/>
+      <c r="A120" s="35"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
@@ -4367,7 +4408,7 @@
       <c r="X120" s="4"/>
     </row>
     <row r="121">
-      <c r="A121" s="37"/>
+      <c r="A121" s="35"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
@@ -4393,7 +4434,7 @@
       <c r="X121" s="4"/>
     </row>
     <row r="122">
-      <c r="A122" s="37"/>
+      <c r="A122" s="35"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
@@ -4419,7 +4460,7 @@
       <c r="X122" s="4"/>
     </row>
     <row r="123">
-      <c r="A123" s="37"/>
+      <c r="A123" s="35"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -4445,7 +4486,7 @@
       <c r="X123" s="4"/>
     </row>
     <row r="124">
-      <c r="A124" s="37"/>
+      <c r="A124" s="35"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
@@ -4471,7 +4512,7 @@
       <c r="X124" s="4"/>
     </row>
     <row r="125">
-      <c r="A125" s="37"/>
+      <c r="A125" s="35"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
@@ -4497,7 +4538,7 @@
       <c r="X125" s="4"/>
     </row>
     <row r="126">
-      <c r="A126" s="37"/>
+      <c r="A126" s="35"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
@@ -4523,7 +4564,7 @@
       <c r="X126" s="4"/>
     </row>
     <row r="127">
-      <c r="A127" s="37"/>
+      <c r="A127" s="35"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
@@ -4549,7 +4590,7 @@
       <c r="X127" s="4"/>
     </row>
     <row r="128">
-      <c r="A128" s="37"/>
+      <c r="A128" s="35"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
@@ -4575,7 +4616,7 @@
       <c r="X128" s="4"/>
     </row>
     <row r="129">
-      <c r="A129" s="37"/>
+      <c r="A129" s="35"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
@@ -4601,7 +4642,7 @@
       <c r="X129" s="4"/>
     </row>
     <row r="130">
-      <c r="A130" s="37"/>
+      <c r="A130" s="35"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -4627,7 +4668,7 @@
       <c r="X130" s="4"/>
     </row>
     <row r="131">
-      <c r="A131" s="37"/>
+      <c r="A131" s="35"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
@@ -4653,7 +4694,7 @@
       <c r="X131" s="4"/>
     </row>
     <row r="132">
-      <c r="A132" s="37"/>
+      <c r="A132" s="35"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -4679,7 +4720,7 @@
       <c r="X132" s="4"/>
     </row>
     <row r="133">
-      <c r="A133" s="37"/>
+      <c r="A133" s="35"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
@@ -4705,7 +4746,7 @@
       <c r="X133" s="4"/>
     </row>
     <row r="134">
-      <c r="A134" s="37"/>
+      <c r="A134" s="35"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
@@ -4731,7 +4772,7 @@
       <c r="X134" s="4"/>
     </row>
     <row r="135">
-      <c r="A135" s="37"/>
+      <c r="A135" s="35"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
@@ -4757,7 +4798,7 @@
       <c r="X135" s="4"/>
     </row>
     <row r="136">
-      <c r="A136" s="37"/>
+      <c r="A136" s="35"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
@@ -4783,7 +4824,7 @@
       <c r="X136" s="4"/>
     </row>
     <row r="137">
-      <c r="A137" s="37"/>
+      <c r="A137" s="35"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
@@ -4809,7 +4850,7 @@
       <c r="X137" s="4"/>
     </row>
     <row r="138">
-      <c r="A138" s="37"/>
+      <c r="A138" s="35"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
@@ -4835,7 +4876,7 @@
       <c r="X138" s="4"/>
     </row>
     <row r="139">
-      <c r="A139" s="37"/>
+      <c r="A139" s="35"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
@@ -4861,7 +4902,7 @@
       <c r="X139" s="4"/>
     </row>
     <row r="140">
-      <c r="A140" s="37"/>
+      <c r="A140" s="35"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
@@ -4887,7 +4928,7 @@
       <c r="X140" s="4"/>
     </row>
     <row r="141">
-      <c r="A141" s="37"/>
+      <c r="A141" s="35"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
@@ -4913,7 +4954,7 @@
       <c r="X141" s="4"/>
     </row>
     <row r="142">
-      <c r="A142" s="37"/>
+      <c r="A142" s="35"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
@@ -4939,7 +4980,7 @@
       <c r="X142" s="4"/>
     </row>
     <row r="143">
-      <c r="A143" s="37"/>
+      <c r="A143" s="35"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
@@ -4965,7 +5006,7 @@
       <c r="X143" s="4"/>
     </row>
     <row r="144">
-      <c r="A144" s="37"/>
+      <c r="A144" s="35"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
@@ -4991,7 +5032,7 @@
       <c r="X144" s="4"/>
     </row>
     <row r="145">
-      <c r="A145" s="37"/>
+      <c r="A145" s="35"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
@@ -5017,7 +5058,7 @@
       <c r="X145" s="4"/>
     </row>
     <row r="146">
-      <c r="A146" s="37"/>
+      <c r="A146" s="35"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
@@ -5043,7 +5084,7 @@
       <c r="X146" s="4"/>
     </row>
     <row r="147">
-      <c r="A147" s="37"/>
+      <c r="A147" s="35"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
@@ -5069,7 +5110,7 @@
       <c r="X147" s="4"/>
     </row>
     <row r="148">
-      <c r="A148" s="37"/>
+      <c r="A148" s="35"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
@@ -5095,7 +5136,7 @@
       <c r="X148" s="4"/>
     </row>
     <row r="149">
-      <c r="A149" s="37"/>
+      <c r="A149" s="35"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
@@ -5121,7 +5162,7 @@
       <c r="X149" s="4"/>
     </row>
     <row r="150">
-      <c r="A150" s="37"/>
+      <c r="A150" s="35"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
@@ -5147,7 +5188,7 @@
       <c r="X150" s="4"/>
     </row>
     <row r="151">
-      <c r="A151" s="37"/>
+      <c r="A151" s="35"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
@@ -5173,7 +5214,7 @@
       <c r="X151" s="4"/>
     </row>
     <row r="152">
-      <c r="A152" s="37"/>
+      <c r="A152" s="35"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
@@ -5199,7 +5240,7 @@
       <c r="X152" s="4"/>
     </row>
     <row r="153">
-      <c r="A153" s="37"/>
+      <c r="A153" s="35"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
@@ -5225,7 +5266,7 @@
       <c r="X153" s="4"/>
     </row>
     <row r="154">
-      <c r="A154" s="37"/>
+      <c r="A154" s="35"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
@@ -5251,7 +5292,7 @@
       <c r="X154" s="4"/>
     </row>
     <row r="155">
-      <c r="A155" s="37"/>
+      <c r="A155" s="35"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -5277,7 +5318,7 @@
       <c r="X155" s="4"/>
     </row>
     <row r="156">
-      <c r="A156" s="37"/>
+      <c r="A156" s="35"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -5303,7 +5344,7 @@
       <c r="X156" s="4"/>
     </row>
     <row r="157">
-      <c r="A157" s="37"/>
+      <c r="A157" s="35"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -5329,7 +5370,7 @@
       <c r="X157" s="4"/>
     </row>
     <row r="158">
-      <c r="A158" s="37"/>
+      <c r="A158" s="35"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
@@ -5355,7 +5396,7 @@
       <c r="X158" s="4"/>
     </row>
     <row r="159">
-      <c r="A159" s="37"/>
+      <c r="A159" s="35"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
@@ -5381,7 +5422,7 @@
       <c r="X159" s="4"/>
     </row>
     <row r="160">
-      <c r="A160" s="37"/>
+      <c r="A160" s="35"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
@@ -5407,7 +5448,7 @@
       <c r="X160" s="4"/>
     </row>
     <row r="161">
-      <c r="A161" s="37"/>
+      <c r="A161" s="35"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -5433,7 +5474,7 @@
       <c r="X161" s="4"/>
     </row>
     <row r="162">
-      <c r="A162" s="37"/>
+      <c r="A162" s="35"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
@@ -5459,7 +5500,7 @@
       <c r="X162" s="4"/>
     </row>
     <row r="163">
-      <c r="A163" s="37"/>
+      <c r="A163" s="35"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
@@ -5485,7 +5526,7 @@
       <c r="X163" s="4"/>
     </row>
     <row r="164">
-      <c r="A164" s="37"/>
+      <c r="A164" s="35"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
@@ -5511,7 +5552,7 @@
       <c r="X164" s="4"/>
     </row>
     <row r="165">
-      <c r="A165" s="37"/>
+      <c r="A165" s="35"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
@@ -5537,7 +5578,7 @@
       <c r="X165" s="4"/>
     </row>
     <row r="166">
-      <c r="A166" s="37"/>
+      <c r="A166" s="35"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
@@ -5563,7 +5604,7 @@
       <c r="X166" s="4"/>
     </row>
     <row r="167">
-      <c r="A167" s="37"/>
+      <c r="A167" s="35"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
@@ -5589,7 +5630,7 @@
       <c r="X167" s="4"/>
     </row>
     <row r="168">
-      <c r="A168" s="37"/>
+      <c r="A168" s="35"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
@@ -5615,7 +5656,7 @@
       <c r="X168" s="4"/>
     </row>
     <row r="169">
-      <c r="A169" s="37"/>
+      <c r="A169" s="35"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
@@ -5641,7 +5682,7 @@
       <c r="X169" s="4"/>
     </row>
     <row r="170">
-      <c r="A170" s="37"/>
+      <c r="A170" s="35"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
@@ -5667,7 +5708,7 @@
       <c r="X170" s="4"/>
     </row>
     <row r="171">
-      <c r="A171" s="37"/>
+      <c r="A171" s="35"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
@@ -5693,7 +5734,7 @@
       <c r="X171" s="4"/>
     </row>
     <row r="172">
-      <c r="A172" s="37"/>
+      <c r="A172" s="35"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
@@ -5719,7 +5760,7 @@
       <c r="X172" s="4"/>
     </row>
     <row r="173">
-      <c r="A173" s="37"/>
+      <c r="A173" s="35"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
@@ -5745,7 +5786,7 @@
       <c r="X173" s="4"/>
     </row>
     <row r="174">
-      <c r="A174" s="37"/>
+      <c r="A174" s="35"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
@@ -5771,7 +5812,7 @@
       <c r="X174" s="4"/>
     </row>
     <row r="175">
-      <c r="A175" s="37"/>
+      <c r="A175" s="35"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
@@ -5797,7 +5838,7 @@
       <c r="X175" s="4"/>
     </row>
     <row r="176">
-      <c r="A176" s="37"/>
+      <c r="A176" s="35"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
@@ -5823,7 +5864,7 @@
       <c r="X176" s="4"/>
     </row>
     <row r="177">
-      <c r="A177" s="37"/>
+      <c r="A177" s="35"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
@@ -5849,7 +5890,7 @@
       <c r="X177" s="4"/>
     </row>
     <row r="178">
-      <c r="A178" s="37"/>
+      <c r="A178" s="35"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
@@ -5875,7 +5916,7 @@
       <c r="X178" s="4"/>
     </row>
     <row r="179">
-      <c r="A179" s="37"/>
+      <c r="A179" s="35"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
@@ -5901,7 +5942,7 @@
       <c r="X179" s="4"/>
     </row>
     <row r="180">
-      <c r="A180" s="37"/>
+      <c r="A180" s="35"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
@@ -5927,7 +5968,7 @@
       <c r="X180" s="4"/>
     </row>
     <row r="181">
-      <c r="A181" s="37"/>
+      <c r="A181" s="35"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
@@ -5953,7 +5994,7 @@
       <c r="X181" s="4"/>
     </row>
     <row r="182">
-      <c r="A182" s="37"/>
+      <c r="A182" s="35"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
@@ -5979,7 +6020,7 @@
       <c r="X182" s="4"/>
     </row>
     <row r="183">
-      <c r="A183" s="37"/>
+      <c r="A183" s="35"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
@@ -6005,7 +6046,7 @@
       <c r="X183" s="4"/>
     </row>
     <row r="184">
-      <c r="A184" s="37"/>
+      <c r="A184" s="35"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
@@ -6031,7 +6072,7 @@
       <c r="X184" s="4"/>
     </row>
     <row r="185">
-      <c r="A185" s="37"/>
+      <c r="A185" s="35"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
@@ -6057,7 +6098,7 @@
       <c r="X185" s="4"/>
     </row>
     <row r="186">
-      <c r="A186" s="37"/>
+      <c r="A186" s="35"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
@@ -6083,7 +6124,7 @@
       <c r="X186" s="4"/>
     </row>
     <row r="187">
-      <c r="A187" s="37"/>
+      <c r="A187" s="35"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
@@ -6109,7 +6150,7 @@
       <c r="X187" s="4"/>
     </row>
     <row r="188">
-      <c r="A188" s="37"/>
+      <c r="A188" s="35"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
@@ -6135,7 +6176,7 @@
       <c r="X188" s="4"/>
     </row>
     <row r="189">
-      <c r="A189" s="37"/>
+      <c r="A189" s="35"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
@@ -6161,7 +6202,7 @@
       <c r="X189" s="4"/>
     </row>
     <row r="190">
-      <c r="A190" s="37"/>
+      <c r="A190" s="35"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
@@ -6187,7 +6228,7 @@
       <c r="X190" s="4"/>
     </row>
     <row r="191">
-      <c r="A191" s="37"/>
+      <c r="A191" s="35"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
@@ -6213,7 +6254,7 @@
       <c r="X191" s="4"/>
     </row>
     <row r="192">
-      <c r="A192" s="37"/>
+      <c r="A192" s="35"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
@@ -6239,7 +6280,7 @@
       <c r="X192" s="4"/>
     </row>
     <row r="193">
-      <c r="A193" s="37"/>
+      <c r="A193" s="35"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
@@ -6265,7 +6306,7 @@
       <c r="X193" s="4"/>
     </row>
     <row r="194">
-      <c r="A194" s="37"/>
+      <c r="A194" s="35"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
@@ -6291,7 +6332,7 @@
       <c r="X194" s="4"/>
     </row>
     <row r="195">
-      <c r="A195" s="37"/>
+      <c r="A195" s="35"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
@@ -6317,7 +6358,7 @@
       <c r="X195" s="4"/>
     </row>
     <row r="196">
-      <c r="A196" s="37"/>
+      <c r="A196" s="35"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
@@ -6343,7 +6384,7 @@
       <c r="X196" s="4"/>
     </row>
     <row r="197">
-      <c r="A197" s="37"/>
+      <c r="A197" s="35"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
@@ -6369,7 +6410,7 @@
       <c r="X197" s="4"/>
     </row>
     <row r="198">
-      <c r="A198" s="37"/>
+      <c r="A198" s="35"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
@@ -6395,7 +6436,7 @@
       <c r="X198" s="4"/>
     </row>
     <row r="199">
-      <c r="A199" s="37"/>
+      <c r="A199" s="35"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
@@ -6421,7 +6462,7 @@
       <c r="X199" s="4"/>
     </row>
     <row r="200">
-      <c r="A200" s="37"/>
+      <c r="A200" s="35"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
@@ -6447,7 +6488,7 @@
       <c r="X200" s="4"/>
     </row>
     <row r="201">
-      <c r="A201" s="37"/>
+      <c r="A201" s="35"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
@@ -6473,7 +6514,7 @@
       <c r="X201" s="4"/>
     </row>
     <row r="202">
-      <c r="A202" s="37"/>
+      <c r="A202" s="35"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
@@ -6499,7 +6540,7 @@
       <c r="X202" s="4"/>
     </row>
     <row r="203">
-      <c r="A203" s="37"/>
+      <c r="A203" s="35"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
@@ -6525,7 +6566,7 @@
       <c r="X203" s="4"/>
     </row>
     <row r="204">
-      <c r="A204" s="37"/>
+      <c r="A204" s="35"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
@@ -6551,7 +6592,7 @@
       <c r="X204" s="4"/>
     </row>
     <row r="205">
-      <c r="A205" s="37"/>
+      <c r="A205" s="35"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
@@ -6577,7 +6618,7 @@
       <c r="X205" s="4"/>
     </row>
     <row r="206">
-      <c r="A206" s="37"/>
+      <c r="A206" s="35"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
@@ -6603,7 +6644,7 @@
       <c r="X206" s="4"/>
     </row>
     <row r="207">
-      <c r="A207" s="37"/>
+      <c r="A207" s="35"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
@@ -6629,7 +6670,7 @@
       <c r="X207" s="4"/>
     </row>
     <row r="208">
-      <c r="A208" s="37"/>
+      <c r="A208" s="35"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
@@ -6655,7 +6696,7 @@
       <c r="X208" s="4"/>
     </row>
     <row r="209">
-      <c r="A209" s="37"/>
+      <c r="A209" s="35"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
@@ -6681,7 +6722,7 @@
       <c r="X209" s="4"/>
     </row>
     <row r="210">
-      <c r="A210" s="37"/>
+      <c r="A210" s="35"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
@@ -6707,7 +6748,7 @@
       <c r="X210" s="4"/>
     </row>
     <row r="211">
-      <c r="A211" s="37"/>
+      <c r="A211" s="35"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
@@ -6733,7 +6774,7 @@
       <c r="X211" s="4"/>
     </row>
     <row r="212">
-      <c r="A212" s="37"/>
+      <c r="A212" s="35"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
@@ -6759,7 +6800,7 @@
       <c r="X212" s="4"/>
     </row>
     <row r="213">
-      <c r="A213" s="37"/>
+      <c r="A213" s="35"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
@@ -6785,7 +6826,7 @@
       <c r="X213" s="4"/>
     </row>
     <row r="214">
-      <c r="A214" s="37"/>
+      <c r="A214" s="35"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
@@ -6811,7 +6852,7 @@
       <c r="X214" s="4"/>
     </row>
     <row r="215">
-      <c r="A215" s="37"/>
+      <c r="A215" s="35"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
@@ -6837,7 +6878,7 @@
       <c r="X215" s="4"/>
     </row>
     <row r="216">
-      <c r="A216" s="37"/>
+      <c r="A216" s="35"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
@@ -6863,7 +6904,7 @@
       <c r="X216" s="4"/>
     </row>
     <row r="217">
-      <c r="A217" s="37"/>
+      <c r="A217" s="35"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
@@ -6889,7 +6930,7 @@
       <c r="X217" s="4"/>
     </row>
     <row r="218">
-      <c r="A218" s="37"/>
+      <c r="A218" s="35"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
@@ -6915,7 +6956,7 @@
       <c r="X218" s="4"/>
     </row>
     <row r="219">
-      <c r="A219" s="37"/>
+      <c r="A219" s="35"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
@@ -6941,7 +6982,7 @@
       <c r="X219" s="4"/>
     </row>
     <row r="220">
-      <c r="A220" s="37"/>
+      <c r="A220" s="35"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
@@ -6967,7 +7008,7 @@
       <c r="X220" s="4"/>
     </row>
     <row r="221">
-      <c r="A221" s="37"/>
+      <c r="A221" s="35"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
@@ -6993,7 +7034,7 @@
       <c r="X221" s="4"/>
     </row>
     <row r="222">
-      <c r="A222" s="37"/>
+      <c r="A222" s="35"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
@@ -7019,7 +7060,7 @@
       <c r="X222" s="4"/>
     </row>
     <row r="223">
-      <c r="A223" s="37"/>
+      <c r="A223" s="35"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
@@ -7045,7 +7086,7 @@
       <c r="X223" s="4"/>
     </row>
     <row r="224">
-      <c r="A224" s="37"/>
+      <c r="A224" s="35"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
@@ -7071,7 +7112,7 @@
       <c r="X224" s="4"/>
     </row>
     <row r="225">
-      <c r="A225" s="37"/>
+      <c r="A225" s="35"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
@@ -7097,7 +7138,7 @@
       <c r="X225" s="4"/>
     </row>
     <row r="226">
-      <c r="A226" s="37"/>
+      <c r="A226" s="35"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
@@ -7123,7 +7164,7 @@
       <c r="X226" s="4"/>
     </row>
     <row r="227">
-      <c r="A227" s="37"/>
+      <c r="A227" s="35"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
@@ -7149,7 +7190,7 @@
       <c r="X227" s="4"/>
     </row>
     <row r="228">
-      <c r="A228" s="37"/>
+      <c r="A228" s="35"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
@@ -7175,7 +7216,7 @@
       <c r="X228" s="4"/>
     </row>
     <row r="229">
-      <c r="A229" s="37"/>
+      <c r="A229" s="35"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
@@ -7201,7 +7242,7 @@
       <c r="X229" s="4"/>
     </row>
     <row r="230">
-      <c r="A230" s="37"/>
+      <c r="A230" s="35"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
@@ -7227,7 +7268,7 @@
       <c r="X230" s="4"/>
     </row>
     <row r="231">
-      <c r="A231" s="37"/>
+      <c r="A231" s="35"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
@@ -7253,7 +7294,7 @@
       <c r="X231" s="4"/>
     </row>
     <row r="232">
-      <c r="A232" s="37"/>
+      <c r="A232" s="35"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
@@ -7279,7 +7320,7 @@
       <c r="X232" s="4"/>
     </row>
     <row r="233">
-      <c r="A233" s="37"/>
+      <c r="A233" s="35"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
@@ -7305,7 +7346,7 @@
       <c r="X233" s="4"/>
     </row>
     <row r="234">
-      <c r="A234" s="37"/>
+      <c r="A234" s="35"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
@@ -7331,7 +7372,7 @@
       <c r="X234" s="4"/>
     </row>
     <row r="235">
-      <c r="A235" s="37"/>
+      <c r="A235" s="35"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
@@ -7357,7 +7398,7 @@
       <c r="X235" s="4"/>
     </row>
     <row r="236">
-      <c r="A236" s="37"/>
+      <c r="A236" s="35"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
@@ -7383,7 +7424,7 @@
       <c r="X236" s="4"/>
     </row>
     <row r="237">
-      <c r="A237" s="37"/>
+      <c r="A237" s="35"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
@@ -7409,7 +7450,7 @@
       <c r="X237" s="4"/>
     </row>
     <row r="238">
-      <c r="A238" s="37"/>
+      <c r="A238" s="35"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
@@ -7435,7 +7476,7 @@
       <c r="X238" s="4"/>
     </row>
     <row r="239">
-      <c r="A239" s="37"/>
+      <c r="A239" s="35"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
@@ -7461,7 +7502,7 @@
       <c r="X239" s="4"/>
     </row>
     <row r="240">
-      <c r="A240" s="37"/>
+      <c r="A240" s="35"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
@@ -7487,7 +7528,7 @@
       <c r="X240" s="4"/>
     </row>
     <row r="241">
-      <c r="A241" s="37"/>
+      <c r="A241" s="35"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
@@ -7513,7 +7554,7 @@
       <c r="X241" s="4"/>
     </row>
     <row r="242">
-      <c r="A242" s="37"/>
+      <c r="A242" s="35"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
@@ -7539,7 +7580,7 @@
       <c r="X242" s="4"/>
     </row>
     <row r="243">
-      <c r="A243" s="37"/>
+      <c r="A243" s="35"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
@@ -7565,7 +7606,7 @@
       <c r="X243" s="4"/>
     </row>
     <row r="244">
-      <c r="A244" s="37"/>
+      <c r="A244" s="35"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
@@ -7591,7 +7632,7 @@
       <c r="X244" s="4"/>
     </row>
     <row r="245">
-      <c r="A245" s="37"/>
+      <c r="A245" s="35"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
@@ -7617,7 +7658,7 @@
       <c r="X245" s="4"/>
     </row>
     <row r="246">
-      <c r="A246" s="37"/>
+      <c r="A246" s="35"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
@@ -7643,7 +7684,7 @@
       <c r="X246" s="4"/>
     </row>
     <row r="247">
-      <c r="A247" s="37"/>
+      <c r="A247" s="35"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
@@ -7669,7 +7710,7 @@
       <c r="X247" s="4"/>
     </row>
     <row r="248">
-      <c r="A248" s="37"/>
+      <c r="A248" s="35"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
@@ -7695,7 +7736,7 @@
       <c r="X248" s="4"/>
     </row>
     <row r="249">
-      <c r="A249" s="37"/>
+      <c r="A249" s="35"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
@@ -7721,7 +7762,7 @@
       <c r="X249" s="4"/>
     </row>
     <row r="250">
-      <c r="A250" s="37"/>
+      <c r="A250" s="35"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
@@ -7747,7 +7788,7 @@
       <c r="X250" s="4"/>
     </row>
     <row r="251">
-      <c r="A251" s="37"/>
+      <c r="A251" s="35"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
@@ -7773,7 +7814,7 @@
       <c r="X251" s="4"/>
     </row>
     <row r="252">
-      <c r="A252" s="37"/>
+      <c r="A252" s="35"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
@@ -7799,7 +7840,7 @@
       <c r="X252" s="4"/>
     </row>
     <row r="253">
-      <c r="A253" s="37"/>
+      <c r="A253" s="35"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
@@ -7825,7 +7866,7 @@
       <c r="X253" s="4"/>
     </row>
     <row r="254">
-      <c r="A254" s="37"/>
+      <c r="A254" s="35"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
@@ -7851,7 +7892,7 @@
       <c r="X254" s="4"/>
     </row>
     <row r="255">
-      <c r="A255" s="37"/>
+      <c r="A255" s="35"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
@@ -7877,7 +7918,7 @@
       <c r="X255" s="4"/>
     </row>
     <row r="256">
-      <c r="A256" s="37"/>
+      <c r="A256" s="35"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
@@ -7903,7 +7944,7 @@
       <c r="X256" s="4"/>
     </row>
     <row r="257">
-      <c r="A257" s="37"/>
+      <c r="A257" s="35"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
@@ -7929,7 +7970,7 @@
       <c r="X257" s="4"/>
     </row>
     <row r="258">
-      <c r="A258" s="37"/>
+      <c r="A258" s="35"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
@@ -7955,7 +7996,7 @@
       <c r="X258" s="4"/>
     </row>
     <row r="259">
-      <c r="A259" s="37"/>
+      <c r="A259" s="35"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
@@ -7981,7 +8022,7 @@
       <c r="X259" s="4"/>
     </row>
     <row r="260">
-      <c r="A260" s="37"/>
+      <c r="A260" s="35"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
@@ -8007,7 +8048,7 @@
       <c r="X260" s="4"/>
     </row>
     <row r="261">
-      <c r="A261" s="37"/>
+      <c r="A261" s="35"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
@@ -8033,7 +8074,7 @@
       <c r="X261" s="4"/>
     </row>
     <row r="262">
-      <c r="A262" s="37"/>
+      <c r="A262" s="35"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
@@ -8059,7 +8100,7 @@
       <c r="X262" s="4"/>
     </row>
     <row r="263">
-      <c r="A263" s="37"/>
+      <c r="A263" s="35"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
@@ -8085,7 +8126,7 @@
       <c r="X263" s="4"/>
     </row>
     <row r="264">
-      <c r="A264" s="37"/>
+      <c r="A264" s="35"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
@@ -8111,7 +8152,7 @@
       <c r="X264" s="4"/>
     </row>
     <row r="265">
-      <c r="A265" s="37"/>
+      <c r="A265" s="35"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
@@ -8137,7 +8178,7 @@
       <c r="X265" s="4"/>
     </row>
     <row r="266">
-      <c r="A266" s="37"/>
+      <c r="A266" s="35"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
@@ -8163,7 +8204,7 @@
       <c r="X266" s="4"/>
     </row>
     <row r="267">
-      <c r="A267" s="37"/>
+      <c r="A267" s="35"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
@@ -8189,7 +8230,7 @@
       <c r="X267" s="4"/>
     </row>
     <row r="268">
-      <c r="A268" s="37"/>
+      <c r="A268" s="35"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
@@ -8215,7 +8256,7 @@
       <c r="X268" s="4"/>
     </row>
     <row r="269">
-      <c r="A269" s="37"/>
+      <c r="A269" s="35"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
@@ -8241,7 +8282,7 @@
       <c r="X269" s="4"/>
     </row>
     <row r="270">
-      <c r="A270" s="37"/>
+      <c r="A270" s="35"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
@@ -8267,7 +8308,7 @@
       <c r="X270" s="4"/>
     </row>
     <row r="271">
-      <c r="A271" s="37"/>
+      <c r="A271" s="35"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
@@ -8293,7 +8334,7 @@
       <c r="X271" s="4"/>
     </row>
     <row r="272">
-      <c r="A272" s="37"/>
+      <c r="A272" s="35"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
@@ -8319,7 +8360,7 @@
       <c r="X272" s="4"/>
     </row>
     <row r="273">
-      <c r="A273" s="37"/>
+      <c r="A273" s="35"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
@@ -8345,7 +8386,7 @@
       <c r="X273" s="4"/>
     </row>
     <row r="274">
-      <c r="A274" s="37"/>
+      <c r="A274" s="35"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
@@ -8371,7 +8412,7 @@
       <c r="X274" s="4"/>
     </row>
     <row r="275">
-      <c r="A275" s="37"/>
+      <c r="A275" s="35"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
@@ -8397,7 +8438,7 @@
       <c r="X275" s="4"/>
     </row>
     <row r="276">
-      <c r="A276" s="37"/>
+      <c r="A276" s="35"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
       <c r="D276" s="4"/>
@@ -8423,7 +8464,7 @@
       <c r="X276" s="4"/>
     </row>
     <row r="277">
-      <c r="A277" s="37"/>
+      <c r="A277" s="35"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
       <c r="D277" s="4"/>
@@ -8449,7 +8490,7 @@
       <c r="X277" s="4"/>
     </row>
     <row r="278">
-      <c r="A278" s="37"/>
+      <c r="A278" s="35"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
       <c r="D278" s="4"/>
@@ -8475,7 +8516,7 @@
       <c r="X278" s="4"/>
     </row>
     <row r="279">
-      <c r="A279" s="37"/>
+      <c r="A279" s="35"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
       <c r="D279" s="4"/>
@@ -8501,7 +8542,7 @@
       <c r="X279" s="4"/>
     </row>
     <row r="280">
-      <c r="A280" s="37"/>
+      <c r="A280" s="35"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
       <c r="D280" s="4"/>
@@ -8527,7 +8568,7 @@
       <c r="X280" s="4"/>
     </row>
     <row r="281">
-      <c r="A281" s="37"/>
+      <c r="A281" s="35"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
       <c r="D281" s="4"/>
@@ -8553,7 +8594,7 @@
       <c r="X281" s="4"/>
     </row>
     <row r="282">
-      <c r="A282" s="37"/>
+      <c r="A282" s="35"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
       <c r="D282" s="4"/>
@@ -8579,7 +8620,7 @@
       <c r="X282" s="4"/>
     </row>
     <row r="283">
-      <c r="A283" s="37"/>
+      <c r="A283" s="35"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
       <c r="D283" s="4"/>
@@ -8605,7 +8646,7 @@
       <c r="X283" s="4"/>
     </row>
     <row r="284">
-      <c r="A284" s="37"/>
+      <c r="A284" s="35"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
       <c r="D284" s="4"/>
@@ -8631,7 +8672,7 @@
       <c r="X284" s="4"/>
     </row>
     <row r="285">
-      <c r="A285" s="37"/>
+      <c r="A285" s="35"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
       <c r="D285" s="4"/>
@@ -8657,7 +8698,7 @@
       <c r="X285" s="4"/>
     </row>
     <row r="286">
-      <c r="A286" s="37"/>
+      <c r="A286" s="35"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
       <c r="D286" s="4"/>
@@ -8683,7 +8724,7 @@
       <c r="X286" s="4"/>
     </row>
     <row r="287">
-      <c r="A287" s="37"/>
+      <c r="A287" s="35"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
       <c r="D287" s="4"/>
@@ -8709,7 +8750,7 @@
       <c r="X287" s="4"/>
     </row>
     <row r="288">
-      <c r="A288" s="37"/>
+      <c r="A288" s="35"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
       <c r="D288" s="4"/>
@@ -8735,7 +8776,7 @@
       <c r="X288" s="4"/>
     </row>
     <row r="289">
-      <c r="A289" s="37"/>
+      <c r="A289" s="35"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
       <c r="D289" s="4"/>
@@ -8761,7 +8802,7 @@
       <c r="X289" s="4"/>
     </row>
     <row r="290">
-      <c r="A290" s="37"/>
+      <c r="A290" s="35"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
       <c r="D290" s="4"/>
@@ -8787,7 +8828,7 @@
       <c r="X290" s="4"/>
     </row>
     <row r="291">
-      <c r="A291" s="37"/>
+      <c r="A291" s="35"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
       <c r="D291" s="4"/>
@@ -8813,7 +8854,7 @@
       <c r="X291" s="4"/>
     </row>
     <row r="292">
-      <c r="A292" s="37"/>
+      <c r="A292" s="35"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
@@ -8839,7 +8880,7 @@
       <c r="X292" s="4"/>
     </row>
     <row r="293">
-      <c r="A293" s="37"/>
+      <c r="A293" s="35"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
       <c r="D293" s="4"/>
@@ -8865,7 +8906,7 @@
       <c r="X293" s="4"/>
     </row>
     <row r="294">
-      <c r="A294" s="37"/>
+      <c r="A294" s="35"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
       <c r="D294" s="4"/>
@@ -8891,7 +8932,7 @@
       <c r="X294" s="4"/>
     </row>
     <row r="295">
-      <c r="A295" s="37"/>
+      <c r="A295" s="35"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
       <c r="D295" s="4"/>
@@ -8917,7 +8958,7 @@
       <c r="X295" s="4"/>
     </row>
     <row r="296">
-      <c r="A296" s="37"/>
+      <c r="A296" s="35"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
       <c r="D296" s="4"/>
@@ -8943,7 +8984,7 @@
       <c r="X296" s="4"/>
     </row>
     <row r="297">
-      <c r="A297" s="37"/>
+      <c r="A297" s="35"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
       <c r="D297" s="4"/>
@@ -8969,7 +9010,7 @@
       <c r="X297" s="4"/>
     </row>
     <row r="298">
-      <c r="A298" s="37"/>
+      <c r="A298" s="35"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
       <c r="D298" s="4"/>
@@ -8995,7 +9036,7 @@
       <c r="X298" s="4"/>
     </row>
     <row r="299">
-      <c r="A299" s="37"/>
+      <c r="A299" s="35"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
@@ -9021,7 +9062,7 @@
       <c r="X299" s="4"/>
     </row>
     <row r="300">
-      <c r="A300" s="37"/>
+      <c r="A300" s="35"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
       <c r="D300" s="4"/>
@@ -9047,7 +9088,7 @@
       <c r="X300" s="4"/>
     </row>
     <row r="301">
-      <c r="A301" s="37"/>
+      <c r="A301" s="35"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
@@ -9073,7 +9114,7 @@
       <c r="X301" s="4"/>
     </row>
     <row r="302">
-      <c r="A302" s="37"/>
+      <c r="A302" s="35"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
@@ -9099,7 +9140,7 @@
       <c r="X302" s="4"/>
     </row>
     <row r="303">
-      <c r="A303" s="37"/>
+      <c r="A303" s="35"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
@@ -9125,7 +9166,7 @@
       <c r="X303" s="4"/>
     </row>
     <row r="304">
-      <c r="A304" s="37"/>
+      <c r="A304" s="35"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
@@ -9151,7 +9192,7 @@
       <c r="X304" s="4"/>
     </row>
     <row r="305">
-      <c r="A305" s="37"/>
+      <c r="A305" s="35"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
@@ -9177,7 +9218,7 @@
       <c r="X305" s="4"/>
     </row>
     <row r="306">
-      <c r="A306" s="37"/>
+      <c r="A306" s="35"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
@@ -9203,7 +9244,7 @@
       <c r="X306" s="4"/>
     </row>
     <row r="307">
-      <c r="A307" s="37"/>
+      <c r="A307" s="35"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
       <c r="D307" s="4"/>
@@ -9229,7 +9270,7 @@
       <c r="X307" s="4"/>
     </row>
     <row r="308">
-      <c r="A308" s="37"/>
+      <c r="A308" s="35"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
       <c r="D308" s="4"/>
@@ -9255,7 +9296,7 @@
       <c r="X308" s="4"/>
     </row>
     <row r="309">
-      <c r="A309" s="37"/>
+      <c r="A309" s="35"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
       <c r="D309" s="4"/>
@@ -9281,7 +9322,7 @@
       <c r="X309" s="4"/>
     </row>
     <row r="310">
-      <c r="A310" s="37"/>
+      <c r="A310" s="35"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
       <c r="D310" s="4"/>
@@ -9307,7 +9348,7 @@
       <c r="X310" s="4"/>
     </row>
     <row r="311">
-      <c r="A311" s="37"/>
+      <c r="A311" s="35"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
       <c r="D311" s="4"/>
@@ -9333,7 +9374,7 @@
       <c r="X311" s="4"/>
     </row>
     <row r="312">
-      <c r="A312" s="37"/>
+      <c r="A312" s="35"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
       <c r="D312" s="4"/>
@@ -9359,7 +9400,7 @@
       <c r="X312" s="4"/>
     </row>
     <row r="313">
-      <c r="A313" s="37"/>
+      <c r="A313" s="35"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
       <c r="D313" s="4"/>
@@ -9385,7 +9426,7 @@
       <c r="X313" s="4"/>
     </row>
     <row r="314">
-      <c r="A314" s="37"/>
+      <c r="A314" s="35"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
       <c r="D314" s="4"/>
@@ -9411,7 +9452,7 @@
       <c r="X314" s="4"/>
     </row>
     <row r="315">
-      <c r="A315" s="37"/>
+      <c r="A315" s="35"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
       <c r="D315" s="4"/>
@@ -9437,7 +9478,7 @@
       <c r="X315" s="4"/>
     </row>
     <row r="316">
-      <c r="A316" s="37"/>
+      <c r="A316" s="35"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
       <c r="D316" s="4"/>
@@ -9463,7 +9504,7 @@
       <c r="X316" s="4"/>
     </row>
     <row r="317">
-      <c r="A317" s="37"/>
+      <c r="A317" s="35"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
@@ -9489,7 +9530,7 @@
       <c r="X317" s="4"/>
     </row>
     <row r="318">
-      <c r="A318" s="37"/>
+      <c r="A318" s="35"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
@@ -9515,7 +9556,7 @@
       <c r="X318" s="4"/>
     </row>
     <row r="319">
-      <c r="A319" s="37"/>
+      <c r="A319" s="35"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
@@ -9541,7 +9582,7 @@
       <c r="X319" s="4"/>
     </row>
     <row r="320">
-      <c r="A320" s="37"/>
+      <c r="A320" s="35"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
@@ -9567,7 +9608,7 @@
       <c r="X320" s="4"/>
     </row>
     <row r="321">
-      <c r="A321" s="37"/>
+      <c r="A321" s="35"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
       <c r="D321" s="4"/>
@@ -9593,7 +9634,7 @@
       <c r="X321" s="4"/>
     </row>
     <row r="322">
-      <c r="A322" s="37"/>
+      <c r="A322" s="35"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
       <c r="D322" s="4"/>
@@ -9619,7 +9660,7 @@
       <c r="X322" s="4"/>
     </row>
     <row r="323">
-      <c r="A323" s="37"/>
+      <c r="A323" s="35"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
       <c r="D323" s="4"/>
@@ -9645,7 +9686,7 @@
       <c r="X323" s="4"/>
     </row>
     <row r="324">
-      <c r="A324" s="37"/>
+      <c r="A324" s="35"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
       <c r="D324" s="4"/>
@@ -9671,7 +9712,7 @@
       <c r="X324" s="4"/>
     </row>
     <row r="325">
-      <c r="A325" s="37"/>
+      <c r="A325" s="35"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
       <c r="D325" s="4"/>
@@ -9697,7 +9738,7 @@
       <c r="X325" s="4"/>
     </row>
     <row r="326">
-      <c r="A326" s="37"/>
+      <c r="A326" s="35"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
       <c r="D326" s="4"/>
@@ -9723,7 +9764,7 @@
       <c r="X326" s="4"/>
     </row>
     <row r="327">
-      <c r="A327" s="37"/>
+      <c r="A327" s="35"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
       <c r="D327" s="4"/>
@@ -9749,7 +9790,7 @@
       <c r="X327" s="4"/>
     </row>
     <row r="328">
-      <c r="A328" s="37"/>
+      <c r="A328" s="35"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
       <c r="D328" s="4"/>
@@ -9775,7 +9816,7 @@
       <c r="X328" s="4"/>
     </row>
     <row r="329">
-      <c r="A329" s="37"/>
+      <c r="A329" s="35"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
       <c r="D329" s="4"/>
@@ -9801,7 +9842,7 @@
       <c r="X329" s="4"/>
     </row>
     <row r="330">
-      <c r="A330" s="37"/>
+      <c r="A330" s="35"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
       <c r="D330" s="4"/>
@@ -9827,7 +9868,7 @@
       <c r="X330" s="4"/>
     </row>
     <row r="331">
-      <c r="A331" s="37"/>
+      <c r="A331" s="35"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
@@ -9853,7 +9894,7 @@
       <c r="X331" s="4"/>
     </row>
     <row r="332">
-      <c r="A332" s="37"/>
+      <c r="A332" s="35"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
       <c r="D332" s="4"/>
@@ -9879,7 +9920,7 @@
       <c r="X332" s="4"/>
     </row>
     <row r="333">
-      <c r="A333" s="37"/>
+      <c r="A333" s="35"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
       <c r="D333" s="4"/>
@@ -9905,7 +9946,7 @@
       <c r="X333" s="4"/>
     </row>
     <row r="334">
-      <c r="A334" s="37"/>
+      <c r="A334" s="35"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
       <c r="D334" s="4"/>
@@ -9931,7 +9972,7 @@
       <c r="X334" s="4"/>
     </row>
     <row r="335">
-      <c r="A335" s="37"/>
+      <c r="A335" s="35"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
       <c r="D335" s="4"/>
@@ -9957,7 +9998,7 @@
       <c r="X335" s="4"/>
     </row>
     <row r="336">
-      <c r="A336" s="37"/>
+      <c r="A336" s="35"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
       <c r="D336" s="4"/>
@@ -9983,7 +10024,7 @@
       <c r="X336" s="4"/>
     </row>
     <row r="337">
-      <c r="A337" s="37"/>
+      <c r="A337" s="35"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
       <c r="D337" s="4"/>
@@ -10009,7 +10050,7 @@
       <c r="X337" s="4"/>
     </row>
     <row r="338">
-      <c r="A338" s="37"/>
+      <c r="A338" s="35"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
@@ -10035,7 +10076,7 @@
       <c r="X338" s="4"/>
     </row>
     <row r="339">
-      <c r="A339" s="37"/>
+      <c r="A339" s="35"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
       <c r="D339" s="4"/>
@@ -10061,7 +10102,7 @@
       <c r="X339" s="4"/>
     </row>
     <row r="340">
-      <c r="A340" s="37"/>
+      <c r="A340" s="35"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
       <c r="D340" s="4"/>
@@ -10087,7 +10128,7 @@
       <c r="X340" s="4"/>
     </row>
     <row r="341">
-      <c r="A341" s="37"/>
+      <c r="A341" s="35"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
       <c r="D341" s="4"/>
@@ -10113,7 +10154,7 @@
       <c r="X341" s="4"/>
     </row>
     <row r="342">
-      <c r="A342" s="37"/>
+      <c r="A342" s="35"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
       <c r="D342" s="4"/>
@@ -10139,7 +10180,7 @@
       <c r="X342" s="4"/>
     </row>
     <row r="343">
-      <c r="A343" s="37"/>
+      <c r="A343" s="35"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
       <c r="D343" s="4"/>
@@ -10165,7 +10206,7 @@
       <c r="X343" s="4"/>
     </row>
     <row r="344">
-      <c r="A344" s="37"/>
+      <c r="A344" s="35"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
       <c r="D344" s="4"/>
@@ -10191,7 +10232,7 @@
       <c r="X344" s="4"/>
     </row>
     <row r="345">
-      <c r="A345" s="37"/>
+      <c r="A345" s="35"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
       <c r="D345" s="4"/>
@@ -10217,7 +10258,7 @@
       <c r="X345" s="4"/>
     </row>
     <row r="346">
-      <c r="A346" s="37"/>
+      <c r="A346" s="35"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
       <c r="D346" s="4"/>
@@ -10243,7 +10284,7 @@
       <c r="X346" s="4"/>
     </row>
     <row r="347">
-      <c r="A347" s="37"/>
+      <c r="A347" s="35"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
       <c r="D347" s="4"/>
@@ -10269,7 +10310,7 @@
       <c r="X347" s="4"/>
     </row>
     <row r="348">
-      <c r="A348" s="37"/>
+      <c r="A348" s="35"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
       <c r="D348" s="4"/>
@@ -10295,7 +10336,7 @@
       <c r="X348" s="4"/>
     </row>
     <row r="349">
-      <c r="A349" s="37"/>
+      <c r="A349" s="35"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
       <c r="D349" s="4"/>
@@ -10321,7 +10362,7 @@
       <c r="X349" s="4"/>
     </row>
     <row r="350">
-      <c r="A350" s="37"/>
+      <c r="A350" s="35"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
       <c r="D350" s="4"/>
@@ -10347,7 +10388,7 @@
       <c r="X350" s="4"/>
     </row>
     <row r="351">
-      <c r="A351" s="37"/>
+      <c r="A351" s="35"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
       <c r="D351" s="4"/>
@@ -10373,7 +10414,7 @@
       <c r="X351" s="4"/>
     </row>
     <row r="352">
-      <c r="A352" s="37"/>
+      <c r="A352" s="35"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
       <c r="D352" s="4"/>
@@ -10399,7 +10440,7 @@
       <c r="X352" s="4"/>
     </row>
     <row r="353">
-      <c r="A353" s="37"/>
+      <c r="A353" s="35"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
       <c r="D353" s="4"/>
@@ -10425,7 +10466,7 @@
       <c r="X353" s="4"/>
     </row>
     <row r="354">
-      <c r="A354" s="37"/>
+      <c r="A354" s="35"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
       <c r="D354" s="4"/>
@@ -10451,7 +10492,7 @@
       <c r="X354" s="4"/>
     </row>
     <row r="355">
-      <c r="A355" s="37"/>
+      <c r="A355" s="35"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
       <c r="D355" s="4"/>
@@ -10477,7 +10518,7 @@
       <c r="X355" s="4"/>
     </row>
     <row r="356">
-      <c r="A356" s="37"/>
+      <c r="A356" s="35"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
       <c r="D356" s="4"/>
@@ -10503,7 +10544,7 @@
       <c r="X356" s="4"/>
     </row>
     <row r="357">
-      <c r="A357" s="37"/>
+      <c r="A357" s="35"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
       <c r="D357" s="4"/>
@@ -10529,7 +10570,7 @@
       <c r="X357" s="4"/>
     </row>
     <row r="358">
-      <c r="A358" s="37"/>
+      <c r="A358" s="35"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
       <c r="D358" s="4"/>
@@ -10555,7 +10596,7 @@
       <c r="X358" s="4"/>
     </row>
     <row r="359">
-      <c r="A359" s="37"/>
+      <c r="A359" s="35"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
       <c r="D359" s="4"/>
@@ -10581,7 +10622,7 @@
       <c r="X359" s="4"/>
     </row>
     <row r="360">
-      <c r="A360" s="37"/>
+      <c r="A360" s="35"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
       <c r="D360" s="4"/>
@@ -10607,7 +10648,7 @@
       <c r="X360" s="4"/>
     </row>
     <row r="361">
-      <c r="A361" s="37"/>
+      <c r="A361" s="35"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
       <c r="D361" s="4"/>
@@ -10633,7 +10674,7 @@
       <c r="X361" s="4"/>
     </row>
     <row r="362">
-      <c r="A362" s="37"/>
+      <c r="A362" s="35"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
       <c r="D362" s="4"/>
@@ -10659,7 +10700,7 @@
       <c r="X362" s="4"/>
     </row>
     <row r="363">
-      <c r="A363" s="37"/>
+      <c r="A363" s="35"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
       <c r="D363" s="4"/>
@@ -10685,7 +10726,7 @@
       <c r="X363" s="4"/>
     </row>
     <row r="364">
-      <c r="A364" s="37"/>
+      <c r="A364" s="35"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
       <c r="D364" s="4"/>
@@ -10711,7 +10752,7 @@
       <c r="X364" s="4"/>
     </row>
     <row r="365">
-      <c r="A365" s="37"/>
+      <c r="A365" s="35"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
       <c r="D365" s="4"/>
@@ -10737,7 +10778,7 @@
       <c r="X365" s="4"/>
     </row>
     <row r="366">
-      <c r="A366" s="37"/>
+      <c r="A366" s="35"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
       <c r="D366" s="4"/>
@@ -10763,7 +10804,7 @@
       <c r="X366" s="4"/>
     </row>
     <row r="367">
-      <c r="A367" s="37"/>
+      <c r="A367" s="35"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
       <c r="D367" s="4"/>
@@ -10789,7 +10830,7 @@
       <c r="X367" s="4"/>
     </row>
     <row r="368">
-      <c r="A368" s="37"/>
+      <c r="A368" s="35"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
       <c r="D368" s="4"/>
@@ -10815,7 +10856,7 @@
       <c r="X368" s="4"/>
     </row>
     <row r="369">
-      <c r="A369" s="37"/>
+      <c r="A369" s="35"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
       <c r="D369" s="4"/>
@@ -10841,7 +10882,7 @@
       <c r="X369" s="4"/>
     </row>
     <row r="370">
-      <c r="A370" s="37"/>
+      <c r="A370" s="35"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
       <c r="D370" s="4"/>
@@ -10867,7 +10908,7 @@
       <c r="X370" s="4"/>
     </row>
     <row r="371">
-      <c r="A371" s="37"/>
+      <c r="A371" s="35"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
       <c r="D371" s="4"/>
@@ -10893,7 +10934,7 @@
       <c r="X371" s="4"/>
     </row>
     <row r="372">
-      <c r="A372" s="37"/>
+      <c r="A372" s="35"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
       <c r="D372" s="4"/>
@@ -10919,7 +10960,7 @@
       <c r="X372" s="4"/>
     </row>
     <row r="373">
-      <c r="A373" s="37"/>
+      <c r="A373" s="35"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
       <c r="D373" s="4"/>
@@ -10945,7 +10986,7 @@
       <c r="X373" s="4"/>
     </row>
     <row r="374">
-      <c r="A374" s="37"/>
+      <c r="A374" s="35"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
       <c r="D374" s="4"/>
@@ -10971,7 +11012,7 @@
       <c r="X374" s="4"/>
     </row>
     <row r="375">
-      <c r="A375" s="37"/>
+      <c r="A375" s="35"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
       <c r="D375" s="4"/>
@@ -10997,7 +11038,7 @@
       <c r="X375" s="4"/>
     </row>
     <row r="376">
-      <c r="A376" s="37"/>
+      <c r="A376" s="35"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
       <c r="D376" s="4"/>
@@ -11023,7 +11064,7 @@
       <c r="X376" s="4"/>
     </row>
     <row r="377">
-      <c r="A377" s="37"/>
+      <c r="A377" s="35"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
       <c r="D377" s="4"/>
@@ -11049,7 +11090,7 @@
       <c r="X377" s="4"/>
     </row>
     <row r="378">
-      <c r="A378" s="37"/>
+      <c r="A378" s="35"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
       <c r="D378" s="4"/>
@@ -11075,7 +11116,7 @@
       <c r="X378" s="4"/>
     </row>
     <row r="379">
-      <c r="A379" s="37"/>
+      <c r="A379" s="35"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
       <c r="D379" s="4"/>
@@ -11101,7 +11142,7 @@
       <c r="X379" s="4"/>
     </row>
     <row r="380">
-      <c r="A380" s="37"/>
+      <c r="A380" s="35"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
       <c r="D380" s="4"/>
@@ -11127,7 +11168,7 @@
       <c r="X380" s="4"/>
     </row>
     <row r="381">
-      <c r="A381" s="37"/>
+      <c r="A381" s="35"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
       <c r="D381" s="4"/>
@@ -11153,7 +11194,7 @@
       <c r="X381" s="4"/>
     </row>
     <row r="382">
-      <c r="A382" s="37"/>
+      <c r="A382" s="35"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
       <c r="D382" s="4"/>
@@ -11179,7 +11220,7 @@
       <c r="X382" s="4"/>
     </row>
     <row r="383">
-      <c r="A383" s="37"/>
+      <c r="A383" s="35"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
       <c r="D383" s="4"/>
@@ -11205,7 +11246,7 @@
       <c r="X383" s="4"/>
     </row>
     <row r="384">
-      <c r="A384" s="37"/>
+      <c r="A384" s="35"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
       <c r="D384" s="4"/>
@@ -11231,7 +11272,7 @@
       <c r="X384" s="4"/>
     </row>
     <row r="385">
-      <c r="A385" s="37"/>
+      <c r="A385" s="35"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
       <c r="D385" s="4"/>
@@ -11257,7 +11298,7 @@
       <c r="X385" s="4"/>
     </row>
     <row r="386">
-      <c r="A386" s="37"/>
+      <c r="A386" s="35"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
       <c r="D386" s="4"/>
@@ -11283,7 +11324,7 @@
       <c r="X386" s="4"/>
     </row>
     <row r="387">
-      <c r="A387" s="37"/>
+      <c r="A387" s="35"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
       <c r="D387" s="4"/>
@@ -11309,7 +11350,7 @@
       <c r="X387" s="4"/>
     </row>
     <row r="388">
-      <c r="A388" s="37"/>
+      <c r="A388" s="35"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
       <c r="D388" s="4"/>
@@ -11335,7 +11376,7 @@
       <c r="X388" s="4"/>
     </row>
     <row r="389">
-      <c r="A389" s="37"/>
+      <c r="A389" s="35"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
       <c r="D389" s="4"/>
@@ -11361,7 +11402,7 @@
       <c r="X389" s="4"/>
     </row>
     <row r="390">
-      <c r="A390" s="37"/>
+      <c r="A390" s="35"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
       <c r="D390" s="4"/>
@@ -11387,7 +11428,7 @@
       <c r="X390" s="4"/>
     </row>
     <row r="391">
-      <c r="A391" s="37"/>
+      <c r="A391" s="35"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
       <c r="D391" s="4"/>
@@ -11413,7 +11454,7 @@
       <c r="X391" s="4"/>
     </row>
     <row r="392">
-      <c r="A392" s="37"/>
+      <c r="A392" s="35"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
       <c r="D392" s="4"/>
@@ -11439,7 +11480,7 @@
       <c r="X392" s="4"/>
     </row>
     <row r="393">
-      <c r="A393" s="37"/>
+      <c r="A393" s="35"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
       <c r="D393" s="4"/>
@@ -11465,7 +11506,7 @@
       <c r="X393" s="4"/>
     </row>
     <row r="394">
-      <c r="A394" s="37"/>
+      <c r="A394" s="35"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
       <c r="D394" s="4"/>
@@ -11491,7 +11532,7 @@
       <c r="X394" s="4"/>
     </row>
     <row r="395">
-      <c r="A395" s="37"/>
+      <c r="A395" s="35"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
       <c r="D395" s="4"/>
@@ -11517,7 +11558,7 @@
       <c r="X395" s="4"/>
     </row>
     <row r="396">
-      <c r="A396" s="37"/>
+      <c r="A396" s="35"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
       <c r="D396" s="4"/>
@@ -11543,7 +11584,7 @@
       <c r="X396" s="4"/>
     </row>
     <row r="397">
-      <c r="A397" s="37"/>
+      <c r="A397" s="35"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
       <c r="D397" s="4"/>
@@ -11569,7 +11610,7 @@
       <c r="X397" s="4"/>
     </row>
     <row r="398">
-      <c r="A398" s="37"/>
+      <c r="A398" s="35"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
       <c r="D398" s="4"/>
@@ -11595,7 +11636,7 @@
       <c r="X398" s="4"/>
     </row>
     <row r="399">
-      <c r="A399" s="37"/>
+      <c r="A399" s="35"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
       <c r="D399" s="4"/>
@@ -11621,7 +11662,7 @@
       <c r="X399" s="4"/>
     </row>
     <row r="400">
-      <c r="A400" s="37"/>
+      <c r="A400" s="35"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
       <c r="D400" s="4"/>
@@ -11647,7 +11688,7 @@
       <c r="X400" s="4"/>
     </row>
     <row r="401">
-      <c r="A401" s="37"/>
+      <c r="A401" s="35"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
       <c r="D401" s="4"/>
@@ -11673,7 +11714,7 @@
       <c r="X401" s="4"/>
     </row>
     <row r="402">
-      <c r="A402" s="37"/>
+      <c r="A402" s="35"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
       <c r="D402" s="4"/>
@@ -11699,7 +11740,7 @@
       <c r="X402" s="4"/>
     </row>
     <row r="403">
-      <c r="A403" s="37"/>
+      <c r="A403" s="35"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
       <c r="D403" s="4"/>
@@ -11725,7 +11766,7 @@
       <c r="X403" s="4"/>
     </row>
     <row r="404">
-      <c r="A404" s="37"/>
+      <c r="A404" s="35"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
       <c r="D404" s="4"/>
@@ -11751,7 +11792,7 @@
       <c r="X404" s="4"/>
     </row>
     <row r="405">
-      <c r="A405" s="37"/>
+      <c r="A405" s="35"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
       <c r="D405" s="4"/>
@@ -11777,7 +11818,7 @@
       <c r="X405" s="4"/>
     </row>
     <row r="406">
-      <c r="A406" s="37"/>
+      <c r="A406" s="35"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
       <c r="D406" s="4"/>
@@ -11803,7 +11844,7 @@
       <c r="X406" s="4"/>
     </row>
     <row r="407">
-      <c r="A407" s="37"/>
+      <c r="A407" s="35"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
       <c r="D407" s="4"/>
@@ -11829,7 +11870,7 @@
       <c r="X407" s="4"/>
     </row>
     <row r="408">
-      <c r="A408" s="37"/>
+      <c r="A408" s="35"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
       <c r="D408" s="4"/>
@@ -11855,7 +11896,7 @@
       <c r="X408" s="4"/>
     </row>
     <row r="409">
-      <c r="A409" s="37"/>
+      <c r="A409" s="35"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
       <c r="D409" s="4"/>
@@ -11881,7 +11922,7 @@
       <c r="X409" s="4"/>
     </row>
     <row r="410">
-      <c r="A410" s="37"/>
+      <c r="A410" s="35"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
       <c r="D410" s="4"/>
@@ -11907,7 +11948,7 @@
       <c r="X410" s="4"/>
     </row>
     <row r="411">
-      <c r="A411" s="37"/>
+      <c r="A411" s="35"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
       <c r="D411" s="4"/>
@@ -11933,7 +11974,7 @@
       <c r="X411" s="4"/>
     </row>
     <row r="412">
-      <c r="A412" s="37"/>
+      <c r="A412" s="35"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
       <c r="D412" s="4"/>
@@ -11959,7 +12000,7 @@
       <c r="X412" s="4"/>
     </row>
     <row r="413">
-      <c r="A413" s="37"/>
+      <c r="A413" s="35"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
       <c r="D413" s="4"/>
@@ -11985,7 +12026,7 @@
       <c r="X413" s="4"/>
     </row>
     <row r="414">
-      <c r="A414" s="37"/>
+      <c r="A414" s="35"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
       <c r="D414" s="4"/>
@@ -12011,7 +12052,7 @@
       <c r="X414" s="4"/>
     </row>
     <row r="415">
-      <c r="A415" s="37"/>
+      <c r="A415" s="35"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
       <c r="D415" s="4"/>
@@ -12037,7 +12078,7 @@
       <c r="X415" s="4"/>
     </row>
     <row r="416">
-      <c r="A416" s="37"/>
+      <c r="A416" s="35"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
       <c r="D416" s="4"/>
@@ -12063,7 +12104,7 @@
       <c r="X416" s="4"/>
     </row>
     <row r="417">
-      <c r="A417" s="37"/>
+      <c r="A417" s="35"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
       <c r="D417" s="4"/>
@@ -12089,7 +12130,7 @@
       <c r="X417" s="4"/>
     </row>
     <row r="418">
-      <c r="A418" s="37"/>
+      <c r="A418" s="35"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
       <c r="D418" s="4"/>
@@ -12115,7 +12156,7 @@
       <c r="X418" s="4"/>
     </row>
     <row r="419">
-      <c r="A419" s="37"/>
+      <c r="A419" s="35"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
       <c r="D419" s="4"/>
@@ -12141,7 +12182,7 @@
       <c r="X419" s="4"/>
     </row>
     <row r="420">
-      <c r="A420" s="37"/>
+      <c r="A420" s="35"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
       <c r="D420" s="4"/>
@@ -12167,7 +12208,7 @@
       <c r="X420" s="4"/>
     </row>
     <row r="421">
-      <c r="A421" s="37"/>
+      <c r="A421" s="35"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
       <c r="D421" s="4"/>
@@ -12193,7 +12234,7 @@
       <c r="X421" s="4"/>
     </row>
     <row r="422">
-      <c r="A422" s="37"/>
+      <c r="A422" s="35"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
       <c r="D422" s="4"/>
@@ -12219,7 +12260,7 @@
       <c r="X422" s="4"/>
     </row>
     <row r="423">
-      <c r="A423" s="37"/>
+      <c r="A423" s="35"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
       <c r="D423" s="4"/>
@@ -12245,7 +12286,7 @@
       <c r="X423" s="4"/>
     </row>
     <row r="424">
-      <c r="A424" s="37"/>
+      <c r="A424" s="35"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
       <c r="D424" s="4"/>
@@ -12271,7 +12312,7 @@
       <c r="X424" s="4"/>
     </row>
     <row r="425">
-      <c r="A425" s="37"/>
+      <c r="A425" s="35"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
       <c r="D425" s="4"/>
@@ -12297,7 +12338,7 @@
       <c r="X425" s="4"/>
     </row>
     <row r="426">
-      <c r="A426" s="37"/>
+      <c r="A426" s="35"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
       <c r="D426" s="4"/>
@@ -12323,7 +12364,7 @@
       <c r="X426" s="4"/>
     </row>
     <row r="427">
-      <c r="A427" s="37"/>
+      <c r="A427" s="35"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
       <c r="D427" s="4"/>
@@ -12349,7 +12390,7 @@
       <c r="X427" s="4"/>
     </row>
     <row r="428">
-      <c r="A428" s="37"/>
+      <c r="A428" s="35"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
       <c r="D428" s="4"/>
@@ -12375,7 +12416,7 @@
       <c r="X428" s="4"/>
     </row>
     <row r="429">
-      <c r="A429" s="37"/>
+      <c r="A429" s="35"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
       <c r="D429" s="4"/>
@@ -12401,7 +12442,7 @@
       <c r="X429" s="4"/>
     </row>
     <row r="430">
-      <c r="A430" s="37"/>
+      <c r="A430" s="35"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
       <c r="D430" s="4"/>
@@ -12427,7 +12468,7 @@
       <c r="X430" s="4"/>
     </row>
     <row r="431">
-      <c r="A431" s="37"/>
+      <c r="A431" s="35"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
       <c r="D431" s="4"/>
@@ -12453,7 +12494,7 @@
       <c r="X431" s="4"/>
     </row>
     <row r="432">
-      <c r="A432" s="37"/>
+      <c r="A432" s="35"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
       <c r="D432" s="4"/>
@@ -12479,7 +12520,7 @@
       <c r="X432" s="4"/>
     </row>
     <row r="433">
-      <c r="A433" s="37"/>
+      <c r="A433" s="35"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
       <c r="D433" s="4"/>
@@ -12505,7 +12546,7 @@
       <c r="X433" s="4"/>
     </row>
     <row r="434">
-      <c r="A434" s="37"/>
+      <c r="A434" s="35"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
       <c r="D434" s="4"/>
@@ -12531,7 +12572,7 @@
       <c r="X434" s="4"/>
     </row>
     <row r="435">
-      <c r="A435" s="37"/>
+      <c r="A435" s="35"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
       <c r="D435" s="4"/>
@@ -12557,7 +12598,7 @@
       <c r="X435" s="4"/>
     </row>
     <row r="436">
-      <c r="A436" s="37"/>
+      <c r="A436" s="35"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
       <c r="D436" s="4"/>
@@ -12583,7 +12624,7 @@
       <c r="X436" s="4"/>
     </row>
     <row r="437">
-      <c r="A437" s="37"/>
+      <c r="A437" s="35"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
       <c r="D437" s="4"/>
@@ -12609,7 +12650,7 @@
       <c r="X437" s="4"/>
     </row>
     <row r="438">
-      <c r="A438" s="37"/>
+      <c r="A438" s="35"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
       <c r="D438" s="4"/>
@@ -12635,7 +12676,7 @@
       <c r="X438" s="4"/>
     </row>
     <row r="439">
-      <c r="A439" s="37"/>
+      <c r="A439" s="35"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
       <c r="D439" s="4"/>
@@ -12661,7 +12702,7 @@
       <c r="X439" s="4"/>
     </row>
     <row r="440">
-      <c r="A440" s="37"/>
+      <c r="A440" s="35"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
       <c r="D440" s="4"/>
@@ -12687,7 +12728,7 @@
       <c r="X440" s="4"/>
     </row>
     <row r="441">
-      <c r="A441" s="37"/>
+      <c r="A441" s="35"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
       <c r="D441" s="4"/>
@@ -12713,7 +12754,7 @@
       <c r="X441" s="4"/>
     </row>
     <row r="442">
-      <c r="A442" s="37"/>
+      <c r="A442" s="35"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
       <c r="D442" s="4"/>
@@ -12739,7 +12780,7 @@
       <c r="X442" s="4"/>
     </row>
     <row r="443">
-      <c r="A443" s="37"/>
+      <c r="A443" s="35"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
       <c r="D443" s="4"/>
@@ -12765,7 +12806,7 @@
       <c r="X443" s="4"/>
     </row>
     <row r="444">
-      <c r="A444" s="37"/>
+      <c r="A444" s="35"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
       <c r="D444" s="4"/>
@@ -12791,7 +12832,7 @@
       <c r="X444" s="4"/>
     </row>
     <row r="445">
-      <c r="A445" s="37"/>
+      <c r="A445" s="35"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
       <c r="D445" s="4"/>
@@ -12817,7 +12858,7 @@
       <c r="X445" s="4"/>
     </row>
     <row r="446">
-      <c r="A446" s="37"/>
+      <c r="A446" s="35"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
       <c r="D446" s="4"/>
@@ -12843,7 +12884,7 @@
       <c r="X446" s="4"/>
     </row>
     <row r="447">
-      <c r="A447" s="37"/>
+      <c r="A447" s="35"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
       <c r="D447" s="4"/>
@@ -12869,7 +12910,7 @@
       <c r="X447" s="4"/>
     </row>
     <row r="448">
-      <c r="A448" s="37"/>
+      <c r="A448" s="35"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
       <c r="D448" s="4"/>
@@ -12895,7 +12936,7 @@
       <c r="X448" s="4"/>
     </row>
     <row r="449">
-      <c r="A449" s="37"/>
+      <c r="A449" s="35"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
       <c r="D449" s="4"/>
@@ -12921,7 +12962,7 @@
       <c r="X449" s="4"/>
     </row>
     <row r="450">
-      <c r="A450" s="37"/>
+      <c r="A450" s="35"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
       <c r="D450" s="4"/>
@@ -12947,7 +12988,7 @@
       <c r="X450" s="4"/>
     </row>
     <row r="451">
-      <c r="A451" s="37"/>
+      <c r="A451" s="35"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
       <c r="D451" s="4"/>
@@ -12973,7 +13014,7 @@
       <c r="X451" s="4"/>
     </row>
     <row r="452">
-      <c r="A452" s="37"/>
+      <c r="A452" s="35"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
       <c r="D452" s="4"/>
@@ -12999,7 +13040,7 @@
       <c r="X452" s="4"/>
     </row>
     <row r="453">
-      <c r="A453" s="37"/>
+      <c r="A453" s="35"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
       <c r="D453" s="4"/>
@@ -13025,7 +13066,7 @@
       <c r="X453" s="4"/>
     </row>
     <row r="454">
-      <c r="A454" s="37"/>
+      <c r="A454" s="35"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
       <c r="D454" s="4"/>
@@ -13051,7 +13092,7 @@
       <c r="X454" s="4"/>
     </row>
     <row r="455">
-      <c r="A455" s="37"/>
+      <c r="A455" s="35"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
       <c r="D455" s="4"/>
@@ -13077,7 +13118,7 @@
       <c r="X455" s="4"/>
     </row>
     <row r="456">
-      <c r="A456" s="37"/>
+      <c r="A456" s="35"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
       <c r="D456" s="4"/>
@@ -13103,7 +13144,7 @@
       <c r="X456" s="4"/>
     </row>
     <row r="457">
-      <c r="A457" s="37"/>
+      <c r="A457" s="35"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
       <c r="D457" s="4"/>
@@ -13129,7 +13170,7 @@
       <c r="X457" s="4"/>
     </row>
     <row r="458">
-      <c r="A458" s="37"/>
+      <c r="A458" s="35"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
       <c r="D458" s="4"/>
@@ -13155,7 +13196,7 @@
       <c r="X458" s="4"/>
     </row>
     <row r="459">
-      <c r="A459" s="37"/>
+      <c r="A459" s="35"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
       <c r="D459" s="4"/>
@@ -13181,7 +13222,7 @@
       <c r="X459" s="4"/>
     </row>
     <row r="460">
-      <c r="A460" s="37"/>
+      <c r="A460" s="35"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
       <c r="D460" s="4"/>
@@ -13207,7 +13248,7 @@
       <c r="X460" s="4"/>
     </row>
     <row r="461">
-      <c r="A461" s="37"/>
+      <c r="A461" s="35"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
       <c r="D461" s="4"/>
@@ -13233,7 +13274,7 @@
       <c r="X461" s="4"/>
     </row>
     <row r="462">
-      <c r="A462" s="37"/>
+      <c r="A462" s="35"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
       <c r="D462" s="4"/>
@@ -13259,7 +13300,7 @@
       <c r="X462" s="4"/>
     </row>
     <row r="463">
-      <c r="A463" s="37"/>
+      <c r="A463" s="35"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
       <c r="D463" s="4"/>
@@ -13285,7 +13326,7 @@
       <c r="X463" s="4"/>
     </row>
     <row r="464">
-      <c r="A464" s="37"/>
+      <c r="A464" s="35"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
       <c r="D464" s="4"/>
@@ -13311,7 +13352,7 @@
       <c r="X464" s="4"/>
     </row>
     <row r="465">
-      <c r="A465" s="37"/>
+      <c r="A465" s="35"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
       <c r="D465" s="4"/>
@@ -13337,7 +13378,7 @@
       <c r="X465" s="4"/>
     </row>
     <row r="466">
-      <c r="A466" s="37"/>
+      <c r="A466" s="35"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
       <c r="D466" s="4"/>
@@ -13363,7 +13404,7 @@
       <c r="X466" s="4"/>
     </row>
     <row r="467">
-      <c r="A467" s="37"/>
+      <c r="A467" s="35"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
       <c r="D467" s="4"/>
@@ -13389,7 +13430,7 @@
       <c r="X467" s="4"/>
     </row>
     <row r="468">
-      <c r="A468" s="37"/>
+      <c r="A468" s="35"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
       <c r="D468" s="4"/>
@@ -13415,7 +13456,7 @@
       <c r="X468" s="4"/>
     </row>
     <row r="469">
-      <c r="A469" s="37"/>
+      <c r="A469" s="35"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
       <c r="D469" s="4"/>
@@ -13441,7 +13482,7 @@
       <c r="X469" s="4"/>
     </row>
     <row r="470">
-      <c r="A470" s="37"/>
+      <c r="A470" s="35"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
       <c r="D470" s="4"/>
@@ -13467,7 +13508,7 @@
       <c r="X470" s="4"/>
     </row>
     <row r="471">
-      <c r="A471" s="37"/>
+      <c r="A471" s="35"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
       <c r="D471" s="4"/>
@@ -13493,7 +13534,7 @@
       <c r="X471" s="4"/>
     </row>
     <row r="472">
-      <c r="A472" s="37"/>
+      <c r="A472" s="35"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
       <c r="D472" s="4"/>
@@ -13519,7 +13560,7 @@
       <c r="X472" s="4"/>
     </row>
     <row r="473">
-      <c r="A473" s="37"/>
+      <c r="A473" s="35"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
       <c r="D473" s="4"/>
@@ -13545,7 +13586,7 @@
       <c r="X473" s="4"/>
     </row>
     <row r="474">
-      <c r="A474" s="37"/>
+      <c r="A474" s="35"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
       <c r="D474" s="4"/>
@@ -13571,7 +13612,7 @@
       <c r="X474" s="4"/>
     </row>
     <row r="475">
-      <c r="A475" s="37"/>
+      <c r="A475" s="35"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
       <c r="D475" s="4"/>
@@ -13597,7 +13638,7 @@
       <c r="X475" s="4"/>
     </row>
     <row r="476">
-      <c r="A476" s="37"/>
+      <c r="A476" s="35"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
       <c r="D476" s="4"/>
@@ -13623,7 +13664,7 @@
       <c r="X476" s="4"/>
     </row>
     <row r="477">
-      <c r="A477" s="37"/>
+      <c r="A477" s="35"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
       <c r="D477" s="4"/>
@@ -13649,7 +13690,7 @@
       <c r="X477" s="4"/>
     </row>
     <row r="478">
-      <c r="A478" s="37"/>
+      <c r="A478" s="35"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
       <c r="D478" s="4"/>
@@ -13675,7 +13716,7 @@
       <c r="X478" s="4"/>
     </row>
     <row r="479">
-      <c r="A479" s="37"/>
+      <c r="A479" s="35"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
       <c r="D479" s="4"/>
@@ -13701,7 +13742,7 @@
       <c r="X479" s="4"/>
     </row>
     <row r="480">
-      <c r="A480" s="37"/>
+      <c r="A480" s="35"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
       <c r="D480" s="4"/>
@@ -13727,7 +13768,7 @@
       <c r="X480" s="4"/>
     </row>
     <row r="481">
-      <c r="A481" s="37"/>
+      <c r="A481" s="35"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
       <c r="D481" s="4"/>
@@ -13753,7 +13794,7 @@
       <c r="X481" s="4"/>
     </row>
     <row r="482">
-      <c r="A482" s="37"/>
+      <c r="A482" s="35"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
       <c r="D482" s="4"/>
@@ -13779,7 +13820,7 @@
       <c r="X482" s="4"/>
     </row>
     <row r="483">
-      <c r="A483" s="37"/>
+      <c r="A483" s="35"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
       <c r="D483" s="4"/>
@@ -13805,7 +13846,7 @@
       <c r="X483" s="4"/>
     </row>
     <row r="484">
-      <c r="A484" s="37"/>
+      <c r="A484" s="35"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
       <c r="D484" s="4"/>
@@ -13831,7 +13872,7 @@
       <c r="X484" s="4"/>
     </row>
     <row r="485">
-      <c r="A485" s="37"/>
+      <c r="A485" s="35"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
       <c r="D485" s="4"/>
@@ -13857,7 +13898,7 @@
       <c r="X485" s="4"/>
     </row>
     <row r="486">
-      <c r="A486" s="37"/>
+      <c r="A486" s="35"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
       <c r="D486" s="4"/>
@@ -13883,7 +13924,7 @@
       <c r="X486" s="4"/>
     </row>
     <row r="487">
-      <c r="A487" s="37"/>
+      <c r="A487" s="35"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
       <c r="D487" s="4"/>
@@ -13909,7 +13950,7 @@
       <c r="X487" s="4"/>
     </row>
     <row r="488">
-      <c r="A488" s="37"/>
+      <c r="A488" s="35"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
       <c r="D488" s="4"/>
@@ -13935,7 +13976,7 @@
       <c r="X488" s="4"/>
     </row>
     <row r="489">
-      <c r="A489" s="37"/>
+      <c r="A489" s="35"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
       <c r="D489" s="4"/>
@@ -13961,7 +14002,7 @@
       <c r="X489" s="4"/>
     </row>
     <row r="490">
-      <c r="A490" s="37"/>
+      <c r="A490" s="35"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
       <c r="D490" s="4"/>
@@ -13987,7 +14028,7 @@
       <c r="X490" s="4"/>
     </row>
     <row r="491">
-      <c r="A491" s="37"/>
+      <c r="A491" s="35"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
       <c r="D491" s="4"/>
@@ -14013,7 +14054,7 @@
       <c r="X491" s="4"/>
     </row>
     <row r="492">
-      <c r="A492" s="37"/>
+      <c r="A492" s="35"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
       <c r="D492" s="4"/>
@@ -14039,7 +14080,7 @@
       <c r="X492" s="4"/>
     </row>
     <row r="493">
-      <c r="A493" s="37"/>
+      <c r="A493" s="35"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
       <c r="D493" s="4"/>
@@ -14065,7 +14106,7 @@
       <c r="X493" s="4"/>
     </row>
     <row r="494">
-      <c r="A494" s="37"/>
+      <c r="A494" s="35"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
       <c r="D494" s="4"/>
@@ -14091,7 +14132,7 @@
       <c r="X494" s="4"/>
     </row>
     <row r="495">
-      <c r="A495" s="37"/>
+      <c r="A495" s="35"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
       <c r="D495" s="4"/>
@@ -14117,7 +14158,7 @@
       <c r="X495" s="4"/>
     </row>
     <row r="496">
-      <c r="A496" s="37"/>
+      <c r="A496" s="35"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
       <c r="D496" s="4"/>
@@ -14143,7 +14184,7 @@
       <c r="X496" s="4"/>
     </row>
     <row r="497">
-      <c r="A497" s="37"/>
+      <c r="A497" s="35"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
       <c r="D497" s="4"/>
@@ -14169,7 +14210,7 @@
       <c r="X497" s="4"/>
     </row>
     <row r="498">
-      <c r="A498" s="37"/>
+      <c r="A498" s="35"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
       <c r="D498" s="4"/>
@@ -14195,7 +14236,7 @@
       <c r="X498" s="4"/>
     </row>
     <row r="499">
-      <c r="A499" s="37"/>
+      <c r="A499" s="35"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
       <c r="D499" s="4"/>
@@ -14221,7 +14262,7 @@
       <c r="X499" s="4"/>
     </row>
     <row r="500">
-      <c r="A500" s="37"/>
+      <c r="A500" s="35"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
       <c r="D500" s="4"/>
@@ -14247,7 +14288,7 @@
       <c r="X500" s="4"/>
     </row>
     <row r="501">
-      <c r="A501" s="37"/>
+      <c r="A501" s="35"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
       <c r="D501" s="4"/>
@@ -14273,7 +14314,7 @@
       <c r="X501" s="4"/>
     </row>
     <row r="502">
-      <c r="A502" s="37"/>
+      <c r="A502" s="35"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
       <c r="D502" s="4"/>
@@ -14299,7 +14340,7 @@
       <c r="X502" s="4"/>
     </row>
     <row r="503">
-      <c r="A503" s="37"/>
+      <c r="A503" s="35"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
       <c r="D503" s="4"/>
@@ -14325,7 +14366,7 @@
       <c r="X503" s="4"/>
     </row>
     <row r="504">
-      <c r="A504" s="37"/>
+      <c r="A504" s="35"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
       <c r="D504" s="4"/>
@@ -14351,7 +14392,7 @@
       <c r="X504" s="4"/>
     </row>
     <row r="505">
-      <c r="A505" s="37"/>
+      <c r="A505" s="35"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
       <c r="D505" s="4"/>
@@ -14377,7 +14418,7 @@
       <c r="X505" s="4"/>
     </row>
     <row r="506">
-      <c r="A506" s="37"/>
+      <c r="A506" s="35"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
       <c r="D506" s="4"/>
@@ -14403,7 +14444,7 @@
       <c r="X506" s="4"/>
     </row>
     <row r="507">
-      <c r="A507" s="37"/>
+      <c r="A507" s="35"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
       <c r="D507" s="4"/>
@@ -14429,7 +14470,7 @@
       <c r="X507" s="4"/>
     </row>
     <row r="508">
-      <c r="A508" s="37"/>
+      <c r="A508" s="35"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
       <c r="D508" s="4"/>
@@ -14455,7 +14496,7 @@
       <c r="X508" s="4"/>
     </row>
     <row r="509">
-      <c r="A509" s="37"/>
+      <c r="A509" s="35"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
       <c r="D509" s="4"/>
@@ -14481,7 +14522,7 @@
       <c r="X509" s="4"/>
     </row>
     <row r="510">
-      <c r="A510" s="37"/>
+      <c r="A510" s="35"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
       <c r="D510" s="4"/>
@@ -14507,7 +14548,7 @@
       <c r="X510" s="4"/>
     </row>
     <row r="511">
-      <c r="A511" s="37"/>
+      <c r="A511" s="35"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
       <c r="D511" s="4"/>
@@ -14533,7 +14574,7 @@
       <c r="X511" s="4"/>
     </row>
     <row r="512">
-      <c r="A512" s="37"/>
+      <c r="A512" s="35"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
       <c r="D512" s="4"/>
@@ -14559,7 +14600,7 @@
       <c r="X512" s="4"/>
     </row>
     <row r="513">
-      <c r="A513" s="37"/>
+      <c r="A513" s="35"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
       <c r="D513" s="4"/>
@@ -14585,7 +14626,7 @@
       <c r="X513" s="4"/>
     </row>
     <row r="514">
-      <c r="A514" s="37"/>
+      <c r="A514" s="35"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
       <c r="D514" s="4"/>
@@ -14611,7 +14652,7 @@
       <c r="X514" s="4"/>
     </row>
     <row r="515">
-      <c r="A515" s="37"/>
+      <c r="A515" s="35"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
       <c r="D515" s="4"/>
@@ -14637,7 +14678,7 @@
       <c r="X515" s="4"/>
     </row>
     <row r="516">
-      <c r="A516" s="37"/>
+      <c r="A516" s="35"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
       <c r="D516" s="4"/>
@@ -14663,7 +14704,7 @@
       <c r="X516" s="4"/>
     </row>
     <row r="517">
-      <c r="A517" s="37"/>
+      <c r="A517" s="35"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
       <c r="D517" s="4"/>
@@ -14689,7 +14730,7 @@
       <c r="X517" s="4"/>
     </row>
     <row r="518">
-      <c r="A518" s="37"/>
+      <c r="A518" s="35"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
       <c r="D518" s="4"/>
@@ -14715,7 +14756,7 @@
       <c r="X518" s="4"/>
     </row>
     <row r="519">
-      <c r="A519" s="37"/>
+      <c r="A519" s="35"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
       <c r="D519" s="4"/>
@@ -14741,7 +14782,7 @@
       <c r="X519" s="4"/>
     </row>
     <row r="520">
-      <c r="A520" s="37"/>
+      <c r="A520" s="35"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
       <c r="D520" s="4"/>
@@ -14767,7 +14808,7 @@
       <c r="X520" s="4"/>
     </row>
     <row r="521">
-      <c r="A521" s="37"/>
+      <c r="A521" s="35"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
       <c r="D521" s="4"/>
@@ -14793,7 +14834,7 @@
       <c r="X521" s="4"/>
     </row>
     <row r="522">
-      <c r="A522" s="37"/>
+      <c r="A522" s="35"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
       <c r="D522" s="4"/>
@@ -14819,7 +14860,7 @@
       <c r="X522" s="4"/>
     </row>
     <row r="523">
-      <c r="A523" s="37"/>
+      <c r="A523" s="35"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
       <c r="D523" s="4"/>
@@ -14845,7 +14886,7 @@
       <c r="X523" s="4"/>
     </row>
     <row r="524">
-      <c r="A524" s="37"/>
+      <c r="A524" s="35"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
       <c r="D524" s="4"/>
@@ -14871,7 +14912,7 @@
       <c r="X524" s="4"/>
     </row>
     <row r="525">
-      <c r="A525" s="37"/>
+      <c r="A525" s="35"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
       <c r="D525" s="4"/>
@@ -14897,7 +14938,7 @@
       <c r="X525" s="4"/>
     </row>
     <row r="526">
-      <c r="A526" s="37"/>
+      <c r="A526" s="35"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
       <c r="D526" s="4"/>
@@ -14923,7 +14964,7 @@
       <c r="X526" s="4"/>
     </row>
     <row r="527">
-      <c r="A527" s="37"/>
+      <c r="A527" s="35"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
       <c r="D527" s="4"/>
@@ -14949,7 +14990,7 @@
       <c r="X527" s="4"/>
     </row>
     <row r="528">
-      <c r="A528" s="37"/>
+      <c r="A528" s="35"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
       <c r="D528" s="4"/>
@@ -14975,7 +15016,7 @@
       <c r="X528" s="4"/>
     </row>
     <row r="529">
-      <c r="A529" s="37"/>
+      <c r="A529" s="35"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
       <c r="D529" s="4"/>
@@ -15001,7 +15042,7 @@
       <c r="X529" s="4"/>
     </row>
     <row r="530">
-      <c r="A530" s="37"/>
+      <c r="A530" s="35"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
       <c r="D530" s="4"/>
@@ -15027,7 +15068,7 @@
       <c r="X530" s="4"/>
     </row>
     <row r="531">
-      <c r="A531" s="37"/>
+      <c r="A531" s="35"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
       <c r="D531" s="4"/>
@@ -15053,7 +15094,7 @@
       <c r="X531" s="4"/>
     </row>
     <row r="532">
-      <c r="A532" s="37"/>
+      <c r="A532" s="35"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
       <c r="D532" s="4"/>
@@ -15079,7 +15120,7 @@
       <c r="X532" s="4"/>
     </row>
     <row r="533">
-      <c r="A533" s="37"/>
+      <c r="A533" s="35"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
       <c r="D533" s="4"/>
@@ -15105,7 +15146,7 @@
       <c r="X533" s="4"/>
     </row>
     <row r="534">
-      <c r="A534" s="37"/>
+      <c r="A534" s="35"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
       <c r="D534" s="4"/>
@@ -15131,7 +15172,7 @@
       <c r="X534" s="4"/>
     </row>
     <row r="535">
-      <c r="A535" s="37"/>
+      <c r="A535" s="35"/>
       <c r="B535" s="4"/>
       <c r="C535" s="4"/>
       <c r="D535" s="4"/>
@@ -15157,7 +15198,7 @@
       <c r="X535" s="4"/>
     </row>
     <row r="536">
-      <c r="A536" s="37"/>
+      <c r="A536" s="35"/>
       <c r="B536" s="4"/>
       <c r="C536" s="4"/>
       <c r="D536" s="4"/>
@@ -15183,7 +15224,7 @@
       <c r="X536" s="4"/>
     </row>
     <row r="537">
-      <c r="A537" s="37"/>
+      <c r="A537" s="35"/>
       <c r="B537" s="4"/>
       <c r="C537" s="4"/>
       <c r="D537" s="4"/>
@@ -15209,7 +15250,7 @@
       <c r="X537" s="4"/>
     </row>
     <row r="538">
-      <c r="A538" s="37"/>
+      <c r="A538" s="35"/>
       <c r="B538" s="4"/>
       <c r="C538" s="4"/>
       <c r="D538" s="4"/>
@@ -15235,7 +15276,7 @@
       <c r="X538" s="4"/>
     </row>
     <row r="539">
-      <c r="A539" s="37"/>
+      <c r="A539" s="35"/>
       <c r="B539" s="4"/>
       <c r="C539" s="4"/>
       <c r="D539" s="4"/>
@@ -15261,7 +15302,7 @@
       <c r="X539" s="4"/>
     </row>
     <row r="540">
-      <c r="A540" s="37"/>
+      <c r="A540" s="35"/>
       <c r="B540" s="4"/>
       <c r="C540" s="4"/>
       <c r="D540" s="4"/>
@@ -15287,7 +15328,7 @@
       <c r="X540" s="4"/>
     </row>
     <row r="541">
-      <c r="A541" s="37"/>
+      <c r="A541" s="35"/>
       <c r="B541" s="4"/>
       <c r="C541" s="4"/>
       <c r="D541" s="4"/>
@@ -15313,7 +15354,7 @@
       <c r="X541" s="4"/>
     </row>
     <row r="542">
-      <c r="A542" s="37"/>
+      <c r="A542" s="35"/>
       <c r="B542" s="4"/>
       <c r="C542" s="4"/>
       <c r="D542" s="4"/>
@@ -15339,7 +15380,7 @@
       <c r="X542" s="4"/>
     </row>
     <row r="543">
-      <c r="A543" s="37"/>
+      <c r="A543" s="35"/>
       <c r="B543" s="4"/>
       <c r="C543" s="4"/>
       <c r="D543" s="4"/>
@@ -15365,7 +15406,7 @@
       <c r="X543" s="4"/>
     </row>
     <row r="544">
-      <c r="A544" s="37"/>
+      <c r="A544" s="35"/>
       <c r="B544" s="4"/>
       <c r="C544" s="4"/>
       <c r="D544" s="4"/>
@@ -15391,7 +15432,7 @@
       <c r="X544" s="4"/>
     </row>
     <row r="545">
-      <c r="A545" s="37"/>
+      <c r="A545" s="35"/>
       <c r="B545" s="4"/>
       <c r="C545" s="4"/>
       <c r="D545" s="4"/>
@@ -15417,7 +15458,7 @@
       <c r="X545" s="4"/>
     </row>
     <row r="546">
-      <c r="A546" s="37"/>
+      <c r="A546" s="35"/>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
       <c r="D546" s="4"/>
@@ -15443,7 +15484,7 @@
       <c r="X546" s="4"/>
     </row>
     <row r="547">
-      <c r="A547" s="37"/>
+      <c r="A547" s="35"/>
       <c r="B547" s="4"/>
       <c r="C547" s="4"/>
       <c r="D547" s="4"/>
@@ -15469,7 +15510,7 @@
       <c r="X547" s="4"/>
     </row>
     <row r="548">
-      <c r="A548" s="37"/>
+      <c r="A548" s="35"/>
       <c r="B548" s="4"/>
       <c r="C548" s="4"/>
       <c r="D548" s="4"/>
@@ -15495,7 +15536,7 @@
       <c r="X548" s="4"/>
     </row>
     <row r="549">
-      <c r="A549" s="37"/>
+      <c r="A549" s="35"/>
       <c r="B549" s="4"/>
       <c r="C549" s="4"/>
       <c r="D549" s="4"/>
@@ -15521,7 +15562,7 @@
       <c r="X549" s="4"/>
     </row>
     <row r="550">
-      <c r="A550" s="37"/>
+      <c r="A550" s="35"/>
       <c r="B550" s="4"/>
       <c r="C550" s="4"/>
       <c r="D550" s="4"/>
@@ -15547,7 +15588,7 @@
       <c r="X550" s="4"/>
     </row>
     <row r="551">
-      <c r="A551" s="37"/>
+      <c r="A551" s="35"/>
       <c r="B551" s="4"/>
       <c r="C551" s="4"/>
       <c r="D551" s="4"/>
@@ -15573,7 +15614,7 @@
       <c r="X551" s="4"/>
     </row>
     <row r="552">
-      <c r="A552" s="37"/>
+      <c r="A552" s="35"/>
       <c r="B552" s="4"/>
       <c r="C552" s="4"/>
       <c r="D552" s="4"/>
@@ -15599,7 +15640,7 @@
       <c r="X552" s="4"/>
     </row>
     <row r="553">
-      <c r="A553" s="37"/>
+      <c r="A553" s="35"/>
       <c r="B553" s="4"/>
       <c r="C553" s="4"/>
       <c r="D553" s="4"/>
@@ -15625,7 +15666,7 @@
       <c r="X553" s="4"/>
     </row>
     <row r="554">
-      <c r="A554" s="37"/>
+      <c r="A554" s="35"/>
       <c r="B554" s="4"/>
       <c r="C554" s="4"/>
       <c r="D554" s="4"/>
@@ -15651,7 +15692,7 @@
       <c r="X554" s="4"/>
     </row>
     <row r="555">
-      <c r="A555" s="37"/>
+      <c r="A555" s="35"/>
       <c r="B555" s="4"/>
       <c r="C555" s="4"/>
       <c r="D555" s="4"/>
@@ -15677,7 +15718,7 @@
       <c r="X555" s="4"/>
     </row>
     <row r="556">
-      <c r="A556" s="37"/>
+      <c r="A556" s="35"/>
       <c r="B556" s="4"/>
       <c r="C556" s="4"/>
       <c r="D556" s="4"/>
@@ -15703,7 +15744,7 @@
       <c r="X556" s="4"/>
     </row>
     <row r="557">
-      <c r="A557" s="37"/>
+      <c r="A557" s="35"/>
       <c r="B557" s="4"/>
       <c r="C557" s="4"/>
       <c r="D557" s="4"/>
@@ -15729,7 +15770,7 @@
       <c r="X557" s="4"/>
     </row>
     <row r="558">
-      <c r="A558" s="37"/>
+      <c r="A558" s="35"/>
       <c r="B558" s="4"/>
       <c r="C558" s="4"/>
       <c r="D558" s="4"/>
@@ -15755,7 +15796,7 @@
       <c r="X558" s="4"/>
     </row>
     <row r="559">
-      <c r="A559" s="37"/>
+      <c r="A559" s="35"/>
       <c r="B559" s="4"/>
       <c r="C559" s="4"/>
       <c r="D559" s="4"/>
@@ -15781,7 +15822,7 @@
       <c r="X559" s="4"/>
     </row>
     <row r="560">
-      <c r="A560" s="37"/>
+      <c r="A560" s="35"/>
       <c r="B560" s="4"/>
       <c r="C560" s="4"/>
       <c r="D560" s="4"/>
@@ -15807,7 +15848,7 @@
       <c r="X560" s="4"/>
     </row>
     <row r="561">
-      <c r="A561" s="37"/>
+      <c r="A561" s="35"/>
       <c r="B561" s="4"/>
       <c r="C561" s="4"/>
       <c r="D561" s="4"/>
@@ -15833,7 +15874,7 @@
       <c r="X561" s="4"/>
     </row>
     <row r="562">
-      <c r="A562" s="37"/>
+      <c r="A562" s="35"/>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
       <c r="D562" s="4"/>
@@ -15859,7 +15900,7 @@
       <c r="X562" s="4"/>
     </row>
     <row r="563">
-      <c r="A563" s="37"/>
+      <c r="A563" s="35"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
       <c r="D563" s="4"/>
@@ -15885,7 +15926,7 @@
       <c r="X563" s="4"/>
     </row>
     <row r="564">
-      <c r="A564" s="37"/>
+      <c r="A564" s="35"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
       <c r="D564" s="4"/>
@@ -15911,7 +15952,7 @@
       <c r="X564" s="4"/>
     </row>
     <row r="565">
-      <c r="A565" s="37"/>
+      <c r="A565" s="35"/>
       <c r="B565" s="4"/>
       <c r="C565" s="4"/>
       <c r="D565" s="4"/>
@@ -15937,7 +15978,7 @@
       <c r="X565" s="4"/>
     </row>
     <row r="566">
-      <c r="A566" s="37"/>
+      <c r="A566" s="35"/>
       <c r="B566" s="4"/>
       <c r="C566" s="4"/>
       <c r="D566" s="4"/>
@@ -15963,7 +16004,7 @@
       <c r="X566" s="4"/>
     </row>
     <row r="567">
-      <c r="A567" s="37"/>
+      <c r="A567" s="35"/>
       <c r="B567" s="4"/>
       <c r="C567" s="4"/>
       <c r="D567" s="4"/>
@@ -15989,7 +16030,7 @@
       <c r="X567" s="4"/>
     </row>
     <row r="568">
-      <c r="A568" s="37"/>
+      <c r="A568" s="35"/>
       <c r="B568" s="4"/>
       <c r="C568" s="4"/>
       <c r="D568" s="4"/>
@@ -16015,7 +16056,7 @@
       <c r="X568" s="4"/>
     </row>
     <row r="569">
-      <c r="A569" s="37"/>
+      <c r="A569" s="35"/>
       <c r="B569" s="4"/>
       <c r="C569" s="4"/>
       <c r="D569" s="4"/>
@@ -16041,7 +16082,7 @@
       <c r="X569" s="4"/>
     </row>
     <row r="570">
-      <c r="A570" s="37"/>
+      <c r="A570" s="35"/>
       <c r="B570" s="4"/>
       <c r="C570" s="4"/>
       <c r="D570" s="4"/>
@@ -16067,7 +16108,7 @@
       <c r="X570" s="4"/>
     </row>
     <row r="571">
-      <c r="A571" s="37"/>
+      <c r="A571" s="35"/>
       <c r="B571" s="4"/>
       <c r="C571" s="4"/>
       <c r="D571" s="4"/>
@@ -16093,7 +16134,7 @@
       <c r="X571" s="4"/>
     </row>
     <row r="572">
-      <c r="A572" s="37"/>
+      <c r="A572" s="35"/>
       <c r="B572" s="4"/>
       <c r="C572" s="4"/>
       <c r="D572" s="4"/>
@@ -16119,7 +16160,7 @@
       <c r="X572" s="4"/>
     </row>
     <row r="573">
-      <c r="A573" s="37"/>
+      <c r="A573" s="35"/>
       <c r="B573" s="4"/>
       <c r="C573" s="4"/>
       <c r="D573" s="4"/>
@@ -16145,7 +16186,7 @@
       <c r="X573" s="4"/>
     </row>
     <row r="574">
-      <c r="A574" s="37"/>
+      <c r="A574" s="35"/>
       <c r="B574" s="4"/>
       <c r="C574" s="4"/>
       <c r="D574" s="4"/>
@@ -16171,7 +16212,7 @@
       <c r="X574" s="4"/>
     </row>
     <row r="575">
-      <c r="A575" s="37"/>
+      <c r="A575" s="35"/>
       <c r="B575" s="4"/>
       <c r="C575" s="4"/>
       <c r="D575" s="4"/>
@@ -16197,7 +16238,7 @@
       <c r="X575" s="4"/>
     </row>
     <row r="576">
-      <c r="A576" s="37"/>
+      <c r="A576" s="35"/>
       <c r="B576" s="4"/>
       <c r="C576" s="4"/>
       <c r="D576" s="4"/>
@@ -16223,7 +16264,7 @@
       <c r="X576" s="4"/>
     </row>
     <row r="577">
-      <c r="A577" s="37"/>
+      <c r="A577" s="35"/>
       <c r="B577" s="4"/>
       <c r="C577" s="4"/>
       <c r="D577" s="4"/>
@@ -16249,7 +16290,7 @@
       <c r="X577" s="4"/>
     </row>
     <row r="578">
-      <c r="A578" s="37"/>
+      <c r="A578" s="35"/>
       <c r="B578" s="4"/>
       <c r="C578" s="4"/>
       <c r="D578" s="4"/>
@@ -16275,7 +16316,7 @@
       <c r="X578" s="4"/>
     </row>
     <row r="579">
-      <c r="A579" s="37"/>
+      <c r="A579" s="35"/>
       <c r="B579" s="4"/>
       <c r="C579" s="4"/>
       <c r="D579" s="4"/>
@@ -16301,7 +16342,7 @@
       <c r="X579" s="4"/>
     </row>
     <row r="580">
-      <c r="A580" s="37"/>
+      <c r="A580" s="35"/>
       <c r="B580" s="4"/>
       <c r="C580" s="4"/>
       <c r="D580" s="4"/>
@@ -16327,7 +16368,7 @@
       <c r="X580" s="4"/>
     </row>
     <row r="581">
-      <c r="A581" s="37"/>
+      <c r="A581" s="35"/>
       <c r="B581" s="4"/>
       <c r="C581" s="4"/>
       <c r="D581" s="4"/>
@@ -16353,7 +16394,7 @@
       <c r="X581" s="4"/>
     </row>
     <row r="582">
-      <c r="A582" s="37"/>
+      <c r="A582" s="35"/>
       <c r="B582" s="4"/>
       <c r="C582" s="4"/>
       <c r="D582" s="4"/>
@@ -16379,7 +16420,7 @@
       <c r="X582" s="4"/>
     </row>
     <row r="583">
-      <c r="A583" s="37"/>
+      <c r="A583" s="35"/>
       <c r="B583" s="4"/>
       <c r="C583" s="4"/>
       <c r="D583" s="4"/>
@@ -16405,7 +16446,7 @@
       <c r="X583" s="4"/>
     </row>
     <row r="584">
-      <c r="A584" s="37"/>
+      <c r="A584" s="35"/>
       <c r="B584" s="4"/>
       <c r="C584" s="4"/>
       <c r="D584" s="4"/>
@@ -16431,7 +16472,7 @@
       <c r="X584" s="4"/>
     </row>
     <row r="585">
-      <c r="A585" s="37"/>
+      <c r="A585" s="35"/>
       <c r="B585" s="4"/>
       <c r="C585" s="4"/>
       <c r="D585" s="4"/>
@@ -16457,7 +16498,7 @@
       <c r="X585" s="4"/>
     </row>
     <row r="586">
-      <c r="A586" s="37"/>
+      <c r="A586" s="35"/>
       <c r="B586" s="4"/>
       <c r="C586" s="4"/>
       <c r="D586" s="4"/>
@@ -16483,7 +16524,7 @@
       <c r="X586" s="4"/>
     </row>
     <row r="587">
-      <c r="A587" s="37"/>
+      <c r="A587" s="35"/>
       <c r="B587" s="4"/>
       <c r="C587" s="4"/>
       <c r="D587" s="4"/>
@@ -16509,7 +16550,7 @@
       <c r="X587" s="4"/>
     </row>
     <row r="588">
-      <c r="A588" s="37"/>
+      <c r="A588" s="35"/>
       <c r="B588" s="4"/>
       <c r="C588" s="4"/>
       <c r="D588" s="4"/>
@@ -16535,7 +16576,7 @@
       <c r="X588" s="4"/>
     </row>
     <row r="589">
-      <c r="A589" s="37"/>
+      <c r="A589" s="35"/>
       <c r="B589" s="4"/>
       <c r="C589" s="4"/>
       <c r="D589" s="4"/>
@@ -16561,7 +16602,7 @@
       <c r="X589" s="4"/>
     </row>
     <row r="590">
-      <c r="A590" s="37"/>
+      <c r="A590" s="35"/>
       <c r="B590" s="4"/>
       <c r="C590" s="4"/>
       <c r="D590" s="4"/>
@@ -16587,7 +16628,7 @@
       <c r="X590" s="4"/>
     </row>
     <row r="591">
-      <c r="A591" s="37"/>
+      <c r="A591" s="35"/>
       <c r="B591" s="4"/>
       <c r="C591" s="4"/>
       <c r="D591" s="4"/>
@@ -16613,7 +16654,7 @@
       <c r="X591" s="4"/>
     </row>
     <row r="592">
-      <c r="A592" s="37"/>
+      <c r="A592" s="35"/>
       <c r="B592" s="4"/>
       <c r="C592" s="4"/>
       <c r="D592" s="4"/>
@@ -16639,7 +16680,7 @@
       <c r="X592" s="4"/>
     </row>
     <row r="593">
-      <c r="A593" s="37"/>
+      <c r="A593" s="35"/>
       <c r="B593" s="4"/>
       <c r="C593" s="4"/>
       <c r="D593" s="4"/>
@@ -16665,7 +16706,7 @@
       <c r="X593" s="4"/>
     </row>
     <row r="594">
-      <c r="A594" s="37"/>
+      <c r="A594" s="35"/>
       <c r="B594" s="4"/>
       <c r="C594" s="4"/>
       <c r="D594" s="4"/>
@@ -16691,7 +16732,7 @@
       <c r="X594" s="4"/>
     </row>
     <row r="595">
-      <c r="A595" s="37"/>
+      <c r="A595" s="35"/>
       <c r="B595" s="4"/>
       <c r="C595" s="4"/>
       <c r="D595" s="4"/>
@@ -16717,7 +16758,7 @@
       <c r="X595" s="4"/>
     </row>
     <row r="596">
-      <c r="A596" s="37"/>
+      <c r="A596" s="35"/>
       <c r="B596" s="4"/>
       <c r="C596" s="4"/>
       <c r="D596" s="4"/>
@@ -16743,7 +16784,7 @@
       <c r="X596" s="4"/>
     </row>
     <row r="597">
-      <c r="A597" s="37"/>
+      <c r="A597" s="35"/>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
       <c r="D597" s="4"/>
@@ -16769,7 +16810,7 @@
       <c r="X597" s="4"/>
     </row>
     <row r="598">
-      <c r="A598" s="37"/>
+      <c r="A598" s="35"/>
       <c r="B598" s="4"/>
       <c r="C598" s="4"/>
       <c r="D598" s="4"/>
@@ -16795,7 +16836,7 @@
       <c r="X598" s="4"/>
     </row>
     <row r="599">
-      <c r="A599" s="37"/>
+      <c r="A599" s="35"/>
       <c r="B599" s="4"/>
       <c r="C599" s="4"/>
       <c r="D599" s="4"/>
@@ -16821,7 +16862,7 @@
       <c r="X599" s="4"/>
     </row>
     <row r="600">
-      <c r="A600" s="37"/>
+      <c r="A600" s="35"/>
       <c r="B600" s="4"/>
       <c r="C600" s="4"/>
       <c r="D600" s="4"/>
@@ -16847,7 +16888,7 @@
       <c r="X600" s="4"/>
     </row>
     <row r="601">
-      <c r="A601" s="37"/>
+      <c r="A601" s="35"/>
       <c r="B601" s="4"/>
       <c r="C601" s="4"/>
       <c r="D601" s="4"/>
@@ -16873,7 +16914,7 @@
       <c r="X601" s="4"/>
     </row>
     <row r="602">
-      <c r="A602" s="37"/>
+      <c r="A602" s="35"/>
       <c r="B602" s="4"/>
       <c r="C602" s="4"/>
       <c r="D602" s="4"/>
@@ -16899,7 +16940,7 @@
       <c r="X602" s="4"/>
     </row>
     <row r="603">
-      <c r="A603" s="37"/>
+      <c r="A603" s="35"/>
       <c r="B603" s="4"/>
       <c r="C603" s="4"/>
       <c r="D603" s="4"/>
@@ -16925,7 +16966,7 @@
       <c r="X603" s="4"/>
     </row>
     <row r="604">
-      <c r="A604" s="37"/>
+      <c r="A604" s="35"/>
       <c r="B604" s="4"/>
       <c r="C604" s="4"/>
       <c r="D604" s="4"/>
@@ -16951,7 +16992,7 @@
       <c r="X604" s="4"/>
     </row>
     <row r="605">
-      <c r="A605" s="37"/>
+      <c r="A605" s="35"/>
       <c r="B605" s="4"/>
       <c r="C605" s="4"/>
       <c r="D605" s="4"/>
@@ -16977,7 +17018,7 @@
       <c r="X605" s="4"/>
     </row>
     <row r="606">
-      <c r="A606" s="37"/>
+      <c r="A606" s="35"/>
       <c r="B606" s="4"/>
       <c r="C606" s="4"/>
       <c r="D606" s="4"/>
@@ -17003,7 +17044,7 @@
       <c r="X606" s="4"/>
     </row>
     <row r="607">
-      <c r="A607" s="37"/>
+      <c r="A607" s="35"/>
       <c r="B607" s="4"/>
       <c r="C607" s="4"/>
       <c r="D607" s="4"/>
@@ -17029,7 +17070,7 @@
       <c r="X607" s="4"/>
     </row>
     <row r="608">
-      <c r="A608" s="37"/>
+      <c r="A608" s="35"/>
       <c r="B608" s="4"/>
       <c r="C608" s="4"/>
       <c r="D608" s="4"/>
@@ -17055,7 +17096,7 @@
       <c r="X608" s="4"/>
     </row>
     <row r="609">
-      <c r="A609" s="37"/>
+      <c r="A609" s="35"/>
       <c r="B609" s="4"/>
       <c r="C609" s="4"/>
       <c r="D609" s="4"/>
@@ -17081,7 +17122,7 @@
       <c r="X609" s="4"/>
     </row>
     <row r="610">
-      <c r="A610" s="37"/>
+      <c r="A610" s="35"/>
       <c r="B610" s="4"/>
       <c r="C610" s="4"/>
       <c r="D610" s="4"/>
@@ -17107,7 +17148,7 @@
       <c r="X610" s="4"/>
     </row>
     <row r="611">
-      <c r="A611" s="37"/>
+      <c r="A611" s="35"/>
       <c r="B611" s="4"/>
       <c r="C611" s="4"/>
       <c r="D611" s="4"/>
@@ -17133,7 +17174,7 @@
       <c r="X611" s="4"/>
     </row>
     <row r="612">
-      <c r="A612" s="37"/>
+      <c r="A612" s="35"/>
       <c r="B612" s="4"/>
       <c r="C612" s="4"/>
       <c r="D612" s="4"/>
@@ -17159,7 +17200,7 @@
       <c r="X612" s="4"/>
     </row>
     <row r="613">
-      <c r="A613" s="37"/>
+      <c r="A613" s="35"/>
       <c r="B613" s="4"/>
       <c r="C613" s="4"/>
       <c r="D613" s="4"/>
@@ -17185,7 +17226,7 @@
       <c r="X613" s="4"/>
     </row>
     <row r="614">
-      <c r="A614" s="37"/>
+      <c r="A614" s="35"/>
       <c r="B614" s="4"/>
       <c r="C614" s="4"/>
       <c r="D614" s="4"/>
@@ -17211,7 +17252,7 @@
       <c r="X614" s="4"/>
     </row>
     <row r="615">
-      <c r="A615" s="37"/>
+      <c r="A615" s="35"/>
       <c r="B615" s="4"/>
       <c r="C615" s="4"/>
       <c r="D615" s="4"/>
@@ -17237,7 +17278,7 @@
       <c r="X615" s="4"/>
     </row>
     <row r="616">
-      <c r="A616" s="37"/>
+      <c r="A616" s="35"/>
       <c r="B616" s="4"/>
       <c r="C616" s="4"/>
       <c r="D616" s="4"/>
@@ -17263,7 +17304,7 @@
       <c r="X616" s="4"/>
     </row>
     <row r="617">
-      <c r="A617" s="37"/>
+      <c r="A617" s="35"/>
       <c r="B617" s="4"/>
       <c r="C617" s="4"/>
       <c r="D617" s="4"/>
@@ -17289,7 +17330,7 @@
       <c r="X617" s="4"/>
     </row>
     <row r="618">
-      <c r="A618" s="37"/>
+      <c r="A618" s="35"/>
       <c r="B618" s="4"/>
       <c r="C618" s="4"/>
       <c r="D618" s="4"/>
@@ -17315,7 +17356,7 @@
       <c r="X618" s="4"/>
     </row>
     <row r="619">
-      <c r="A619" s="37"/>
+      <c r="A619" s="35"/>
       <c r="B619" s="4"/>
       <c r="C619" s="4"/>
       <c r="D619" s="4"/>
@@ -17341,7 +17382,7 @@
       <c r="X619" s="4"/>
     </row>
     <row r="620">
-      <c r="A620" s="37"/>
+      <c r="A620" s="35"/>
       <c r="B620" s="4"/>
       <c r="C620" s="4"/>
       <c r="D620" s="4"/>
@@ -17367,7 +17408,7 @@
       <c r="X620" s="4"/>
     </row>
     <row r="621">
-      <c r="A621" s="37"/>
+      <c r="A621" s="35"/>
       <c r="B621" s="4"/>
       <c r="C621" s="4"/>
       <c r="D621" s="4"/>
@@ -17393,7 +17434,7 @@
       <c r="X621" s="4"/>
     </row>
     <row r="622">
-      <c r="A622" s="37"/>
+      <c r="A622" s="35"/>
       <c r="B622" s="4"/>
       <c r="C622" s="4"/>
       <c r="D622" s="4"/>
@@ -17419,7 +17460,7 @@
       <c r="X622" s="4"/>
     </row>
     <row r="623">
-      <c r="A623" s="37"/>
+      <c r="A623" s="35"/>
       <c r="B623" s="4"/>
       <c r="C623" s="4"/>
       <c r="D623" s="4"/>
@@ -17445,7 +17486,7 @@
       <c r="X623" s="4"/>
     </row>
     <row r="624">
-      <c r="A624" s="37"/>
+      <c r="A624" s="35"/>
       <c r="B624" s="4"/>
       <c r="C624" s="4"/>
       <c r="D624" s="4"/>
@@ -17471,7 +17512,7 @@
       <c r="X624" s="4"/>
     </row>
     <row r="625">
-      <c r="A625" s="37"/>
+      <c r="A625" s="35"/>
       <c r="B625" s="4"/>
       <c r="C625" s="4"/>
       <c r="D625" s="4"/>
@@ -17497,7 +17538,7 @@
       <c r="X625" s="4"/>
     </row>
     <row r="626">
-      <c r="A626" s="37"/>
+      <c r="A626" s="35"/>
       <c r="B626" s="4"/>
       <c r="C626" s="4"/>
       <c r="D626" s="4"/>
@@ -17523,7 +17564,7 @@
       <c r="X626" s="4"/>
     </row>
     <row r="627">
-      <c r="A627" s="37"/>
+      <c r="A627" s="35"/>
       <c r="B627" s="4"/>
       <c r="C627" s="4"/>
       <c r="D627" s="4"/>
@@ -17549,7 +17590,7 @@
       <c r="X627" s="4"/>
     </row>
     <row r="628">
-      <c r="A628" s="37"/>
+      <c r="A628" s="35"/>
       <c r="B628" s="4"/>
       <c r="C628" s="4"/>
       <c r="D628" s="4"/>
@@ -17575,7 +17616,7 @@
       <c r="X628" s="4"/>
     </row>
     <row r="629">
-      <c r="A629" s="37"/>
+      <c r="A629" s="35"/>
       <c r="B629" s="4"/>
       <c r="C629" s="4"/>
       <c r="D629" s="4"/>
@@ -17601,7 +17642,7 @@
       <c r="X629" s="4"/>
     </row>
     <row r="630">
-      <c r="A630" s="37"/>
+      <c r="A630" s="35"/>
       <c r="B630" s="4"/>
       <c r="C630" s="4"/>
       <c r="D630" s="4"/>
@@ -17627,7 +17668,7 @@
       <c r="X630" s="4"/>
     </row>
     <row r="631">
-      <c r="A631" s="37"/>
+      <c r="A631" s="35"/>
       <c r="B631" s="4"/>
       <c r="C631" s="4"/>
       <c r="D631" s="4"/>
@@ -17653,7 +17694,7 @@
       <c r="X631" s="4"/>
     </row>
     <row r="632">
-      <c r="A632" s="37"/>
+      <c r="A632" s="35"/>
       <c r="B632" s="4"/>
       <c r="C632" s="4"/>
       <c r="D632" s="4"/>
@@ -17679,7 +17720,7 @@
       <c r="X632" s="4"/>
     </row>
     <row r="633">
-      <c r="A633" s="37"/>
+      <c r="A633" s="35"/>
       <c r="B633" s="4"/>
       <c r="C633" s="4"/>
       <c r="D633" s="4"/>
@@ -17705,7 +17746,7 @@
       <c r="X633" s="4"/>
     </row>
     <row r="634">
-      <c r="A634" s="37"/>
+      <c r="A634" s="35"/>
       <c r="B634" s="4"/>
       <c r="C634" s="4"/>
       <c r="D634" s="4"/>
@@ -17731,7 +17772,7 @@
       <c r="X634" s="4"/>
     </row>
     <row r="635">
-      <c r="A635" s="37"/>
+      <c r="A635" s="35"/>
       <c r="B635" s="4"/>
       <c r="C635" s="4"/>
       <c r="D635" s="4"/>
@@ -17757,7 +17798,7 @@
       <c r="X635" s="4"/>
     </row>
     <row r="636">
-      <c r="A636" s="37"/>
+      <c r="A636" s="35"/>
       <c r="B636" s="4"/>
       <c r="C636" s="4"/>
       <c r="D636" s="4"/>
@@ -17783,7 +17824,7 @@
       <c r="X636" s="4"/>
     </row>
     <row r="637">
-      <c r="A637" s="37"/>
+      <c r="A637" s="35"/>
       <c r="B637" s="4"/>
       <c r="C637" s="4"/>
       <c r="D637" s="4"/>
@@ -17809,7 +17850,7 @@
       <c r="X637" s="4"/>
     </row>
     <row r="638">
-      <c r="A638" s="37"/>
+      <c r="A638" s="35"/>
       <c r="B638" s="4"/>
       <c r="C638" s="4"/>
       <c r="D638" s="4"/>
@@ -17835,7 +17876,7 @@
       <c r="X638" s="4"/>
     </row>
     <row r="639">
-      <c r="A639" s="37"/>
+      <c r="A639" s="35"/>
       <c r="B639" s="4"/>
       <c r="C639" s="4"/>
       <c r="D639" s="4"/>
@@ -17861,7 +17902,7 @@
       <c r="X639" s="4"/>
     </row>
     <row r="640">
-      <c r="A640" s="37"/>
+      <c r="A640" s="35"/>
       <c r="B640" s="4"/>
       <c r="C640" s="4"/>
       <c r="D640" s="4"/>
@@ -17887,7 +17928,7 @@
       <c r="X640" s="4"/>
     </row>
     <row r="641">
-      <c r="A641" s="37"/>
+      <c r="A641" s="35"/>
       <c r="B641" s="4"/>
       <c r="C641" s="4"/>
       <c r="D641" s="4"/>
@@ -17913,7 +17954,7 @@
       <c r="X641" s="4"/>
     </row>
     <row r="642">
-      <c r="A642" s="37"/>
+      <c r="A642" s="35"/>
       <c r="B642" s="4"/>
       <c r="C642" s="4"/>
       <c r="D642" s="4"/>
@@ -17939,7 +17980,7 @@
       <c r="X642" s="4"/>
     </row>
     <row r="643">
-      <c r="A643" s="37"/>
+      <c r="A643" s="35"/>
       <c r="B643" s="4"/>
       <c r="C643" s="4"/>
       <c r="D643" s="4"/>
@@ -17965,7 +18006,7 @@
       <c r="X643" s="4"/>
     </row>
     <row r="644">
-      <c r="A644" s="37"/>
+      <c r="A644" s="35"/>
       <c r="B644" s="4"/>
       <c r="C644" s="4"/>
       <c r="D644" s="4"/>
@@ -17991,7 +18032,7 @@
       <c r="X644" s="4"/>
     </row>
     <row r="645">
-      <c r="A645" s="37"/>
+      <c r="A645" s="35"/>
       <c r="B645" s="4"/>
       <c r="C645" s="4"/>
       <c r="D645" s="4"/>
@@ -18017,7 +18058,7 @@
       <c r="X645" s="4"/>
     </row>
     <row r="646">
-      <c r="A646" s="37"/>
+      <c r="A646" s="35"/>
       <c r="B646" s="4"/>
       <c r="C646" s="4"/>
       <c r="D646" s="4"/>
@@ -18043,7 +18084,7 @@
       <c r="X646" s="4"/>
     </row>
     <row r="647">
-      <c r="A647" s="37"/>
+      <c r="A647" s="35"/>
       <c r="B647" s="4"/>
       <c r="C647" s="4"/>
       <c r="D647" s="4"/>
@@ -18069,7 +18110,7 @@
       <c r="X647" s="4"/>
     </row>
     <row r="648">
-      <c r="A648" s="37"/>
+      <c r="A648" s="35"/>
       <c r="B648" s="4"/>
       <c r="C648" s="4"/>
       <c r="D648" s="4"/>
@@ -18095,7 +18136,7 @@
       <c r="X648" s="4"/>
     </row>
     <row r="649">
-      <c r="A649" s="37"/>
+      <c r="A649" s="35"/>
       <c r="B649" s="4"/>
       <c r="C649" s="4"/>
       <c r="D649" s="4"/>
@@ -18121,7 +18162,7 @@
       <c r="X649" s="4"/>
     </row>
     <row r="650">
-      <c r="A650" s="37"/>
+      <c r="A650" s="35"/>
       <c r="B650" s="4"/>
       <c r="C650" s="4"/>
       <c r="D650" s="4"/>
@@ -18147,7 +18188,7 @@
       <c r="X650" s="4"/>
     </row>
     <row r="651">
-      <c r="A651" s="37"/>
+      <c r="A651" s="35"/>
       <c r="B651" s="4"/>
       <c r="C651" s="4"/>
       <c r="D651" s="4"/>
@@ -18173,7 +18214,7 @@
       <c r="X651" s="4"/>
     </row>
     <row r="652">
-      <c r="A652" s="37"/>
+      <c r="A652" s="35"/>
       <c r="B652" s="4"/>
       <c r="C652" s="4"/>
       <c r="D652" s="4"/>
@@ -18199,7 +18240,7 @@
       <c r="X652" s="4"/>
     </row>
     <row r="653">
-      <c r="A653" s="37"/>
+      <c r="A653" s="35"/>
       <c r="B653" s="4"/>
       <c r="C653" s="4"/>
       <c r="D653" s="4"/>
@@ -18225,7 +18266,7 @@
       <c r="X653" s="4"/>
     </row>
     <row r="654">
-      <c r="A654" s="37"/>
+      <c r="A654" s="35"/>
       <c r="B654" s="4"/>
       <c r="C654" s="4"/>
       <c r="D654" s="4"/>
@@ -18251,7 +18292,7 @@
       <c r="X654" s="4"/>
     </row>
     <row r="655">
-      <c r="A655" s="37"/>
+      <c r="A655" s="35"/>
       <c r="B655" s="4"/>
       <c r="C655" s="4"/>
       <c r="D655" s="4"/>
@@ -18277,7 +18318,7 @@
       <c r="X655" s="4"/>
     </row>
     <row r="656">
-      <c r="A656" s="37"/>
+      <c r="A656" s="35"/>
       <c r="B656" s="4"/>
       <c r="C656" s="4"/>
       <c r="D656" s="4"/>
@@ -18303,7 +18344,7 @@
       <c r="X656" s="4"/>
     </row>
     <row r="657">
-      <c r="A657" s="37"/>
+      <c r="A657" s="35"/>
       <c r="B657" s="4"/>
       <c r="C657" s="4"/>
       <c r="D657" s="4"/>
@@ -18329,7 +18370,7 @@
       <c r="X657" s="4"/>
     </row>
     <row r="658">
-      <c r="A658" s="37"/>
+      <c r="A658" s="35"/>
       <c r="B658" s="4"/>
       <c r="C658" s="4"/>
       <c r="D658" s="4"/>
@@ -18355,7 +18396,7 @@
       <c r="X658" s="4"/>
     </row>
     <row r="659">
-      <c r="A659" s="37"/>
+      <c r="A659" s="35"/>
       <c r="B659" s="4"/>
       <c r="C659" s="4"/>
       <c r="D659" s="4"/>
@@ -18381,7 +18422,7 @@
       <c r="X659" s="4"/>
     </row>
     <row r="660">
-      <c r="A660" s="37"/>
+      <c r="A660" s="35"/>
       <c r="B660" s="4"/>
       <c r="C660" s="4"/>
       <c r="D660" s="4"/>
@@ -18407,7 +18448,7 @@
       <c r="X660" s="4"/>
     </row>
     <row r="661">
-      <c r="A661" s="37"/>
+      <c r="A661" s="35"/>
       <c r="B661" s="4"/>
       <c r="C661" s="4"/>
       <c r="D661" s="4"/>
@@ -18433,7 +18474,7 @@
       <c r="X661" s="4"/>
     </row>
     <row r="662">
-      <c r="A662" s="37"/>
+      <c r="A662" s="35"/>
       <c r="B662" s="4"/>
       <c r="C662" s="4"/>
       <c r="D662" s="4"/>
@@ -18459,7 +18500,7 @@
       <c r="X662" s="4"/>
     </row>
     <row r="663">
-      <c r="A663" s="37"/>
+      <c r="A663" s="35"/>
       <c r="B663" s="4"/>
       <c r="C663" s="4"/>
       <c r="D663" s="4"/>
@@ -18485,7 +18526,7 @@
       <c r="X663" s="4"/>
     </row>
     <row r="664">
-      <c r="A664" s="37"/>
+      <c r="A664" s="35"/>
       <c r="B664" s="4"/>
       <c r="C664" s="4"/>
       <c r="D664" s="4"/>
@@ -18511,7 +18552,7 @@
       <c r="X664" s="4"/>
     </row>
     <row r="665">
-      <c r="A665" s="37"/>
+      <c r="A665" s="35"/>
       <c r="B665" s="4"/>
       <c r="C665" s="4"/>
       <c r="D665" s="4"/>
@@ -18537,7 +18578,7 @@
       <c r="X665" s="4"/>
     </row>
     <row r="666">
-      <c r="A666" s="37"/>
+      <c r="A666" s="35"/>
       <c r="B666" s="4"/>
       <c r="C666" s="4"/>
       <c r="D666" s="4"/>
@@ -18563,7 +18604,7 @@
       <c r="X666" s="4"/>
     </row>
     <row r="667">
-      <c r="A667" s="37"/>
+      <c r="A667" s="35"/>
       <c r="B667" s="4"/>
       <c r="C667" s="4"/>
       <c r="D667" s="4"/>
@@ -18589,7 +18630,7 @@
       <c r="X667" s="4"/>
     </row>
     <row r="668">
-      <c r="A668" s="37"/>
+      <c r="A668" s="35"/>
       <c r="B668" s="4"/>
       <c r="C668" s="4"/>
       <c r="D668" s="4"/>
@@ -18615,7 +18656,7 @@
       <c r="X668" s="4"/>
     </row>
     <row r="669">
-      <c r="A669" s="37"/>
+      <c r="A669" s="35"/>
       <c r="B669" s="4"/>
       <c r="C669" s="4"/>
       <c r="D669" s="4"/>
@@ -18641,7 +18682,7 @@
       <c r="X669" s="4"/>
     </row>
     <row r="670">
-      <c r="A670" s="37"/>
+      <c r="A670" s="35"/>
       <c r="B670" s="4"/>
       <c r="C670" s="4"/>
       <c r="D670" s="4"/>
@@ -18667,7 +18708,7 @@
       <c r="X670" s="4"/>
     </row>
     <row r="671">
-      <c r="A671" s="37"/>
+      <c r="A671" s="35"/>
       <c r="B671" s="4"/>
       <c r="C671" s="4"/>
       <c r="D671" s="4"/>
@@ -18693,7 +18734,7 @@
       <c r="X671" s="4"/>
     </row>
     <row r="672">
-      <c r="A672" s="37"/>
+      <c r="A672" s="35"/>
       <c r="B672" s="4"/>
       <c r="C672" s="4"/>
       <c r="D672" s="4"/>
@@ -18719,7 +18760,7 @@
       <c r="X672" s="4"/>
     </row>
     <row r="673">
-      <c r="A673" s="37"/>
+      <c r="A673" s="35"/>
       <c r="B673" s="4"/>
       <c r="C673" s="4"/>
       <c r="D673" s="4"/>
@@ -18745,7 +18786,7 @@
       <c r="X673" s="4"/>
     </row>
     <row r="674">
-      <c r="A674" s="37"/>
+      <c r="A674" s="35"/>
       <c r="B674" s="4"/>
       <c r="C674" s="4"/>
       <c r="D674" s="4"/>
@@ -18771,7 +18812,7 @@
       <c r="X674" s="4"/>
     </row>
     <row r="675">
-      <c r="A675" s="37"/>
+      <c r="A675" s="35"/>
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
       <c r="D675" s="4"/>
@@ -18797,7 +18838,7 @@
       <c r="X675" s="4"/>
     </row>
     <row r="676">
-      <c r="A676" s="37"/>
+      <c r="A676" s="35"/>
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
       <c r="D676" s="4"/>
@@ -18823,7 +18864,7 @@
       <c r="X676" s="4"/>
     </row>
     <row r="677">
-      <c r="A677" s="37"/>
+      <c r="A677" s="35"/>
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
       <c r="D677" s="4"/>
@@ -18849,7 +18890,7 @@
       <c r="X677" s="4"/>
     </row>
     <row r="678">
-      <c r="A678" s="37"/>
+      <c r="A678" s="35"/>
       <c r="B678" s="4"/>
       <c r="C678" s="4"/>
       <c r="D678" s="4"/>
@@ -18875,7 +18916,7 @@
       <c r="X678" s="4"/>
     </row>
     <row r="679">
-      <c r="A679" s="37"/>
+      <c r="A679" s="35"/>
       <c r="B679" s="4"/>
       <c r="C679" s="4"/>
       <c r="D679" s="4"/>
@@ -18901,7 +18942,7 @@
       <c r="X679" s="4"/>
     </row>
     <row r="680">
-      <c r="A680" s="37"/>
+      <c r="A680" s="35"/>
       <c r="B680" s="4"/>
       <c r="C680" s="4"/>
       <c r="D680" s="4"/>
@@ -18927,7 +18968,7 @@
       <c r="X680" s="4"/>
     </row>
     <row r="681">
-      <c r="A681" s="37"/>
+      <c r="A681" s="35"/>
       <c r="B681" s="4"/>
       <c r="C681" s="4"/>
       <c r="D681" s="4"/>
@@ -18953,7 +18994,7 @@
       <c r="X681" s="4"/>
     </row>
     <row r="682">
-      <c r="A682" s="37"/>
+      <c r="A682" s="35"/>
       <c r="B682" s="4"/>
       <c r="C682" s="4"/>
       <c r="D682" s="4"/>
@@ -18979,7 +19020,7 @@
       <c r="X682" s="4"/>
     </row>
     <row r="683">
-      <c r="A683" s="37"/>
+      <c r="A683" s="35"/>
       <c r="B683" s="4"/>
       <c r="C683" s="4"/>
       <c r="D683" s="4"/>
@@ -19005,7 +19046,7 @@
       <c r="X683" s="4"/>
     </row>
     <row r="684">
-      <c r="A684" s="37"/>
+      <c r="A684" s="35"/>
       <c r="B684" s="4"/>
       <c r="C684" s="4"/>
       <c r="D684" s="4"/>
@@ -19031,7 +19072,7 @@
       <c r="X684" s="4"/>
     </row>
     <row r="685">
-      <c r="A685" s="37"/>
+      <c r="A685" s="35"/>
       <c r="B685" s="4"/>
       <c r="C685" s="4"/>
       <c r="D685" s="4"/>
@@ -19057,7 +19098,7 @@
       <c r="X685" s="4"/>
     </row>
     <row r="686">
-      <c r="A686" s="37"/>
+      <c r="A686" s="35"/>
       <c r="B686" s="4"/>
       <c r="C686" s="4"/>
       <c r="D686" s="4"/>
@@ -19083,7 +19124,7 @@
       <c r="X686" s="4"/>
     </row>
     <row r="687">
-      <c r="A687" s="37"/>
+      <c r="A687" s="35"/>
       <c r="B687" s="4"/>
       <c r="C687" s="4"/>
       <c r="D687" s="4"/>
@@ -19109,7 +19150,7 @@
       <c r="X687" s="4"/>
     </row>
     <row r="688">
-      <c r="A688" s="37"/>
+      <c r="A688" s="35"/>
       <c r="B688" s="4"/>
       <c r="C688" s="4"/>
       <c r="D688" s="4"/>
@@ -19135,7 +19176,7 @@
       <c r="X688" s="4"/>
     </row>
     <row r="689">
-      <c r="A689" s="37"/>
+      <c r="A689" s="35"/>
       <c r="B689" s="4"/>
       <c r="C689" s="4"/>
       <c r="D689" s="4"/>
@@ -19161,7 +19202,7 @@
       <c r="X689" s="4"/>
     </row>
     <row r="690">
-      <c r="A690" s="37"/>
+      <c r="A690" s="35"/>
       <c r="B690" s="4"/>
       <c r="C690" s="4"/>
       <c r="D690" s="4"/>
@@ -19187,7 +19228,7 @@
       <c r="X690" s="4"/>
     </row>
     <row r="691">
-      <c r="A691" s="37"/>
+      <c r="A691" s="35"/>
       <c r="B691" s="4"/>
       <c r="C691" s="4"/>
       <c r="D691" s="4"/>
@@ -19213,7 +19254,7 @@
       <c r="X691" s="4"/>
     </row>
     <row r="692">
-      <c r="A692" s="37"/>
+      <c r="A692" s="35"/>
       <c r="B692" s="4"/>
       <c r="C692" s="4"/>
       <c r="D692" s="4"/>
@@ -19239,7 +19280,7 @@
       <c r="X692" s="4"/>
     </row>
     <row r="693">
-      <c r="A693" s="37"/>
+      <c r="A693" s="35"/>
       <c r="B693" s="4"/>
       <c r="C693" s="4"/>
       <c r="D693" s="4"/>
@@ -19265,7 +19306,7 @@
       <c r="X693" s="4"/>
     </row>
     <row r="694">
-      <c r="A694" s="37"/>
+      <c r="A694" s="35"/>
       <c r="B694" s="4"/>
       <c r="C694" s="4"/>
       <c r="D694" s="4"/>
@@ -19291,7 +19332,7 @@
       <c r="X694" s="4"/>
     </row>
     <row r="695">
-      <c r="A695" s="37"/>
+      <c r="A695" s="35"/>
       <c r="B695" s="4"/>
       <c r="C695" s="4"/>
       <c r="D695" s="4"/>
@@ -19317,7 +19358,7 @@
       <c r="X695" s="4"/>
     </row>
     <row r="696">
-      <c r="A696" s="37"/>
+      <c r="A696" s="35"/>
       <c r="B696" s="4"/>
       <c r="C696" s="4"/>
       <c r="D696" s="4"/>
@@ -19343,7 +19384,7 @@
       <c r="X696" s="4"/>
     </row>
     <row r="697">
-      <c r="A697" s="37"/>
+      <c r="A697" s="35"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
       <c r="D697" s="4"/>
@@ -19369,7 +19410,7 @@
       <c r="X697" s="4"/>
     </row>
     <row r="698">
-      <c r="A698" s="37"/>
+      <c r="A698" s="35"/>
       <c r="B698" s="4"/>
       <c r="C698" s="4"/>
       <c r="D698" s="4"/>
@@ -19395,7 +19436,7 @@
       <c r="X698" s="4"/>
     </row>
     <row r="699">
-      <c r="A699" s="37"/>
+      <c r="A699" s="35"/>
       <c r="B699" s="4"/>
       <c r="C699" s="4"/>
       <c r="D699" s="4"/>
@@ -19421,7 +19462,7 @@
       <c r="X699" s="4"/>
     </row>
     <row r="700">
-      <c r="A700" s="37"/>
+      <c r="A700" s="35"/>
       <c r="B700" s="4"/>
       <c r="C700" s="4"/>
       <c r="D700" s="4"/>
@@ -19447,7 +19488,7 @@
       <c r="X700" s="4"/>
     </row>
     <row r="701">
-      <c r="A701" s="37"/>
+      <c r="A701" s="35"/>
       <c r="B701" s="4"/>
       <c r="C701" s="4"/>
       <c r="D701" s="4"/>
@@ -19473,7 +19514,7 @@
       <c r="X701" s="4"/>
     </row>
     <row r="702">
-      <c r="A702" s="37"/>
+      <c r="A702" s="35"/>
       <c r="B702" s="4"/>
       <c r="C702" s="4"/>
       <c r="D702" s="4"/>
@@ -19499,7 +19540,7 @@
       <c r="X702" s="4"/>
     </row>
     <row r="703">
-      <c r="A703" s="37"/>
+      <c r="A703" s="35"/>
       <c r="B703" s="4"/>
       <c r="C703" s="4"/>
       <c r="D703" s="4"/>
@@ -19525,7 +19566,7 @@
       <c r="X703" s="4"/>
     </row>
     <row r="704">
-      <c r="A704" s="37"/>
+      <c r="A704" s="35"/>
       <c r="B704" s="4"/>
       <c r="C704" s="4"/>
       <c r="D704" s="4"/>
@@ -19551,7 +19592,7 @@
       <c r="X704" s="4"/>
     </row>
     <row r="705">
-      <c r="A705" s="37"/>
+      <c r="A705" s="35"/>
       <c r="B705" s="4"/>
       <c r="C705" s="4"/>
       <c r="D705" s="4"/>
@@ -19577,7 +19618,7 @@
       <c r="X705" s="4"/>
     </row>
     <row r="706">
-      <c r="A706" s="37"/>
+      <c r="A706" s="35"/>
       <c r="B706" s="4"/>
       <c r="C706" s="4"/>
       <c r="D706" s="4"/>
@@ -19603,7 +19644,7 @@
       <c r="X706" s="4"/>
     </row>
     <row r="707">
-      <c r="A707" s="37"/>
+      <c r="A707" s="35"/>
       <c r="B707" s="4"/>
       <c r="C707" s="4"/>
       <c r="D707" s="4"/>
@@ -19629,7 +19670,7 @@
       <c r="X707" s="4"/>
     </row>
     <row r="708">
-      <c r="A708" s="37"/>
+      <c r="A708" s="35"/>
       <c r="B708" s="4"/>
       <c r="C708" s="4"/>
       <c r="D708" s="4"/>
@@ -19655,7 +19696,7 @@
       <c r="X708" s="4"/>
     </row>
     <row r="709">
-      <c r="A709" s="37"/>
+      <c r="A709" s="35"/>
       <c r="B709" s="4"/>
       <c r="C709" s="4"/>
       <c r="D709" s="4"/>
@@ -19681,7 +19722,7 @@
       <c r="X709" s="4"/>
     </row>
     <row r="710">
-      <c r="A710" s="37"/>
+      <c r="A710" s="35"/>
       <c r="B710" s="4"/>
       <c r="C710" s="4"/>
       <c r="D710" s="4"/>
@@ -19707,7 +19748,7 @@
       <c r="X710" s="4"/>
     </row>
     <row r="711">
-      <c r="A711" s="37"/>
+      <c r="A711" s="35"/>
       <c r="B711" s="4"/>
       <c r="C711" s="4"/>
       <c r="D711" s="4"/>
@@ -19733,7 +19774,7 @@
       <c r="X711" s="4"/>
     </row>
     <row r="712">
-      <c r="A712" s="37"/>
+      <c r="A712" s="35"/>
       <c r="B712" s="4"/>
       <c r="C712" s="4"/>
       <c r="D712" s="4"/>
@@ -19759,7 +19800,7 @@
       <c r="X712" s="4"/>
     </row>
     <row r="713">
-      <c r="A713" s="37"/>
+      <c r="A713" s="35"/>
       <c r="B713" s="4"/>
       <c r="C713" s="4"/>
       <c r="D713" s="4"/>
@@ -19785,7 +19826,7 @@
       <c r="X713" s="4"/>
     </row>
     <row r="714">
-      <c r="A714" s="37"/>
+      <c r="A714" s="35"/>
       <c r="B714" s="4"/>
       <c r="C714" s="4"/>
       <c r="D714" s="4"/>
@@ -19811,7 +19852,7 @@
       <c r="X714" s="4"/>
     </row>
     <row r="715">
-      <c r="A715" s="37"/>
+      <c r="A715" s="35"/>
       <c r="B715" s="4"/>
       <c r="C715" s="4"/>
       <c r="D715" s="4"/>
@@ -19837,7 +19878,7 @@
       <c r="X715" s="4"/>
     </row>
     <row r="716">
-      <c r="A716" s="37"/>
+      <c r="A716" s="35"/>
       <c r="B716" s="4"/>
       <c r="C716" s="4"/>
       <c r="D716" s="4"/>
@@ -19863,7 +19904,7 @@
       <c r="X716" s="4"/>
     </row>
     <row r="717">
-      <c r="A717" s="37"/>
+      <c r="A717" s="35"/>
       <c r="B717" s="4"/>
       <c r="C717" s="4"/>
       <c r="D717" s="4"/>
@@ -19889,7 +19930,7 @@
       <c r="X717" s="4"/>
     </row>
     <row r="718">
-      <c r="A718" s="37"/>
+      <c r="A718" s="35"/>
       <c r="B718" s="4"/>
       <c r="C718" s="4"/>
       <c r="D718" s="4"/>
@@ -19915,7 +19956,7 @@
       <c r="X718" s="4"/>
     </row>
     <row r="719">
-      <c r="A719" s="37"/>
+      <c r="A719" s="35"/>
       <c r="B719" s="4"/>
       <c r="C719" s="4"/>
       <c r="D719" s="4"/>
@@ -19941,7 +19982,7 @@
       <c r="X719" s="4"/>
     </row>
     <row r="720">
-      <c r="A720" s="37"/>
+      <c r="A720" s="35"/>
       <c r="B720" s="4"/>
       <c r="C720" s="4"/>
       <c r="D720" s="4"/>
@@ -19967,7 +20008,7 @@
       <c r="X720" s="4"/>
     </row>
     <row r="721">
-      <c r="A721" s="37"/>
+      <c r="A721" s="35"/>
       <c r="B721" s="4"/>
       <c r="C721" s="4"/>
       <c r="D721" s="4"/>
@@ -19993,7 +20034,7 @@
       <c r="X721" s="4"/>
     </row>
     <row r="722">
-      <c r="A722" s="37"/>
+      <c r="A722" s="35"/>
       <c r="B722" s="4"/>
       <c r="C722" s="4"/>
       <c r="D722" s="4"/>
@@ -20019,7 +20060,7 @@
       <c r="X722" s="4"/>
     </row>
     <row r="723">
-      <c r="A723" s="37"/>
+      <c r="A723" s="35"/>
       <c r="B723" s="4"/>
       <c r="C723" s="4"/>
       <c r="D723" s="4"/>
@@ -20045,7 +20086,7 @@
       <c r="X723" s="4"/>
     </row>
     <row r="724">
-      <c r="A724" s="37"/>
+      <c r="A724" s="35"/>
       <c r="B724" s="4"/>
       <c r="C724" s="4"/>
       <c r="D724" s="4"/>
@@ -20071,7 +20112,7 @@
       <c r="X724" s="4"/>
     </row>
     <row r="725">
-      <c r="A725" s="37"/>
+      <c r="A725" s="35"/>
       <c r="B725" s="4"/>
       <c r="C725" s="4"/>
       <c r="D725" s="4"/>
@@ -20097,7 +20138,7 @@
       <c r="X725" s="4"/>
     </row>
     <row r="726">
-      <c r="A726" s="37"/>
+      <c r="A726" s="35"/>
       <c r="B726" s="4"/>
       <c r="C726" s="4"/>
       <c r="D726" s="4"/>
@@ -20123,7 +20164,7 @@
       <c r="X726" s="4"/>
     </row>
     <row r="727">
-      <c r="A727" s="37"/>
+      <c r="A727" s="35"/>
       <c r="B727" s="4"/>
       <c r="C727" s="4"/>
       <c r="D727" s="4"/>
@@ -20149,7 +20190,7 @@
       <c r="X727" s="4"/>
     </row>
     <row r="728">
-      <c r="A728" s="37"/>
+      <c r="A728" s="35"/>
       <c r="B728" s="4"/>
       <c r="C728" s="4"/>
       <c r="D728" s="4"/>
@@ -20175,7 +20216,7 @@
       <c r="X728" s="4"/>
     </row>
     <row r="729">
-      <c r="A729" s="37"/>
+      <c r="A729" s="35"/>
       <c r="B729" s="4"/>
       <c r="C729" s="4"/>
       <c r="D729" s="4"/>
@@ -20201,7 +20242,7 @@
       <c r="X729" s="4"/>
     </row>
     <row r="730">
-      <c r="A730" s="37"/>
+      <c r="A730" s="35"/>
       <c r="B730" s="4"/>
       <c r="C730" s="4"/>
       <c r="D730" s="4"/>
@@ -20227,7 +20268,7 @@
       <c r="X730" s="4"/>
     </row>
     <row r="731">
-      <c r="A731" s="37"/>
+      <c r="A731" s="35"/>
       <c r="B731" s="4"/>
       <c r="C731" s="4"/>
       <c r="D731" s="4"/>
@@ -20253,7 +20294,7 @@
       <c r="X731" s="4"/>
     </row>
     <row r="732">
-      <c r="A732" s="37"/>
+      <c r="A732" s="35"/>
       <c r="B732" s="4"/>
       <c r="C732" s="4"/>
       <c r="D732" s="4"/>
@@ -20279,7 +20320,7 @@
       <c r="X732" s="4"/>
     </row>
     <row r="733">
-      <c r="A733" s="37"/>
+      <c r="A733" s="35"/>
       <c r="B733" s="4"/>
       <c r="C733" s="4"/>
       <c r="D733" s="4"/>
@@ -20305,7 +20346,7 @@
       <c r="X733" s="4"/>
     </row>
     <row r="734">
-      <c r="A734" s="37"/>
+      <c r="A734" s="35"/>
       <c r="B734" s="4"/>
       <c r="C734" s="4"/>
       <c r="D734" s="4"/>
@@ -20331,7 +20372,7 @@
       <c r="X734" s="4"/>
     </row>
     <row r="735">
-      <c r="A735" s="37"/>
+      <c r="A735" s="35"/>
       <c r="B735" s="4"/>
       <c r="C735" s="4"/>
       <c r="D735" s="4"/>
@@ -20357,7 +20398,7 @@
       <c r="X735" s="4"/>
     </row>
     <row r="736">
-      <c r="A736" s="37"/>
+      <c r="A736" s="35"/>
       <c r="B736" s="4"/>
       <c r="C736" s="4"/>
       <c r="D736" s="4"/>
@@ -20383,7 +20424,7 @@
       <c r="X736" s="4"/>
     </row>
     <row r="737">
-      <c r="A737" s="37"/>
+      <c r="A737" s="35"/>
       <c r="B737" s="4"/>
       <c r="C737" s="4"/>
       <c r="D737" s="4"/>
@@ -20409,7 +20450,7 @@
       <c r="X737" s="4"/>
     </row>
     <row r="738">
-      <c r="A738" s="37"/>
+      <c r="A738" s="35"/>
       <c r="B738" s="4"/>
       <c r="C738" s="4"/>
       <c r="D738" s="4"/>
@@ -20435,7 +20476,7 @@
       <c r="X738" s="4"/>
     </row>
     <row r="739">
-      <c r="A739" s="37"/>
+      <c r="A739" s="35"/>
       <c r="B739" s="4"/>
       <c r="C739" s="4"/>
       <c r="D739" s="4"/>
@@ -20461,7 +20502,7 @@
       <c r="X739" s="4"/>
     </row>
     <row r="740">
-      <c r="A740" s="37"/>
+      <c r="A740" s="35"/>
       <c r="B740" s="4"/>
       <c r="C740" s="4"/>
       <c r="D740" s="4"/>
@@ -20487,7 +20528,7 @@
       <c r="X740" s="4"/>
     </row>
     <row r="741">
-      <c r="A741" s="37"/>
+      <c r="A741" s="35"/>
       <c r="B741" s="4"/>
       <c r="C741" s="4"/>
       <c r="D741" s="4"/>
@@ -20513,7 +20554,7 @@
       <c r="X741" s="4"/>
     </row>
     <row r="742">
-      <c r="A742" s="37"/>
+      <c r="A742" s="35"/>
       <c r="B742" s="4"/>
       <c r="C742" s="4"/>
       <c r="D742" s="4"/>
@@ -20539,7 +20580,7 @@
       <c r="X742" s="4"/>
     </row>
     <row r="743">
-      <c r="A743" s="37"/>
+      <c r="A743" s="35"/>
       <c r="B743" s="4"/>
       <c r="C743" s="4"/>
       <c r="D743" s="4"/>
@@ -20565,7 +20606,7 @@
       <c r="X743" s="4"/>
     </row>
     <row r="744">
-      <c r="A744" s="37"/>
+      <c r="A744" s="35"/>
       <c r="B744" s="4"/>
       <c r="C744" s="4"/>
       <c r="D744" s="4"/>
@@ -20591,7 +20632,7 @@
       <c r="X744" s="4"/>
     </row>
     <row r="745">
-      <c r="A745" s="37"/>
+      <c r="A745" s="35"/>
       <c r="B745" s="4"/>
       <c r="C745" s="4"/>
       <c r="D745" s="4"/>
@@ -20617,7 +20658,7 @@
       <c r="X745" s="4"/>
     </row>
     <row r="746">
-      <c r="A746" s="37"/>
+      <c r="A746" s="35"/>
       <c r="B746" s="4"/>
       <c r="C746" s="4"/>
       <c r="D746" s="4"/>
@@ -20643,7 +20684,7 @@
       <c r="X746" s="4"/>
     </row>
     <row r="747">
-      <c r="A747" s="37"/>
+      <c r="A747" s="35"/>
       <c r="B747" s="4"/>
       <c r="C747" s="4"/>
       <c r="D747" s="4"/>
@@ -20669,7 +20710,7 @@
       <c r="X747" s="4"/>
     </row>
     <row r="748">
-      <c r="A748" s="37"/>
+      <c r="A748" s="35"/>
       <c r="B748" s="4"/>
       <c r="C748" s="4"/>
       <c r="D748" s="4"/>
@@ -20695,7 +20736,7 @@
       <c r="X748" s="4"/>
     </row>
     <row r="749">
-      <c r="A749" s="37"/>
+      <c r="A749" s="35"/>
       <c r="B749" s="4"/>
       <c r="C749" s="4"/>
       <c r="D749" s="4"/>
@@ -20721,7 +20762,7 @@
       <c r="X749" s="4"/>
     </row>
     <row r="750">
-      <c r="A750" s="37"/>
+      <c r="A750" s="35"/>
       <c r="B750" s="4"/>
       <c r="C750" s="4"/>
       <c r="D750" s="4"/>
@@ -20747,7 +20788,7 @@
       <c r="X750" s="4"/>
     </row>
     <row r="751">
-      <c r="A751" s="37"/>
+      <c r="A751" s="35"/>
       <c r="B751" s="4"/>
       <c r="C751" s="4"/>
       <c r="D751" s="4"/>
@@ -20773,7 +20814,7 @@
       <c r="X751" s="4"/>
     </row>
     <row r="752">
-      <c r="A752" s="37"/>
+      <c r="A752" s="35"/>
       <c r="B752" s="4"/>
       <c r="C752" s="4"/>
       <c r="D752" s="4"/>
@@ -20799,7 +20840,7 @@
       <c r="X752" s="4"/>
     </row>
     <row r="753">
-      <c r="A753" s="37"/>
+      <c r="A753" s="35"/>
       <c r="B753" s="4"/>
       <c r="C753" s="4"/>
       <c r="D753" s="4"/>
@@ -20825,7 +20866,7 @@
       <c r="X753" s="4"/>
     </row>
     <row r="754">
-      <c r="A754" s="37"/>
+      <c r="A754" s="35"/>
       <c r="B754" s="4"/>
       <c r="C754" s="4"/>
       <c r="D754" s="4"/>
@@ -20851,7 +20892,7 @@
       <c r="X754" s="4"/>
     </row>
     <row r="755">
-      <c r="A755" s="37"/>
+      <c r="A755" s="35"/>
       <c r="B755" s="4"/>
       <c r="C755" s="4"/>
       <c r="D755" s="4"/>
@@ -20877,7 +20918,7 @@
       <c r="X755" s="4"/>
     </row>
     <row r="756">
-      <c r="A756" s="37"/>
+      <c r="A756" s="35"/>
       <c r="B756" s="4"/>
       <c r="C756" s="4"/>
       <c r="D756" s="4"/>
@@ -20903,7 +20944,7 @@
       <c r="X756" s="4"/>
     </row>
     <row r="757">
-      <c r="A757" s="37"/>
+      <c r="A757" s="35"/>
       <c r="B757" s="4"/>
       <c r="C757" s="4"/>
       <c r="D757" s="4"/>
@@ -20929,7 +20970,7 @@
       <c r="X757" s="4"/>
     </row>
     <row r="758">
-      <c r="A758" s="37"/>
+      <c r="A758" s="35"/>
       <c r="B758" s="4"/>
       <c r="C758" s="4"/>
       <c r="D758" s="4"/>
@@ -20955,7 +20996,7 @@
       <c r="X758" s="4"/>
     </row>
     <row r="759">
-      <c r="A759" s="37"/>
+      <c r="A759" s="35"/>
       <c r="B759" s="4"/>
       <c r="C759" s="4"/>
       <c r="D759" s="4"/>
@@ -20981,7 +21022,7 @@
       <c r="X759" s="4"/>
     </row>
     <row r="760">
-      <c r="A760" s="37"/>
+      <c r="A760" s="35"/>
       <c r="B760" s="4"/>
       <c r="C760" s="4"/>
       <c r="D760" s="4"/>
@@ -21007,7 +21048,7 @@
       <c r="X760" s="4"/>
     </row>
     <row r="761">
-      <c r="A761" s="37"/>
+      <c r="A761" s="35"/>
       <c r="B761" s="4"/>
       <c r="C761" s="4"/>
       <c r="D761" s="4"/>
@@ -21033,7 +21074,7 @@
       <c r="X761" s="4"/>
     </row>
     <row r="762">
-      <c r="A762" s="37"/>
+      <c r="A762" s="35"/>
       <c r="B762" s="4"/>
       <c r="C762" s="4"/>
       <c r="D762" s="4"/>
@@ -21059,7 +21100,7 @@
       <c r="X762" s="4"/>
     </row>
     <row r="763">
-      <c r="A763" s="37"/>
+      <c r="A763" s="35"/>
       <c r="B763" s="4"/>
       <c r="C763" s="4"/>
       <c r="D763" s="4"/>
@@ -21085,7 +21126,7 @@
       <c r="X763" s="4"/>
     </row>
     <row r="764">
-      <c r="A764" s="37"/>
+      <c r="A764" s="35"/>
       <c r="B764" s="4"/>
       <c r="C764" s="4"/>
       <c r="D764" s="4"/>
@@ -21111,7 +21152,7 @@
       <c r="X764" s="4"/>
     </row>
     <row r="765">
-      <c r="A765" s="37"/>
+      <c r="A765" s="35"/>
       <c r="B765" s="4"/>
       <c r="C765" s="4"/>
       <c r="D765" s="4"/>
@@ -21137,7 +21178,7 @@
       <c r="X765" s="4"/>
     </row>
     <row r="766">
-      <c r="A766" s="37"/>
+      <c r="A766" s="35"/>
       <c r="B766" s="4"/>
       <c r="C766" s="4"/>
       <c r="D766" s="4"/>
@@ -21163,7 +21204,7 @@
       <c r="X766" s="4"/>
     </row>
     <row r="767">
-      <c r="A767" s="37"/>
+      <c r="A767" s="35"/>
       <c r="B767" s="4"/>
       <c r="C767" s="4"/>
       <c r="D767" s="4"/>
@@ -21189,7 +21230,7 @@
       <c r="X767" s="4"/>
     </row>
     <row r="768">
-      <c r="A768" s="37"/>
+      <c r="A768" s="35"/>
       <c r="B768" s="4"/>
       <c r="C768" s="4"/>
       <c r="D768" s="4"/>
@@ -21215,7 +21256,7 @@
       <c r="X768" s="4"/>
     </row>
     <row r="769">
-      <c r="A769" s="37"/>
+      <c r="A769" s="35"/>
       <c r="B769" s="4"/>
       <c r="C769" s="4"/>
       <c r="D769" s="4"/>
@@ -21241,7 +21282,7 @@
       <c r="X769" s="4"/>
     </row>
     <row r="770">
-      <c r="A770" s="37"/>
+      <c r="A770" s="35"/>
       <c r="B770" s="4"/>
       <c r="C770" s="4"/>
       <c r="D770" s="4"/>
@@ -21267,7 +21308,7 @@
       <c r="X770" s="4"/>
     </row>
     <row r="771">
-      <c r="A771" s="37"/>
+      <c r="A771" s="35"/>
       <c r="B771" s="4"/>
       <c r="C771" s="4"/>
       <c r="D771" s="4"/>
@@ -21293,7 +21334,7 @@
       <c r="X771" s="4"/>
     </row>
     <row r="772">
-      <c r="A772" s="37"/>
+      <c r="A772" s="35"/>
       <c r="B772" s="4"/>
       <c r="C772" s="4"/>
       <c r="D772" s="4"/>
@@ -21319,7 +21360,7 @@
       <c r="X772" s="4"/>
     </row>
     <row r="773">
-      <c r="A773" s="37"/>
+      <c r="A773" s="35"/>
       <c r="B773" s="4"/>
       <c r="C773" s="4"/>
       <c r="D773" s="4"/>
@@ -21345,7 +21386,7 @@
       <c r="X773" s="4"/>
     </row>
     <row r="774">
-      <c r="A774" s="37"/>
+      <c r="A774" s="35"/>
       <c r="B774" s="4"/>
       <c r="C774" s="4"/>
       <c r="D774" s="4"/>
@@ -21371,7 +21412,7 @@
       <c r="X774" s="4"/>
     </row>
     <row r="775">
-      <c r="A775" s="37"/>
+      <c r="A775" s="35"/>
       <c r="B775" s="4"/>
       <c r="C775" s="4"/>
       <c r="D775" s="4"/>
@@ -21397,7 +21438,7 @@
       <c r="X775" s="4"/>
     </row>
     <row r="776">
-      <c r="A776" s="37"/>
+      <c r="A776" s="35"/>
       <c r="B776" s="4"/>
       <c r="C776" s="4"/>
       <c r="D776" s="4"/>
@@ -21423,7 +21464,7 @@
       <c r="X776" s="4"/>
     </row>
     <row r="777">
-      <c r="A777" s="37"/>
+      <c r="A777" s="35"/>
       <c r="B777" s="4"/>
       <c r="C777" s="4"/>
       <c r="D777" s="4"/>
@@ -21449,7 +21490,7 @@
       <c r="X777" s="4"/>
     </row>
     <row r="778">
-      <c r="A778" s="37"/>
+      <c r="A778" s="35"/>
       <c r="B778" s="4"/>
       <c r="C778" s="4"/>
       <c r="D778" s="4"/>
@@ -21475,7 +21516,7 @@
       <c r="X778" s="4"/>
     </row>
     <row r="779">
-      <c r="A779" s="37"/>
+      <c r="A779" s="35"/>
       <c r="B779" s="4"/>
       <c r="C779" s="4"/>
       <c r="D779" s="4"/>
@@ -21501,7 +21542,7 @@
       <c r="X779" s="4"/>
     </row>
     <row r="780">
-      <c r="A780" s="37"/>
+      <c r="A780" s="35"/>
       <c r="B780" s="4"/>
       <c r="C780" s="4"/>
       <c r="D780" s="4"/>
@@ -21527,7 +21568,7 @@
       <c r="X780" s="4"/>
     </row>
     <row r="781">
-      <c r="A781" s="37"/>
+      <c r="A781" s="35"/>
       <c r="B781" s="4"/>
       <c r="C781" s="4"/>
       <c r="D781" s="4"/>
@@ -21553,7 +21594,7 @@
       <c r="X781" s="4"/>
     </row>
     <row r="782">
-      <c r="A782" s="37"/>
+      <c r="A782" s="35"/>
       <c r="B782" s="4"/>
       <c r="C782" s="4"/>
       <c r="D782" s="4"/>
@@ -21579,7 +21620,7 @@
       <c r="X782" s="4"/>
     </row>
     <row r="783">
-      <c r="A783" s="37"/>
+      <c r="A783" s="35"/>
       <c r="B783" s="4"/>
       <c r="C783" s="4"/>
       <c r="D783" s="4"/>
@@ -21605,7 +21646,7 @@
       <c r="X783" s="4"/>
     </row>
     <row r="784">
-      <c r="A784" s="37"/>
+      <c r="A784" s="35"/>
       <c r="B784" s="4"/>
       <c r="C784" s="4"/>
       <c r="D784" s="4"/>
@@ -21631,7 +21672,7 @@
       <c r="X784" s="4"/>
     </row>
     <row r="785">
-      <c r="A785" s="37"/>
+      <c r="A785" s="35"/>
       <c r="B785" s="4"/>
       <c r="C785" s="4"/>
       <c r="D785" s="4"/>
@@ -21657,7 +21698,7 @@
       <c r="X785" s="4"/>
     </row>
     <row r="786">
-      <c r="A786" s="37"/>
+      <c r="A786" s="35"/>
       <c r="B786" s="4"/>
       <c r="C786" s="4"/>
       <c r="D786" s="4"/>
@@ -21683,7 +21724,7 @@
       <c r="X786" s="4"/>
     </row>
     <row r="787">
-      <c r="A787" s="37"/>
+      <c r="A787" s="35"/>
       <c r="B787" s="4"/>
       <c r="C787" s="4"/>
       <c r="D787" s="4"/>
@@ -21709,7 +21750,7 @@
       <c r="X787" s="4"/>
     </row>
     <row r="788">
-      <c r="A788" s="37"/>
+      <c r="A788" s="35"/>
       <c r="B788" s="4"/>
       <c r="C788" s="4"/>
       <c r="D788" s="4"/>
@@ -21735,7 +21776,7 @@
       <c r="X788" s="4"/>
     </row>
     <row r="789">
-      <c r="A789" s="37"/>
+      <c r="A789" s="35"/>
       <c r="B789" s="4"/>
       <c r="C789" s="4"/>
       <c r="D789" s="4"/>
@@ -21761,7 +21802,7 @@
       <c r="X789" s="4"/>
     </row>
     <row r="790">
-      <c r="A790" s="37"/>
+      <c r="A790" s="35"/>
       <c r="B790" s="4"/>
       <c r="C790" s="4"/>
       <c r="D790" s="4"/>
@@ -21787,7 +21828,7 @@
       <c r="X790" s="4"/>
     </row>
     <row r="791">
-      <c r="A791" s="37"/>
+      <c r="A791" s="35"/>
       <c r="B791" s="4"/>
       <c r="C791" s="4"/>
       <c r="D791" s="4"/>
@@ -21813,7 +21854,7 @@
       <c r="X791" s="4"/>
     </row>
     <row r="792">
-      <c r="A792" s="37"/>
+      <c r="A792" s="35"/>
       <c r="B792" s="4"/>
       <c r="C792" s="4"/>
       <c r="D792" s="4"/>
@@ -21839,7 +21880,7 @@
       <c r="X792" s="4"/>
     </row>
     <row r="793">
-      <c r="A793" s="37"/>
+      <c r="A793" s="35"/>
       <c r="B793" s="4"/>
       <c r="C793" s="4"/>
       <c r="D793" s="4"/>
@@ -21865,7 +21906,7 @@
       <c r="X793" s="4"/>
     </row>
     <row r="794">
-      <c r="A794" s="37"/>
+      <c r="A794" s="35"/>
       <c r="B794" s="4"/>
       <c r="C794" s="4"/>
       <c r="D794" s="4"/>
@@ -21891,7 +21932,7 @@
       <c r="X794" s="4"/>
     </row>
     <row r="795">
-      <c r="A795" s="37"/>
+      <c r="A795" s="35"/>
       <c r="B795" s="4"/>
       <c r="C795" s="4"/>
       <c r="D795" s="4"/>
@@ -21917,7 +21958,7 @@
       <c r="X795" s="4"/>
     </row>
     <row r="796">
-      <c r="A796" s="37"/>
+      <c r="A796" s="35"/>
       <c r="B796" s="4"/>
       <c r="C796" s="4"/>
       <c r="D796" s="4"/>
@@ -21943,7 +21984,7 @@
       <c r="X796" s="4"/>
     </row>
     <row r="797">
-      <c r="A797" s="37"/>
+      <c r="A797" s="35"/>
       <c r="B797" s="4"/>
       <c r="C797" s="4"/>
       <c r="D797" s="4"/>
@@ -21969,7 +22010,7 @@
       <c r="X797" s="4"/>
     </row>
     <row r="798">
-      <c r="A798" s="37"/>
+      <c r="A798" s="35"/>
       <c r="B798" s="4"/>
       <c r="C798" s="4"/>
       <c r="D798" s="4"/>
@@ -21995,7 +22036,7 @@
       <c r="X798" s="4"/>
     </row>
     <row r="799">
-      <c r="A799" s="37"/>
+      <c r="A799" s="35"/>
       <c r="B799" s="4"/>
       <c r="C799" s="4"/>
       <c r="D799" s="4"/>
@@ -22021,7 +22062,7 @@
       <c r="X799" s="4"/>
     </row>
     <row r="800">
-      <c r="A800" s="37"/>
+      <c r="A800" s="35"/>
       <c r="B800" s="4"/>
       <c r="C800" s="4"/>
       <c r="D800" s="4"/>
@@ -22047,7 +22088,7 @@
       <c r="X800" s="4"/>
     </row>
     <row r="801">
-      <c r="A801" s="37"/>
+      <c r="A801" s="35"/>
       <c r="B801" s="4"/>
       <c r="C801" s="4"/>
       <c r="D801" s="4"/>
@@ -22073,7 +22114,7 @@
       <c r="X801" s="4"/>
     </row>
     <row r="802">
-      <c r="A802" s="37"/>
+      <c r="A802" s="35"/>
       <c r="B802" s="4"/>
       <c r="C802" s="4"/>
       <c r="D802" s="4"/>
@@ -22099,7 +22140,7 @@
       <c r="X802" s="4"/>
     </row>
     <row r="803">
-      <c r="A803" s="37"/>
+      <c r="A803" s="35"/>
       <c r="B803" s="4"/>
       <c r="C803" s="4"/>
       <c r="D803" s="4"/>
@@ -22125,7 +22166,7 @@
       <c r="X803" s="4"/>
     </row>
     <row r="804">
-      <c r="A804" s="37"/>
+      <c r="A804" s="35"/>
       <c r="B804" s="4"/>
       <c r="C804" s="4"/>
       <c r="D804" s="4"/>
@@ -22151,7 +22192,7 @@
       <c r="X804" s="4"/>
     </row>
     <row r="805">
-      <c r="A805" s="37"/>
+      <c r="A805" s="35"/>
       <c r="B805" s="4"/>
       <c r="C805" s="4"/>
       <c r="D805" s="4"/>
@@ -22177,7 +22218,7 @@
       <c r="X805" s="4"/>
     </row>
     <row r="806">
-      <c r="A806" s="37"/>
+      <c r="A806" s="35"/>
       <c r="B806" s="4"/>
       <c r="C806" s="4"/>
       <c r="D806" s="4"/>
@@ -22203,7 +22244,7 @@
       <c r="X806" s="4"/>
     </row>
     <row r="807">
-      <c r="A807" s="37"/>
+      <c r="A807" s="35"/>
       <c r="B807" s="4"/>
       <c r="C807" s="4"/>
       <c r="D807" s="4"/>
@@ -22229,7 +22270,7 @@
       <c r="X807" s="4"/>
     </row>
     <row r="808">
-      <c r="A808" s="37"/>
+      <c r="A808" s="35"/>
       <c r="B808" s="4"/>
       <c r="C808" s="4"/>
       <c r="D808" s="4"/>
@@ -22255,7 +22296,7 @@
       <c r="X808" s="4"/>
     </row>
     <row r="809">
-      <c r="A809" s="37"/>
+      <c r="A809" s="35"/>
       <c r="B809" s="4"/>
       <c r="C809" s="4"/>
       <c r="D809" s="4"/>
@@ -22281,7 +22322,7 @@
       <c r="X809" s="4"/>
     </row>
     <row r="810">
-      <c r="A810" s="37"/>
+      <c r="A810" s="35"/>
       <c r="B810" s="4"/>
       <c r="C810" s="4"/>
       <c r="D810" s="4"/>
@@ -22307,7 +22348,7 @@
       <c r="X810" s="4"/>
     </row>
     <row r="811">
-      <c r="A811" s="37"/>
+      <c r="A811" s="35"/>
       <c r="B811" s="4"/>
       <c r="C811" s="4"/>
       <c r="D811" s="4"/>
@@ -22333,7 +22374,7 @@
       <c r="X811" s="4"/>
     </row>
     <row r="812">
-      <c r="A812" s="37"/>
+      <c r="A812" s="35"/>
       <c r="B812" s="4"/>
       <c r="C812" s="4"/>
       <c r="D812" s="4"/>
@@ -22359,7 +22400,7 @@
       <c r="X812" s="4"/>
     </row>
     <row r="813">
-      <c r="A813" s="37"/>
+      <c r="A813" s="35"/>
       <c r="B813" s="4"/>
       <c r="C813" s="4"/>
       <c r="D813" s="4"/>
@@ -22385,7 +22426,7 @@
       <c r="X813" s="4"/>
     </row>
     <row r="814">
-      <c r="A814" s="37"/>
+      <c r="A814" s="35"/>
       <c r="B814" s="4"/>
       <c r="C814" s="4"/>
       <c r="D814" s="4"/>
@@ -22411,7 +22452,7 @@
       <c r="X814" s="4"/>
     </row>
     <row r="815">
-      <c r="A815" s="37"/>
+      <c r="A815" s="35"/>
       <c r="B815" s="4"/>
       <c r="C815" s="4"/>
       <c r="D815" s="4"/>
@@ -22437,7 +22478,7 @@
       <c r="X815" s="4"/>
     </row>
     <row r="816">
-      <c r="A816" s="37"/>
+      <c r="A816" s="35"/>
       <c r="B816" s="4"/>
       <c r="C816" s="4"/>
       <c r="D816" s="4"/>
@@ -22463,7 +22504,7 @@
       <c r="X816" s="4"/>
     </row>
     <row r="817">
-      <c r="A817" s="37"/>
+      <c r="A817" s="35"/>
       <c r="B817" s="4"/>
       <c r="C817" s="4"/>
       <c r="D817" s="4"/>
@@ -22489,7 +22530,7 @@
       <c r="X817" s="4"/>
     </row>
     <row r="818">
-      <c r="A818" s="37"/>
+      <c r="A818" s="35"/>
       <c r="B818" s="4"/>
       <c r="C818" s="4"/>
       <c r="D818" s="4"/>
@@ -22515,7 +22556,7 @@
       <c r="X818" s="4"/>
     </row>
     <row r="819">
-      <c r="A819" s="37"/>
+      <c r="A819" s="35"/>
       <c r="B819" s="4"/>
       <c r="C819" s="4"/>
       <c r="D819" s="4"/>
@@ -22541,7 +22582,7 @@
       <c r="X819" s="4"/>
     </row>
     <row r="820">
-      <c r="A820" s="37"/>
+      <c r="A820" s="35"/>
       <c r="B820" s="4"/>
       <c r="C820" s="4"/>
       <c r="D820" s="4"/>
@@ -22567,7 +22608,7 @@
       <c r="X820" s="4"/>
     </row>
     <row r="821">
-      <c r="A821" s="37"/>
+      <c r="A821" s="35"/>
       <c r="B821" s="4"/>
       <c r="C821" s="4"/>
       <c r="D821" s="4"/>
@@ -22593,7 +22634,7 @@
       <c r="X821" s="4"/>
     </row>
     <row r="822">
-      <c r="A822" s="37"/>
+      <c r="A822" s="35"/>
       <c r="B822" s="4"/>
       <c r="C822" s="4"/>
       <c r="D822" s="4"/>
@@ -22619,7 +22660,7 @@
       <c r="X822" s="4"/>
     </row>
     <row r="823">
-      <c r="A823" s="37"/>
+      <c r="A823" s="35"/>
       <c r="B823" s="4"/>
       <c r="C823" s="4"/>
       <c r="D823" s="4"/>
@@ -22645,7 +22686,7 @@
       <c r="X823" s="4"/>
     </row>
     <row r="824">
-      <c r="A824" s="37"/>
+      <c r="A824" s="35"/>
       <c r="B824" s="4"/>
       <c r="C824" s="4"/>
       <c r="D824" s="4"/>
@@ -22671,7 +22712,7 @@
       <c r="X824" s="4"/>
     </row>
     <row r="825">
-      <c r="A825" s="37"/>
+      <c r="A825" s="35"/>
       <c r="B825" s="4"/>
       <c r="C825" s="4"/>
       <c r="D825" s="4"/>
@@ -22697,7 +22738,7 @@
       <c r="X825" s="4"/>
     </row>
     <row r="826">
-      <c r="A826" s="37"/>
+      <c r="A826" s="35"/>
       <c r="B826" s="4"/>
       <c r="C826" s="4"/>
       <c r="D826" s="4"/>
@@ -22723,7 +22764,7 @@
       <c r="X826" s="4"/>
     </row>
     <row r="827">
-      <c r="A827" s="37"/>
+      <c r="A827" s="35"/>
       <c r="B827" s="4"/>
       <c r="C827" s="4"/>
       <c r="D827" s="4"/>
@@ -22749,7 +22790,7 @@
       <c r="X827" s="4"/>
     </row>
     <row r="828">
-      <c r="A828" s="37"/>
+      <c r="A828" s="35"/>
       <c r="B828" s="4"/>
       <c r="C828" s="4"/>
       <c r="D828" s="4"/>
@@ -22775,7 +22816,7 @@
       <c r="X828" s="4"/>
     </row>
     <row r="829">
-      <c r="A829" s="37"/>
+      <c r="A829" s="35"/>
       <c r="B829" s="4"/>
       <c r="C829" s="4"/>
       <c r="D829" s="4"/>
@@ -22801,7 +22842,7 @@
       <c r="X829" s="4"/>
     </row>
     <row r="830">
-      <c r="A830" s="37"/>
+      <c r="A830" s="35"/>
       <c r="B830" s="4"/>
       <c r="C830" s="4"/>
       <c r="D830" s="4"/>
@@ -22827,7 +22868,7 @@
       <c r="X830" s="4"/>
     </row>
     <row r="831">
-      <c r="A831" s="37"/>
+      <c r="A831" s="35"/>
       <c r="B831" s="4"/>
       <c r="C831" s="4"/>
       <c r="D831" s="4"/>
@@ -22853,7 +22894,7 @@
       <c r="X831" s="4"/>
     </row>
     <row r="832">
-      <c r="A832" s="37"/>
+      <c r="A832" s="35"/>
       <c r="B832" s="4"/>
       <c r="C832" s="4"/>
       <c r="D832" s="4"/>
@@ -22879,7 +22920,7 @@
       <c r="X832" s="4"/>
     </row>
     <row r="833">
-      <c r="A833" s="37"/>
+      <c r="A833" s="35"/>
       <c r="B833" s="4"/>
       <c r="C833" s="4"/>
       <c r="D833" s="4"/>
@@ -22905,7 +22946,7 @@
       <c r="X833" s="4"/>
     </row>
     <row r="834">
-      <c r="A834" s="37"/>
+      <c r="A834" s="35"/>
       <c r="B834" s="4"/>
       <c r="C834" s="4"/>
       <c r="D834" s="4"/>
@@ -22931,7 +22972,7 @@
       <c r="X834" s="4"/>
     </row>
     <row r="835">
-      <c r="A835" s="37"/>
+      <c r="A835" s="35"/>
       <c r="B835" s="4"/>
       <c r="C835" s="4"/>
       <c r="D835" s="4"/>
@@ -22957,7 +22998,7 @@
       <c r="X835" s="4"/>
     </row>
     <row r="836">
-      <c r="A836" s="37"/>
+      <c r="A836" s="35"/>
       <c r="B836" s="4"/>
       <c r="C836" s="4"/>
       <c r="D836" s="4"/>
@@ -22983,7 +23024,7 @@
       <c r="X836" s="4"/>
     </row>
     <row r="837">
-      <c r="A837" s="37"/>
+      <c r="A837" s="35"/>
       <c r="B837" s="4"/>
       <c r="C837" s="4"/>
       <c r="D837" s="4"/>
@@ -23009,7 +23050,7 @@
       <c r="X837" s="4"/>
     </row>
     <row r="838">
-      <c r="A838" s="37"/>
+      <c r="A838" s="35"/>
       <c r="B838" s="4"/>
       <c r="C838" s="4"/>
       <c r="D838" s="4"/>
@@ -23035,7 +23076,7 @@
       <c r="X838" s="4"/>
     </row>
     <row r="839">
-      <c r="A839" s="37"/>
+      <c r="A839" s="35"/>
       <c r="B839" s="4"/>
       <c r="C839" s="4"/>
       <c r="D839" s="4"/>
@@ -23061,7 +23102,7 @@
       <c r="X839" s="4"/>
     </row>
     <row r="840">
-      <c r="A840" s="37"/>
+      <c r="A840" s="35"/>
       <c r="B840" s="4"/>
       <c r="C840" s="4"/>
       <c r="D840" s="4"/>
@@ -23087,7 +23128,7 @@
       <c r="X840" s="4"/>
     </row>
     <row r="841">
-      <c r="A841" s="37"/>
+      <c r="A841" s="35"/>
       <c r="B841" s="4"/>
       <c r="C841" s="4"/>
       <c r="D841" s="4"/>
@@ -23113,7 +23154,7 @@
       <c r="X841" s="4"/>
     </row>
     <row r="842">
-      <c r="A842" s="37"/>
+      <c r="A842" s="35"/>
       <c r="B842" s="4"/>
       <c r="C842" s="4"/>
       <c r="D842" s="4"/>
@@ -23139,7 +23180,7 @@
       <c r="X842" s="4"/>
     </row>
     <row r="843">
-      <c r="A843" s="37"/>
+      <c r="A843" s="35"/>
       <c r="B843" s="4"/>
       <c r="C843" s="4"/>
       <c r="D843" s="4"/>
@@ -23165,7 +23206,7 @@
       <c r="X843" s="4"/>
     </row>
     <row r="844">
-      <c r="A844" s="37"/>
+      <c r="A844" s="35"/>
       <c r="B844" s="4"/>
       <c r="C844" s="4"/>
       <c r="D844" s="4"/>
@@ -23191,7 +23232,7 @@
       <c r="X844" s="4"/>
     </row>
     <row r="845">
-      <c r="A845" s="37"/>
+      <c r="A845" s="35"/>
       <c r="B845" s="4"/>
       <c r="C845" s="4"/>
       <c r="D845" s="4"/>
@@ -23217,7 +23258,7 @@
       <c r="X845" s="4"/>
     </row>
     <row r="846">
-      <c r="A846" s="37"/>
+      <c r="A846" s="35"/>
       <c r="B846" s="4"/>
       <c r="C846" s="4"/>
       <c r="D846" s="4"/>
@@ -23243,7 +23284,7 @@
       <c r="X846" s="4"/>
     </row>
     <row r="847">
-      <c r="A847" s="37"/>
+      <c r="A847" s="35"/>
       <c r="B847" s="4"/>
       <c r="C847" s="4"/>
       <c r="D847" s="4"/>
@@ -23269,7 +23310,7 @@
       <c r="X847" s="4"/>
     </row>
     <row r="848">
-      <c r="A848" s="37"/>
+      <c r="A848" s="35"/>
       <c r="B848" s="4"/>
       <c r="C848" s="4"/>
       <c r="D848" s="4"/>
@@ -23295,7 +23336,7 @@
       <c r="X848" s="4"/>
     </row>
     <row r="849">
-      <c r="A849" s="37"/>
+      <c r="A849" s="35"/>
       <c r="B849" s="4"/>
       <c r="C849" s="4"/>
       <c r="D849" s="4"/>
@@ -23321,7 +23362,7 @@
       <c r="X849" s="4"/>
     </row>
     <row r="850">
-      <c r="A850" s="37"/>
+      <c r="A850" s="35"/>
       <c r="B850" s="4"/>
       <c r="C850" s="4"/>
       <c r="D850" s="4"/>
@@ -23347,7 +23388,7 @@
       <c r="X850" s="4"/>
     </row>
     <row r="851">
-      <c r="A851" s="37"/>
+      <c r="A851" s="35"/>
       <c r="B851" s="4"/>
       <c r="C851" s="4"/>
       <c r="D851" s="4"/>
@@ -23373,7 +23414,7 @@
       <c r="X851" s="4"/>
     </row>
     <row r="852">
-      <c r="A852" s="37"/>
+      <c r="A852" s="35"/>
       <c r="B852" s="4"/>
       <c r="C852" s="4"/>
       <c r="D852" s="4"/>
@@ -23399,7 +23440,7 @@
       <c r="X852" s="4"/>
     </row>
     <row r="853">
-      <c r="A853" s="37"/>
+      <c r="A853" s="35"/>
       <c r="B853" s="4"/>
       <c r="C853" s="4"/>
       <c r="D853" s="4"/>
@@ -23425,7 +23466,7 @@
       <c r="X853" s="4"/>
     </row>
     <row r="854">
-      <c r="A854" s="37"/>
+      <c r="A854" s="35"/>
       <c r="B854" s="4"/>
       <c r="C854" s="4"/>
       <c r="D854" s="4"/>
@@ -23451,7 +23492,7 @@
       <c r="X854" s="4"/>
     </row>
     <row r="855">
-      <c r="A855" s="37"/>
+      <c r="A855" s="35"/>
       <c r="B855" s="4"/>
       <c r="C855" s="4"/>
       <c r="D855" s="4"/>
@@ -23477,7 +23518,7 @@
       <c r="X855" s="4"/>
     </row>
     <row r="856">
-      <c r="A856" s="37"/>
+      <c r="A856" s="35"/>
       <c r="B856" s="4"/>
       <c r="C856" s="4"/>
       <c r="D856" s="4"/>
@@ -23503,7 +23544,7 @@
       <c r="X856" s="4"/>
     </row>
     <row r="857">
-      <c r="A857" s="37"/>
+      <c r="A857" s="35"/>
       <c r="B857" s="4"/>
       <c r="C857" s="4"/>
       <c r="D857" s="4"/>
@@ -23529,7 +23570,7 @@
       <c r="X857" s="4"/>
     </row>
     <row r="858">
-      <c r="A858" s="37"/>
+      <c r="A858" s="35"/>
       <c r="B858" s="4"/>
       <c r="C858" s="4"/>
       <c r="D858" s="4"/>
@@ -23555,7 +23596,7 @@
       <c r="X858" s="4"/>
     </row>
     <row r="859">
-      <c r="A859" s="37"/>
+      <c r="A859" s="35"/>
       <c r="B859" s="4"/>
       <c r="C859" s="4"/>
       <c r="D859" s="4"/>
@@ -23581,7 +23622,7 @@
       <c r="X859" s="4"/>
     </row>
     <row r="860">
-      <c r="A860" s="37"/>
+      <c r="A860" s="35"/>
       <c r="B860" s="4"/>
       <c r="C860" s="4"/>
       <c r="D860" s="4"/>
@@ -23607,7 +23648,7 @@
       <c r="X860" s="4"/>
     </row>
     <row r="861">
-      <c r="A861" s="37"/>
+      <c r="A861" s="35"/>
       <c r="B861" s="4"/>
       <c r="C861" s="4"/>
       <c r="D861" s="4"/>
@@ -23633,7 +23674,7 @@
       <c r="X861" s="4"/>
     </row>
     <row r="862">
-      <c r="A862" s="37"/>
+      <c r="A862" s="35"/>
       <c r="B862" s="4"/>
       <c r="C862" s="4"/>
       <c r="D862" s="4"/>
@@ -23659,7 +23700,7 @@
       <c r="X862" s="4"/>
     </row>
     <row r="863">
-      <c r="A863" s="37"/>
+      <c r="A863" s="35"/>
       <c r="B863" s="4"/>
       <c r="C863" s="4"/>
       <c r="D863" s="4"/>
@@ -23685,7 +23726,7 @@
       <c r="X863" s="4"/>
     </row>
     <row r="864">
-      <c r="A864" s="37"/>
+      <c r="A864" s="35"/>
       <c r="B864" s="4"/>
       <c r="C864" s="4"/>
       <c r="D864" s="4"/>
@@ -23711,7 +23752,7 @@
       <c r="X864" s="4"/>
     </row>
     <row r="865">
-      <c r="A865" s="37"/>
+      <c r="A865" s="35"/>
       <c r="B865" s="4"/>
       <c r="C865" s="4"/>
       <c r="D865" s="4"/>
@@ -23737,7 +23778,7 @@
       <c r="X865" s="4"/>
     </row>
     <row r="866">
-      <c r="A866" s="37"/>
+      <c r="A866" s="35"/>
       <c r="B866" s="4"/>
       <c r="C866" s="4"/>
       <c r="D866" s="4"/>
@@ -23763,7 +23804,7 @@
       <c r="X866" s="4"/>
     </row>
     <row r="867">
-      <c r="A867" s="37"/>
+      <c r="A867" s="35"/>
       <c r="B867" s="4"/>
       <c r="C867" s="4"/>
       <c r="D867" s="4"/>
@@ -23789,7 +23830,7 @@
       <c r="X867" s="4"/>
     </row>
     <row r="868">
-      <c r="A868" s="37"/>
+      <c r="A868" s="35"/>
       <c r="B868" s="4"/>
       <c r="C868" s="4"/>
       <c r="D868" s="4"/>
@@ -23815,7 +23856,7 @@
       <c r="X868" s="4"/>
     </row>
     <row r="869">
-      <c r="A869" s="37"/>
+      <c r="A869" s="35"/>
       <c r="B869" s="4"/>
       <c r="C869" s="4"/>
       <c r="D869" s="4"/>
@@ -23841,7 +23882,7 @@
       <c r="X869" s="4"/>
     </row>
     <row r="870">
-      <c r="A870" s="37"/>
+      <c r="A870" s="35"/>
       <c r="B870" s="4"/>
       <c r="C870" s="4"/>
       <c r="D870" s="4"/>
@@ -23867,7 +23908,7 @@
       <c r="X870" s="4"/>
     </row>
     <row r="871">
-      <c r="A871" s="37"/>
+      <c r="A871" s="35"/>
       <c r="B871" s="4"/>
       <c r="C871" s="4"/>
       <c r="D871" s="4"/>
@@ -23893,7 +23934,7 @@
       <c r="X871" s="4"/>
     </row>
     <row r="872">
-      <c r="A872" s="37"/>
+      <c r="A872" s="35"/>
       <c r="B872" s="4"/>
       <c r="C872" s="4"/>
       <c r="D872" s="4"/>
@@ -23919,7 +23960,7 @@
       <c r="X872" s="4"/>
     </row>
     <row r="873">
-      <c r="A873" s="37"/>
+      <c r="A873" s="35"/>
       <c r="B873" s="4"/>
       <c r="C873" s="4"/>
       <c r="D873" s="4"/>
@@ -23945,7 +23986,7 @@
       <c r="X873" s="4"/>
     </row>
     <row r="874">
-      <c r="A874" s="37"/>
+      <c r="A874" s="35"/>
       <c r="B874" s="4"/>
       <c r="C874" s="4"/>
       <c r="D874" s="4"/>
@@ -23971,7 +24012,7 @@
       <c r="X874" s="4"/>
     </row>
     <row r="875">
-      <c r="A875" s="37"/>
+      <c r="A875" s="35"/>
       <c r="B875" s="4"/>
       <c r="C875" s="4"/>
       <c r="D875" s="4"/>
@@ -23997,7 +24038,7 @@
       <c r="X875" s="4"/>
     </row>
     <row r="876">
-      <c r="A876" s="37"/>
+      <c r="A876" s="35"/>
       <c r="B876" s="4"/>
       <c r="C876" s="4"/>
       <c r="D876" s="4"/>
@@ -24023,7 +24064,7 @@
       <c r="X876" s="4"/>
     </row>
     <row r="877">
-      <c r="A877" s="37"/>
+      <c r="A877" s="35"/>
       <c r="B877" s="4"/>
       <c r="C877" s="4"/>
       <c r="D877" s="4"/>
@@ -24049,7 +24090,7 @@
       <c r="X877" s="4"/>
     </row>
     <row r="878">
-      <c r="A878" s="37"/>
+      <c r="A878" s="35"/>
       <c r="B878" s="4"/>
       <c r="C878" s="4"/>
       <c r="D878" s="4"/>
@@ -24075,7 +24116,7 @@
       <c r="X878" s="4"/>
     </row>
     <row r="879">
-      <c r="A879" s="37"/>
+      <c r="A879" s="35"/>
       <c r="B879" s="4"/>
       <c r="C879" s="4"/>
       <c r="D879" s="4"/>
@@ -24101,7 +24142,7 @@
       <c r="X879" s="4"/>
     </row>
     <row r="880">
-      <c r="A880" s="37"/>
+      <c r="A880" s="35"/>
       <c r="B880" s="4"/>
       <c r="C880" s="4"/>
       <c r="D880" s="4"/>
@@ -24127,7 +24168,7 @@
       <c r="X880" s="4"/>
     </row>
     <row r="881">
-      <c r="A881" s="37"/>
+      <c r="A881" s="35"/>
       <c r="B881" s="4"/>
       <c r="C881" s="4"/>
       <c r="D881" s="4"/>
@@ -24153,7 +24194,7 @@
       <c r="X881" s="4"/>
     </row>
     <row r="882">
-      <c r="A882" s="37"/>
+      <c r="A882" s="35"/>
       <c r="B882" s="4"/>
       <c r="C882" s="4"/>
       <c r="D882" s="4"/>
@@ -24179,7 +24220,7 @@
       <c r="X882" s="4"/>
     </row>
     <row r="883">
-      <c r="A883" s="37"/>
+      <c r="A883" s="35"/>
       <c r="B883" s="4"/>
       <c r="C883" s="4"/>
       <c r="D883" s="4"/>
@@ -24205,7 +24246,7 @@
       <c r="X883" s="4"/>
     </row>
     <row r="884">
-      <c r="A884" s="37"/>
+      <c r="A884" s="35"/>
       <c r="B884" s="4"/>
       <c r="C884" s="4"/>
       <c r="D884" s="4"/>
@@ -24231,7 +24272,7 @@
       <c r="X884" s="4"/>
     </row>
     <row r="885">
-      <c r="A885" s="37"/>
+      <c r="A885" s="35"/>
       <c r="B885" s="4"/>
       <c r="C885" s="4"/>
       <c r="D885" s="4"/>
@@ -24257,7 +24298,7 @@
       <c r="X885" s="4"/>
     </row>
     <row r="886">
-      <c r="A886" s="37"/>
+      <c r="A886" s="35"/>
       <c r="B886" s="4"/>
       <c r="C886" s="4"/>
       <c r="D886" s="4"/>
@@ -24283,7 +24324,7 @@
       <c r="X886" s="4"/>
     </row>
     <row r="887">
-      <c r="A887" s="37"/>
+      <c r="A887" s="35"/>
       <c r="B887" s="4"/>
       <c r="C887" s="4"/>
       <c r="D887" s="4"/>
@@ -24309,7 +24350,7 @@
       <c r="X887" s="4"/>
     </row>
     <row r="888">
-      <c r="A888" s="37"/>
+      <c r="A888" s="35"/>
       <c r="B888" s="4"/>
       <c r="C888" s="4"/>
       <c r="D888" s="4"/>
@@ -24335,7 +24376,7 @@
       <c r="X888" s="4"/>
     </row>
     <row r="889">
-      <c r="A889" s="37"/>
+      <c r="A889" s="35"/>
       <c r="B889" s="4"/>
       <c r="C889" s="4"/>
       <c r="D889" s="4"/>
@@ -24361,7 +24402,7 @@
       <c r="X889" s="4"/>
     </row>
     <row r="890">
-      <c r="A890" s="37"/>
+      <c r="A890" s="35"/>
       <c r="B890" s="4"/>
       <c r="C890" s="4"/>
       <c r="D890" s="4"/>
@@ -24387,7 +24428,7 @@
       <c r="X890" s="4"/>
     </row>
     <row r="891">
-      <c r="A891" s="37"/>
+      <c r="A891" s="35"/>
       <c r="B891" s="4"/>
       <c r="C891" s="4"/>
       <c r="D891" s="4"/>
@@ -24413,7 +24454,7 @@
       <c r="X891" s="4"/>
     </row>
     <row r="892">
-      <c r="A892" s="37"/>
+      <c r="A892" s="35"/>
       <c r="B892" s="4"/>
       <c r="C892" s="4"/>
       <c r="D892" s="4"/>
@@ -24439,7 +24480,7 @@
       <c r="X892" s="4"/>
     </row>
     <row r="893">
-      <c r="A893" s="37"/>
+      <c r="A893" s="35"/>
       <c r="B893" s="4"/>
       <c r="C893" s="4"/>
       <c r="D893" s="4"/>
@@ -24465,7 +24506,7 @@
       <c r="X893" s="4"/>
     </row>
     <row r="894">
-      <c r="A894" s="37"/>
+      <c r="A894" s="35"/>
       <c r="B894" s="4"/>
       <c r="C894" s="4"/>
       <c r="D894" s="4"/>
@@ -24491,7 +24532,7 @@
       <c r="X894" s="4"/>
     </row>
     <row r="895">
-      <c r="A895" s="37"/>
+      <c r="A895" s="35"/>
       <c r="B895" s="4"/>
       <c r="C895" s="4"/>
       <c r="D895" s="4"/>
@@ -24517,7 +24558,7 @@
       <c r="X895" s="4"/>
     </row>
     <row r="896">
-      <c r="A896" s="37"/>
+      <c r="A896" s="35"/>
       <c r="B896" s="4"/>
       <c r="C896" s="4"/>
       <c r="D896" s="4"/>
@@ -24543,7 +24584,7 @@
       <c r="X896" s="4"/>
     </row>
     <row r="897">
-      <c r="A897" s="37"/>
+      <c r="A897" s="35"/>
       <c r="B897" s="4"/>
       <c r="C897" s="4"/>
       <c r="D897" s="4"/>
@@ -24569,7 +24610,7 @@
       <c r="X897" s="4"/>
     </row>
     <row r="898">
-      <c r="A898" s="37"/>
+      <c r="A898" s="35"/>
       <c r="B898" s="4"/>
       <c r="C898" s="4"/>
       <c r="D898" s="4"/>
@@ -24595,7 +24636,7 @@
       <c r="X898" s="4"/>
     </row>
     <row r="899">
-      <c r="A899" s="37"/>
+      <c r="A899" s="35"/>
       <c r="B899" s="4"/>
       <c r="C899" s="4"/>
       <c r="D899" s="4"/>
@@ -24621,7 +24662,7 @@
       <c r="X899" s="4"/>
     </row>
     <row r="900">
-      <c r="A900" s="37"/>
+      <c r="A900" s="35"/>
       <c r="B900" s="4"/>
       <c r="C900" s="4"/>
       <c r="D900" s="4"/>
@@ -24647,7 +24688,7 @@
       <c r="X900" s="4"/>
     </row>
     <row r="901">
-      <c r="A901" s="37"/>
+      <c r="A901" s="35"/>
       <c r="B901" s="4"/>
       <c r="C901" s="4"/>
       <c r="D901" s="4"/>
@@ -24673,7 +24714,7 @@
       <c r="X901" s="4"/>
     </row>
     <row r="902">
-      <c r="A902" s="37"/>
+      <c r="A902" s="35"/>
       <c r="B902" s="4"/>
       <c r="C902" s="4"/>
       <c r="D902" s="4"/>
@@ -24699,7 +24740,7 @@
       <c r="X902" s="4"/>
     </row>
     <row r="903">
-      <c r="A903" s="37"/>
+      <c r="A903" s="35"/>
       <c r="B903" s="4"/>
       <c r="C903" s="4"/>
       <c r="D903" s="4"/>
@@ -24725,7 +24766,7 @@
       <c r="X903" s="4"/>
     </row>
     <row r="904">
-      <c r="A904" s="37"/>
+      <c r="A904" s="35"/>
       <c r="B904" s="4"/>
       <c r="C904" s="4"/>
       <c r="D904" s="4"/>
@@ -24751,7 +24792,7 @@
       <c r="X904" s="4"/>
     </row>
     <row r="905">
-      <c r="A905" s="37"/>
+      <c r="A905" s="35"/>
       <c r="B905" s="4"/>
       <c r="C905" s="4"/>
       <c r="D905" s="4"/>
@@ -24777,7 +24818,7 @@
       <c r="X905" s="4"/>
     </row>
     <row r="906">
-      <c r="A906" s="37"/>
+      <c r="A906" s="35"/>
       <c r="B906" s="4"/>
       <c r="C906" s="4"/>
       <c r="D906" s="4"/>
@@ -24803,7 +24844,7 @@
       <c r="X906" s="4"/>
     </row>
     <row r="907">
-      <c r="A907" s="37"/>
+      <c r="A907" s="35"/>
       <c r="B907" s="4"/>
       <c r="C907" s="4"/>
       <c r="D907" s="4"/>
@@ -24829,7 +24870,7 @@
       <c r="X907" s="4"/>
     </row>
     <row r="908">
-      <c r="A908" s="37"/>
+      <c r="A908" s="35"/>
       <c r="B908" s="4"/>
       <c r="C908" s="4"/>
       <c r="D908" s="4"/>
@@ -24855,7 +24896,7 @@
       <c r="X908" s="4"/>
     </row>
     <row r="909">
-      <c r="A909" s="37"/>
+      <c r="A909" s="35"/>
       <c r="B909" s="4"/>
       <c r="C909" s="4"/>
       <c r="D909" s="4"/>
@@ -24881,7 +24922,7 @@
       <c r="X909" s="4"/>
     </row>
     <row r="910">
-      <c r="A910" s="37"/>
+      <c r="A910" s="35"/>
       <c r="B910" s="4"/>
       <c r="C910" s="4"/>
       <c r="D910" s="4"/>
@@ -24907,7 +24948,7 @@
       <c r="X910" s="4"/>
     </row>
     <row r="911">
-      <c r="A911" s="37"/>
+      <c r="A911" s="35"/>
       <c r="B911" s="4"/>
       <c r="C911" s="4"/>
       <c r="D911" s="4"/>
@@ -24933,7 +24974,7 @@
       <c r="X911" s="4"/>
     </row>
     <row r="912">
-      <c r="A912" s="37"/>
+      <c r="A912" s="35"/>
       <c r="B912" s="4"/>
       <c r="C912" s="4"/>
       <c r="D912" s="4"/>
@@ -24959,7 +25000,7 @@
       <c r="X912" s="4"/>
     </row>
     <row r="913">
-      <c r="A913" s="37"/>
+      <c r="A913" s="35"/>
       <c r="B913" s="4"/>
       <c r="C913" s="4"/>
       <c r="D913" s="4"/>
@@ -24985,7 +25026,7 @@
       <c r="X913" s="4"/>
     </row>
     <row r="914">
-      <c r="A914" s="37"/>
+      <c r="A914" s="35"/>
       <c r="B914" s="4"/>
       <c r="C914" s="4"/>
       <c r="D914" s="4"/>
@@ -25011,7 +25052,7 @@
       <c r="X914" s="4"/>
     </row>
     <row r="915">
-      <c r="A915" s="37"/>
+      <c r="A915" s="35"/>
       <c r="B915" s="4"/>
       <c r="C915" s="4"/>
       <c r="D915" s="4"/>
@@ -25037,7 +25078,7 @@
       <c r="X915" s="4"/>
     </row>
     <row r="916">
-      <c r="A916" s="37"/>
+      <c r="A916" s="35"/>
       <c r="B916" s="4"/>
       <c r="C916" s="4"/>
       <c r="D916" s="4"/>
@@ -25063,7 +25104,7 @@
       <c r="X916" s="4"/>
     </row>
     <row r="917">
-      <c r="A917" s="37"/>
+      <c r="A917" s="35"/>
       <c r="B917" s="4"/>
       <c r="C917" s="4"/>
       <c r="D917" s="4"/>
@@ -25089,7 +25130,7 @@
       <c r="X917" s="4"/>
     </row>
     <row r="918">
-      <c r="A918" s="37"/>
+      <c r="A918" s="35"/>
       <c r="B918" s="4"/>
       <c r="C918" s="4"/>
       <c r="D918" s="4"/>
@@ -25115,7 +25156,7 @@
       <c r="X918" s="4"/>
     </row>
     <row r="919">
-      <c r="A919" s="37"/>
+      <c r="A919" s="35"/>
       <c r="B919" s="4"/>
       <c r="C919" s="4"/>
       <c r="D919" s="4"/>
@@ -25141,7 +25182,7 @@
       <c r="X919" s="4"/>
     </row>
     <row r="920">
-      <c r="A920" s="37"/>
+      <c r="A920" s="35"/>
       <c r="B920" s="4"/>
       <c r="C920" s="4"/>
       <c r="D920" s="4"/>
@@ -25167,7 +25208,7 @@
       <c r="X920" s="4"/>
     </row>
     <row r="921">
-      <c r="A921" s="37"/>
+      <c r="A921" s="35"/>
       <c r="B921" s="4"/>
       <c r="C921" s="4"/>
       <c r="D921" s="4"/>
@@ -25193,7 +25234,7 @@
       <c r="X921" s="4"/>
     </row>
     <row r="922">
-      <c r="A922" s="37"/>
+      <c r="A922" s="35"/>
       <c r="B922" s="4"/>
       <c r="C922" s="4"/>
       <c r="D922" s="4"/>
@@ -25219,7 +25260,7 @@
       <c r="X922" s="4"/>
     </row>
     <row r="923">
-      <c r="A923" s="37"/>
+      <c r="A923" s="35"/>
       <c r="B923" s="4"/>
       <c r="C923" s="4"/>
       <c r="D923" s="4"/>
@@ -25245,7 +25286,7 @@
       <c r="X923" s="4"/>
     </row>
     <row r="924">
-      <c r="A924" s="37"/>
+      <c r="A924" s="35"/>
       <c r="B924" s="4"/>
       <c r="C924" s="4"/>
       <c r="D924" s="4"/>
@@ -25271,7 +25312,7 @@
       <c r="X924" s="4"/>
     </row>
     <row r="925">
-      <c r="A925" s="37"/>
+      <c r="A925" s="35"/>
       <c r="B925" s="4"/>
       <c r="C925" s="4"/>
       <c r="D925" s="4"/>
@@ -25297,7 +25338,7 @@
       <c r="X925" s="4"/>
     </row>
     <row r="926">
-      <c r="A926" s="37"/>
+      <c r="A926" s="35"/>
       <c r="B926" s="4"/>
       <c r="C926" s="4"/>
       <c r="D926" s="4"/>
@@ -25323,7 +25364,7 @@
       <c r="X926" s="4"/>
     </row>
     <row r="927">
-      <c r="A927" s="37"/>
+      <c r="A927" s="35"/>
       <c r="B927" s="4"/>
       <c r="C927" s="4"/>
       <c r="D927" s="4"/>
@@ -25349,7 +25390,7 @@
       <c r="X927" s="4"/>
     </row>
     <row r="928">
-      <c r="A928" s="37"/>
+      <c r="A928" s="35"/>
       <c r="B928" s="4"/>
       <c r="C928" s="4"/>
       <c r="D928" s="4"/>
@@ -25375,7 +25416,7 @@
       <c r="X928" s="4"/>
     </row>
     <row r="929">
-      <c r="A929" s="37"/>
+      <c r="A929" s="35"/>
       <c r="B929" s="4"/>
       <c r="C929" s="4"/>
       <c r="D929" s="4"/>
@@ -25401,7 +25442,7 @@
       <c r="X929" s="4"/>
     </row>
     <row r="930">
-      <c r="A930" s="37"/>
+      <c r="A930" s="35"/>
       <c r="B930" s="4"/>
       <c r="C930" s="4"/>
       <c r="D930" s="4"/>
@@ -25427,7 +25468,7 @@
       <c r="X930" s="4"/>
     </row>
     <row r="931">
-      <c r="A931" s="37"/>
+      <c r="A931" s="35"/>
       <c r="B931" s="4"/>
       <c r="C931" s="4"/>
       <c r="D931" s="4"/>
@@ -25453,7 +25494,7 @@
       <c r="X931" s="4"/>
     </row>
     <row r="932">
-      <c r="A932" s="37"/>
+      <c r="A932" s="35"/>
       <c r="B932" s="4"/>
       <c r="C932" s="4"/>
       <c r="D932" s="4"/>
@@ -25479,7 +25520,7 @@
       <c r="X932" s="4"/>
     </row>
     <row r="933">
-      <c r="A933" s="37"/>
+      <c r="A933" s="35"/>
       <c r="B933" s="4"/>
       <c r="C933" s="4"/>
       <c r="D933" s="4"/>
@@ -25505,7 +25546,7 @@
       <c r="X933" s="4"/>
     </row>
     <row r="934">
-      <c r="A934" s="37"/>
+      <c r="A934" s="35"/>
       <c r="B934" s="4"/>
       <c r="C934" s="4"/>
       <c r="D934" s="4"/>
@@ -25531,7 +25572,7 @@
       <c r="X934" s="4"/>
     </row>
     <row r="935">
-      <c r="A935" s="37"/>
+      <c r="A935" s="35"/>
       <c r="B935" s="4"/>
       <c r="C935" s="4"/>
       <c r="D935" s="4"/>
@@ -25557,7 +25598,7 @@
       <c r="X935" s="4"/>
     </row>
     <row r="936">
-      <c r="A936" s="37"/>
+      <c r="A936" s="35"/>
       <c r="B936" s="4"/>
       <c r="C936" s="4"/>
       <c r="D936" s="4"/>
@@ -25583,7 +25624,7 @@
       <c r="X936" s="4"/>
     </row>
     <row r="937">
-      <c r="A937" s="37"/>
+      <c r="A937" s="35"/>
       <c r="B937" s="4"/>
       <c r="C937" s="4"/>
       <c r="D937" s="4"/>
@@ -25609,7 +25650,7 @@
       <c r="X937" s="4"/>
     </row>
     <row r="938">
-      <c r="A938" s="37"/>
+      <c r="A938" s="35"/>
       <c r="B938" s="4"/>
       <c r="C938" s="4"/>
       <c r="D938" s="4"/>
@@ -25635,7 +25676,7 @@
       <c r="X938" s="4"/>
     </row>
     <row r="939">
-      <c r="A939" s="37"/>
+      <c r="A939" s="35"/>
       <c r="B939" s="4"/>
       <c r="C939" s="4"/>
       <c r="D939" s="4"/>
@@ -25661,7 +25702,7 @@
       <c r="X939" s="4"/>
     </row>
     <row r="940">
-      <c r="A940" s="37"/>
+      <c r="A940" s="35"/>
       <c r="B940" s="4"/>
       <c r="C940" s="4"/>
       <c r="D940" s="4"/>
@@ -25687,7 +25728,7 @@
       <c r="X940" s="4"/>
     </row>
     <row r="941">
-      <c r="A941" s="37"/>
+      <c r="A941" s="35"/>
       <c r="B941" s="4"/>
       <c r="C941" s="4"/>
       <c r="D941" s="4"/>
@@ -25713,7 +25754,7 @@
       <c r="X941" s="4"/>
     </row>
     <row r="942">
-      <c r="A942" s="37"/>
+      <c r="A942" s="35"/>
       <c r="B942" s="4"/>
       <c r="C942" s="4"/>
       <c r="D942" s="4"/>
@@ -25739,7 +25780,7 @@
       <c r="X942" s="4"/>
     </row>
     <row r="943">
-      <c r="A943" s="37"/>
+      <c r="A943" s="35"/>
       <c r="B943" s="4"/>
       <c r="C943" s="4"/>
       <c r="D943" s="4"/>
@@ -25765,7 +25806,7 @@
       <c r="X943" s="4"/>
     </row>
     <row r="944">
-      <c r="A944" s="37"/>
+      <c r="A944" s="35"/>
       <c r="B944" s="4"/>
       <c r="C944" s="4"/>
       <c r="D944" s="4"/>
@@ -25791,7 +25832,7 @@
       <c r="X944" s="4"/>
     </row>
     <row r="945">
-      <c r="A945" s="37"/>
+      <c r="A945" s="35"/>
       <c r="B945" s="4"/>
       <c r="C945" s="4"/>
       <c r="D945" s="4"/>
@@ -25817,7 +25858,7 @@
       <c r="X945" s="4"/>
     </row>
     <row r="946">
-      <c r="A946" s="37"/>
+      <c r="A946" s="35"/>
       <c r="B946" s="4"/>
       <c r="C946" s="4"/>
       <c r="D946" s="4"/>
@@ -25843,7 +25884,7 @@
       <c r="X946" s="4"/>
     </row>
     <row r="947">
-      <c r="A947" s="37"/>
+      <c r="A947" s="35"/>
       <c r="B947" s="4"/>
       <c r="C947" s="4"/>
       <c r="D947" s="4"/>
@@ -25869,7 +25910,7 @@
       <c r="X947" s="4"/>
     </row>
     <row r="948">
-      <c r="A948" s="37"/>
+      <c r="A948" s="35"/>
       <c r="B948" s="4"/>
       <c r="C948" s="4"/>
       <c r="D948" s="4"/>
@@ -25895,7 +25936,7 @@
       <c r="X948" s="4"/>
     </row>
     <row r="949">
-      <c r="A949" s="37"/>
+      <c r="A949" s="35"/>
       <c r="B949" s="4"/>
       <c r="C949" s="4"/>
       <c r="D949" s="4"/>
@@ -25921,7 +25962,7 @@
       <c r="X949" s="4"/>
     </row>
     <row r="950">
-      <c r="A950" s="37"/>
+      <c r="A950" s="35"/>
       <c r="B950" s="4"/>
       <c r="C950" s="4"/>
       <c r="D950" s="4"/>
@@ -25947,7 +25988,7 @@
       <c r="X950" s="4"/>
     </row>
     <row r="951">
-      <c r="A951" s="37"/>
+      <c r="A951" s="35"/>
       <c r="B951" s="4"/>
       <c r="C951" s="4"/>
       <c r="D951" s="4"/>
@@ -25973,7 +26014,7 @@
       <c r="X951" s="4"/>
     </row>
     <row r="952">
-      <c r="A952" s="37"/>
+      <c r="A952" s="35"/>
       <c r="B952" s="4"/>
       <c r="C952" s="4"/>
       <c r="D952" s="4"/>
@@ -25999,7 +26040,7 @@
       <c r="X952" s="4"/>
     </row>
     <row r="953">
-      <c r="A953" s="37"/>
+      <c r="A953" s="35"/>
       <c r="B953" s="4"/>
       <c r="C953" s="4"/>
       <c r="D953" s="4"/>
@@ -26025,7 +26066,7 @@
       <c r="X953" s="4"/>
     </row>
     <row r="954">
-      <c r="A954" s="37"/>
+      <c r="A954" s="35"/>
       <c r="B954" s="4"/>
       <c r="C954" s="4"/>
       <c r="D954" s="4"/>
@@ -26051,7 +26092,7 @@
       <c r="X954" s="4"/>
     </row>
     <row r="955">
-      <c r="A955" s="37"/>
+      <c r="A955" s="35"/>
       <c r="B955" s="4"/>
       <c r="C955" s="4"/>
       <c r="D955" s="4"/>
@@ -26077,7 +26118,7 @@
       <c r="X955" s="4"/>
     </row>
     <row r="956">
-      <c r="A956" s="37"/>
+      <c r="A956" s="35"/>
       <c r="B956" s="4"/>
       <c r="C956" s="4"/>
       <c r="D956" s="4"/>
@@ -26103,7 +26144,7 @@
       <c r="X956" s="4"/>
     </row>
     <row r="957">
-      <c r="A957" s="37"/>
+      <c r="A957" s="35"/>
       <c r="B957" s="4"/>
       <c r="C957" s="4"/>
       <c r="D957" s="4"/>
@@ -26129,7 +26170,7 @@
       <c r="X957" s="4"/>
     </row>
     <row r="958">
-      <c r="A958" s="37"/>
+      <c r="A958" s="35"/>
       <c r="B958" s="4"/>
       <c r="C958" s="4"/>
       <c r="D958" s="4"/>
@@ -26155,7 +26196,7 @@
       <c r="X958" s="4"/>
     </row>
     <row r="959">
-      <c r="A959" s="37"/>
+      <c r="A959" s="35"/>
       <c r="B959" s="4"/>
       <c r="C959" s="4"/>
       <c r="D959" s="4"/>
@@ -26181,7 +26222,7 @@
       <c r="X959" s="4"/>
     </row>
     <row r="960">
-      <c r="A960" s="37"/>
+      <c r="A960" s="35"/>
       <c r="B960" s="4"/>
       <c r="C960" s="4"/>
       <c r="D960" s="4"/>
@@ -26207,7 +26248,7 @@
       <c r="X960" s="4"/>
     </row>
     <row r="961">
-      <c r="A961" s="37"/>
+      <c r="A961" s="35"/>
       <c r="B961" s="4"/>
       <c r="C961" s="4"/>
       <c r="D961" s="4"/>
@@ -26233,7 +26274,7 @@
       <c r="X961" s="4"/>
     </row>
     <row r="962">
-      <c r="A962" s="37"/>
+      <c r="A962" s="35"/>
       <c r="B962" s="4"/>
       <c r="C962" s="4"/>
       <c r="D962" s="4"/>
@@ -26259,7 +26300,7 @@
       <c r="X962" s="4"/>
     </row>
     <row r="963">
-      <c r="A963" s="37"/>
+      <c r="A963" s="35"/>
       <c r="B963" s="4"/>
       <c r="C963" s="4"/>
       <c r="D963" s="4"/>
@@ -26285,7 +26326,7 @@
       <c r="X963" s="4"/>
     </row>
     <row r="964">
-      <c r="A964" s="37"/>
+      <c r="A964" s="35"/>
       <c r="B964" s="4"/>
       <c r="C964" s="4"/>
       <c r="D964" s="4"/>
@@ -26311,7 +26352,7 @@
       <c r="X964" s="4"/>
     </row>
     <row r="965">
-      <c r="A965" s="37"/>
+      <c r="A965" s="35"/>
       <c r="B965" s="4"/>
       <c r="C965" s="4"/>
       <c r="D965" s="4"/>
@@ -26337,7 +26378,7 @@
       <c r="X965" s="4"/>
     </row>
     <row r="966">
-      <c r="A966" s="37"/>
+      <c r="A966" s="35"/>
       <c r="B966" s="4"/>
       <c r="C966" s="4"/>
       <c r="D966" s="4"/>
@@ -26363,7 +26404,7 @@
       <c r="X966" s="4"/>
     </row>
     <row r="967">
-      <c r="A967" s="37"/>
+      <c r="A967" s="35"/>
       <c r="B967" s="4"/>
       <c r="C967" s="4"/>
       <c r="D967" s="4"/>
@@ -26389,7 +26430,7 @@
       <c r="X967" s="4"/>
     </row>
     <row r="968">
-      <c r="A968" s="37"/>
+      <c r="A968" s="35"/>
       <c r="B968" s="4"/>
       <c r="C968" s="4"/>
       <c r="D968" s="4"/>
@@ -26415,7 +26456,7 @@
       <c r="X968" s="4"/>
     </row>
     <row r="969">
-      <c r="A969" s="37"/>
+      <c r="A969" s="35"/>
       <c r="B969" s="4"/>
       <c r="C969" s="4"/>
       <c r="D969" s="4"/>
@@ -26441,7 +26482,7 @@
       <c r="X969" s="4"/>
     </row>
     <row r="970">
-      <c r="A970" s="37"/>
+      <c r="A970" s="35"/>
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
       <c r="D970" s="4"/>
@@ -26467,7 +26508,7 @@
       <c r="X970" s="4"/>
     </row>
     <row r="971">
-      <c r="A971" s="37"/>
+      <c r="A971" s="35"/>
       <c r="B971" s="4"/>
       <c r="C971" s="4"/>
       <c r="D971" s="4"/>
@@ -26493,7 +26534,7 @@
       <c r="X971" s="4"/>
     </row>
     <row r="972">
-      <c r="A972" s="37"/>
+      <c r="A972" s="35"/>
       <c r="B972" s="4"/>
       <c r="C972" s="4"/>
       <c r="D972" s="4"/>
@@ -26519,7 +26560,7 @@
       <c r="X972" s="4"/>
     </row>
     <row r="973">
-      <c r="A973" s="37"/>
+      <c r="A973" s="35"/>
       <c r="B973" s="4"/>
       <c r="C973" s="4"/>
       <c r="D973" s="4"/>
@@ -26545,7 +26586,7 @@
       <c r="X973" s="4"/>
     </row>
     <row r="974">
-      <c r="A974" s="37"/>
+      <c r="A974" s="35"/>
       <c r="B974" s="4"/>
       <c r="C974" s="4"/>
       <c r="D974" s="4"/>
@@ -26571,7 +26612,7 @@
       <c r="X974" s="4"/>
     </row>
     <row r="975">
-      <c r="A975" s="37"/>
+      <c r="A975" s="35"/>
       <c r="B975" s="4"/>
       <c r="C975" s="4"/>
       <c r="D975" s="4"/>
@@ -26597,7 +26638,7 @@
       <c r="X975" s="4"/>
     </row>
     <row r="976">
-      <c r="A976" s="37"/>
+      <c r="A976" s="35"/>
       <c r="B976" s="4"/>
       <c r="C976" s="4"/>
       <c r="D976" s="4"/>
@@ -26623,7 +26664,7 @@
       <c r="X976" s="4"/>
     </row>
     <row r="977">
-      <c r="A977" s="37"/>
+      <c r="A977" s="35"/>
       <c r="B977" s="4"/>
       <c r="C977" s="4"/>
       <c r="D977" s="4"/>
@@ -26649,7 +26690,7 @@
       <c r="X977" s="4"/>
     </row>
     <row r="978">
-      <c r="A978" s="37"/>
+      <c r="A978" s="35"/>
       <c r="B978" s="4"/>
       <c r="C978" s="4"/>
       <c r="D978" s="4"/>
@@ -26675,7 +26716,7 @@
       <c r="X978" s="4"/>
     </row>
     <row r="979">
-      <c r="A979" s="37"/>
+      <c r="A979" s="35"/>
       <c r="B979" s="4"/>
       <c r="C979" s="4"/>
       <c r="D979" s="4"/>
@@ -26701,7 +26742,7 @@
       <c r="X979" s="4"/>
     </row>
     <row r="980">
-      <c r="A980" s="37"/>
+      <c r="A980" s="35"/>
       <c r="B980" s="4"/>
       <c r="C980" s="4"/>
       <c r="D980" s="4"/>
@@ -26727,7 +26768,7 @@
       <c r="X980" s="4"/>
     </row>
     <row r="981">
-      <c r="A981" s="37"/>
+      <c r="A981" s="35"/>
       <c r="B981" s="4"/>
       <c r="C981" s="4"/>
       <c r="D981" s="4"/>
@@ -26753,7 +26794,7 @@
       <c r="X981" s="4"/>
     </row>
     <row r="982">
-      <c r="A982" s="37"/>
+      <c r="A982" s="35"/>
       <c r="B982" s="4"/>
       <c r="C982" s="4"/>
       <c r="D982" s="4"/>
@@ -26779,7 +26820,7 @@
       <c r="X982" s="4"/>
     </row>
     <row r="983">
-      <c r="A983" s="37"/>
+      <c r="A983" s="35"/>
       <c r="B983" s="4"/>
       <c r="C983" s="4"/>
       <c r="D983" s="4"/>
@@ -26805,7 +26846,7 @@
       <c r="X983" s="4"/>
     </row>
     <row r="984">
-      <c r="A984" s="37"/>
+      <c r="A984" s="35"/>
       <c r="B984" s="4"/>
       <c r="C984" s="4"/>
       <c r="D984" s="4"/>
@@ -26831,7 +26872,7 @@
       <c r="X984" s="4"/>
     </row>
     <row r="985">
-      <c r="A985" s="37"/>
+      <c r="A985" s="35"/>
       <c r="B985" s="4"/>
       <c r="C985" s="4"/>
       <c r="D985" s="4"/>
@@ -26857,7 +26898,7 @@
       <c r="X985" s="4"/>
     </row>
     <row r="986">
-      <c r="A986" s="37"/>
+      <c r="A986" s="35"/>
       <c r="B986" s="4"/>
       <c r="C986" s="4"/>
       <c r="D986" s="4"/>
@@ -26883,7 +26924,7 @@
       <c r="X986" s="4"/>
     </row>
     <row r="987">
-      <c r="A987" s="37"/>
+      <c r="A987" s="35"/>
       <c r="B987" s="4"/>
       <c r="C987" s="4"/>
       <c r="D987" s="4"/>
@@ -26909,7 +26950,7 @@
       <c r="X987" s="4"/>
     </row>
     <row r="988">
-      <c r="A988" s="37"/>
+      <c r="A988" s="35"/>
       <c r="B988" s="4"/>
       <c r="C988" s="4"/>
       <c r="D988" s="4"/>
@@ -26935,7 +26976,7 @@
       <c r="X988" s="4"/>
     </row>
     <row r="989">
-      <c r="A989" s="37"/>
+      <c r="A989" s="35"/>
       <c r="B989" s="4"/>
       <c r="C989" s="4"/>
       <c r="D989" s="4"/>
@@ -26961,7 +27002,7 @@
       <c r="X989" s="4"/>
     </row>
     <row r="990">
-      <c r="A990" s="37"/>
+      <c r="A990" s="35"/>
       <c r="B990" s="4"/>
       <c r="C990" s="4"/>
       <c r="D990" s="4"/>
@@ -26986,8 +27027,34 @@
       <c r="W990" s="4"/>
       <c r="X990" s="4"/>
     </row>
+    <row r="991">
+      <c r="A991" s="35"/>
+      <c r="B991" s="4"/>
+      <c r="C991" s="4"/>
+      <c r="D991" s="4"/>
+      <c r="E991" s="4"/>
+      <c r="F991" s="4"/>
+      <c r="G991" s="4"/>
+      <c r="H991" s="4"/>
+      <c r="I991" s="4"/>
+      <c r="J991" s="4"/>
+      <c r="K991" s="4"/>
+      <c r="L991" s="4"/>
+      <c r="M991" s="4"/>
+      <c r="N991" s="4"/>
+      <c r="O991" s="4"/>
+      <c r="P991" s="4"/>
+      <c r="Q991" s="4"/>
+      <c r="R991" s="4"/>
+      <c r="S991" s="4"/>
+      <c r="T991" s="4"/>
+      <c r="U991" s="4"/>
+      <c r="V991" s="4"/>
+      <c r="W991" s="4"/>
+      <c r="X991" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -26999,6 +27066,7 @@
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0" horizontalCentered="1"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0" footer="0"/>
